--- a/kobo/gestores_semana2_diagnostico.xlsx
+++ b/kobo/gestores_semana2_diagnostico.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nome da escola</t>
+          <t>Nome do local de atuação</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Código INEP (8 dígitos; deixe em branco se não souber)</t>
+          <t>Código INEP (apenas se for local; 8 dígitos)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Q2.1. Onde a Educação Ambiental acontece hoje na escola</t>
+          <t>Q2.1. Onde a Educação Ambiental acontece hoje neste local</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q2.2. Como caracterizar a institucionalização da Educação Ambiental na escola?</t>
+          <t>Q2.2. Como caracterizar a institucionalização da Educação Ambiental neste local?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Q2.24. Quais métodos/estratégias a escola já utilizou em práticas de Educação Ambiental?</t>
+          <t>Q2.24. Quais métodos/estratégias o local já utilizou em práticas de Educação Ambiental?</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Q2.33. Quão confiante você se sente, como gestor(a), para liderar e apoiar a Educação Ambiental na escola hoje?</t>
+          <t>Q2.33. Quão confiante você se sente, como gestor(a), para liderar e apoiar a Educação Ambiental neste local hoje?</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Q2.42. Essa leitura reflete a realidade da escola?</t>
+          <t>Q2.42. Essa leitura reflete a realidade do local?</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Q3.6. Nível de envolvimento das famílias com a escola</t>
+          <t>Q3.6. Nível de envolvimento das famílias com o local</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Q3.8. Frequência de atividades da escola com o território/comunidade</t>
+          <t>Q3.8. Frequência de atividades do local com o território/comunidade</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Q3.10. A escola tem mecanismos de escuta da comunidade?</t>
+          <t>Q3.10. O local tem mecanismos de escuta da comunidade?</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Q3.10a. Quais instâncias de decisão colegiada existem e funcionam na escola?</t>
+          <t>Q3.10a. Quais instâncias de decisão colegiada existem e funcionam neste local?</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Existência, contato, parceria e articulação permanente são níveis diferentes — não confunda um com o outro. Só marque "Parceria" ou "Articulação permanente" se a escola já colabora de fato com esse ator; se ele apenas existe no território ou já houve um contato pontual, isso ainda NÃO é parceria. Use "Adicionar" para registrar um ator por vez.</t>
+          <t>Existência, contato, parceria e articulação permanente são níveis diferentes — não confunda um com o outro. Só marque "Parceria" ou "Articulação permanente" se o local já colabora de fato com esse ator; se ele apenas existe no território ou já houve um contato pontual, isso ainda NÃO é parceria. Use "Adicionar" para registrar um ator por vez.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Q3.11. A escola sabe a quem contatar em uma emergência climática?</t>
+          <t>Q3.11. O local sabe a quem contatar em uma emergência climática?</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Q3.16. Canais de comunicação da escola com a comunidade</t>
+          <t>Q3.16. Canais de comunicação do local com a comunidade</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Materiais produzidos pela escola</t>
+          <t>Materiais produzidos pelo local</t>
         </is>
       </c>
     </row>

--- a/kobo/gestores_semana2_diagnostico.xlsx
+++ b/kobo/gestores_semana2_diagnostico.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J164"/>
+  <dimension ref="A1:J171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -579,12 +579,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>identificacao</t>
+          <t>tcle</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Identificação (igual à Semana 1)</t>
+          <t>Termo de Consentimento</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -598,25 +598,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>id_escola</t>
+          <t>tcle_texto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nome do local de atuação</t>
+          <t>TERMO DE CONSENTIMENTO LIVRE E ESCLARECIDO. Você está sendo convidado(a) a responder este Diagnóstico Socioambiental, Climático e de Educação Ambiental. A participação é voluntária: você pode recusar ou interromper a qualquer momento, sem qualquer prejuízo. As informações fornecidas, inclusive seus dados pessoais e de identificação (nome, função, local de atuação), serão tratadas com sigilo, NÃO serão compartilhadas com terceiros de forma que identifique você ou o seu local de atuação e serão utilizadas apenas para compor um banco de dados do projeto. Eventuais resultados e relatórios serão apresentados somente de forma agregada, sem identificar pessoas. O tratamento dos dados segue a Lei Geral de Proteção de Dados (Lei nº 13.709/2018). Em caso de dúvidas, procure a equipe responsável pelo projeto.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -626,58 +622,54 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one concordo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>id_inep</t>
+          <t>tcle_consentimento</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Código INEP (apenas se for local; 8 dígitos)</t>
+          <t>Li o termo acima e concordo em participar e em ter minhas respostas e meus dados utilizados no banco de dados do projeto, nos termos descritos.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>regex(., '^[0-9]{8}$')</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>O código INEP deve ter 8 dígitos.</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>id_nome</t>
+          <t>tcle_recusa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seu nome</t>
+          <t>Sem o seu consentimento não é possível continuar. Obrigado(a) pelo seu tempo! Você pode encerrar o formulário.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>${tcle_consentimento} = 'nao_concordo'</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -707,17 +699,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>etapa2</t>
+          <t>conteudo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Etapa 2 — Educação Ambiental</t>
+          <t>Diagnóstico</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>${tcle_consentimento} = 'concordo'</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -726,17 +722,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple onde_ea</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>q2_1</t>
+          <t>identificacao</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Q2.1. Onde a Educação Ambiental acontece hoje neste local</t>
+          <t>Identificação (igual à Semana 1)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -755,21 +751,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>q2_1_outro</t>
+          <t>id_escola</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Nome do local de atuação</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>selected(${q2_1}, 'outro')</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -778,49 +774,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one instit_ea</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>q2_2</t>
+          <t>id_inep</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q2.2. Como caracterizar a institucionalização da Educação Ambiental neste local?</t>
+          <t>Código INEP (apenas se for local; 8 dígitos)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>regex(., '^[0-9]{8}$')</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O código INEP deve ter 8 dígitos.</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one ppp_sit</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>q2_3</t>
+          <t>id_nome</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Q2.3. Situação da Educação Ambiental no Projeto Político-Pedagógico (PPP)</t>
+          <t>Seu nome</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -830,31 +834,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>q2_4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Q2.4. Como a Educação Ambiental aparece no PPP?</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>${q2_3} = 'presente_e_detalhada' or ${q2_3} = 'presente_de_forma_generica'</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -862,26 +850,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one ppp_pratica</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>q2_5</t>
+          <t>etapa2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Q2.5. O que está no PPP se traduz em prática?</t>
+          <t>Etapa 2 — Educação Ambiental</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>${q2_3} = 'presente_e_detalhada' or ${q2_3} = 'presente_de_forma_generica'</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -890,17 +874,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple areas_curr</t>
+          <t>select_multiple onde_ea</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>q2_6</t>
+          <t>q2_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Q2.6. Áreas curriculares que já trabalharam Educação Ambiental</t>
+          <t>Q2.1. Onde a Educação Ambiental acontece hoje neste local</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -919,7 +903,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>q2_6_outro</t>
+          <t>q2_1_outro</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -931,7 +915,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>selected(${q2_6}, 'outro')</t>
+          <t>selected(${q2_1}, 'outro')</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -942,25 +926,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple articulacao</t>
+          <t>select_one instit_ea</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>q2_7</t>
+          <t>q2_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Q2.7. Como ocorre a articulação entre áreas/disciplinas?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Mais de uma forma de articulação pode coexistir — marque todas que se aplicam.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>Q2.2. Como caracterizar a institucionalização da Educação Ambiental neste local?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -970,17 +954,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one freq_ea</t>
+          <t>select_one ppp_sit</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>q2_8</t>
+          <t>q2_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Q2.8. Frequência das práticas de Educação Ambiental</t>
+          <t>Q2.3. Situação da Educação Ambiental no Projeto Político-Pedagógico (PPP)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -994,23 +978,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple contexto_ea</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>q2_9</t>
+          <t>q2_4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Q2.9. Em que contextos essas práticas costumam acontecer?</t>
+          <t>Q2.4. Como a Educação Ambiental aparece no PPP?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>${q2_3} = 'presente_e_detalhada' or ${q2_3} = 'presente_de_forma_generica'</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -1018,24 +1010,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one ppp_pratica</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>q2_9_outro</t>
+          <t>q2_5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q2.5. O que está no PPP se traduz em prática?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>selected(${q2_9}, 'outro')</t>
+          <t>${q2_3} = 'presente_e_detalhada' or ${q2_3} = 'presente_de_forma_generica'</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1046,29 +1038,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>select_multiple areas_curr</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>q2_10</t>
+          <t>q2_6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Q2.10. Houve alguma atividade concreta de Educação Ambiental nos últimos meses?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Se não houve, tudo bem responder que não — não é necessário inventar uma prática.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+          <t>Q2.6. Áreas curriculares que já trabalharam Educação Ambiental</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -1083,19 +1067,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>q2_11</t>
+          <t>q2_6_outro</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Q2.11. Quando ocorreu?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>${q2_10}='sim'</t>
+          <t>selected(${q2_6}, 'outro')</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1106,26 +1090,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple articulacao</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>q2_12</t>
+          <t>q2_7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Q2.12. Qual foi o tema?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Q2.7. Como ocorre a articulação entre áreas/disciplinas?</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Mais de uma forma de articulação pode coexistir — marque todas que se aplicam.</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>${q2_10}='sim'</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1134,31 +1118,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one freq_ea</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>q2_13</t>
+          <t>q2_8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Q2.13. O que motivou essa atividade?</t>
+          <t>Q2.8. Frequência das práticas de Educação Ambiental</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>${q2_10}='sim'</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -1166,26 +1142,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_multiple quem_planejou</t>
+          <t>select_multiple contexto_ea</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>q2_14</t>
+          <t>q2_9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Q2.14. Quem planejou essa atividade?</t>
+          <t>Q2.9. Em que contextos essas práticas costumam acontecer?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>${q2_10}='sim'</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1199,7 +1171,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>q2_14_outro</t>
+          <t>q2_9_outro</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1211,7 +1183,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>(${q2_10}='sim') and selected(${q2_14}, 'outro')</t>
+          <t>selected(${q2_9}, 'outro')</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1222,26 +1194,30 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>q2_15</t>
+          <t>q2_10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Q2.15. Qual foi a duração?</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>${q2_10}='sim'</t>
-        </is>
-      </c>
+          <t>Q2.10. Houve alguma atividade concreta de Educação Ambiental nos últimos meses?</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Se não houve, tudo bem responder que não — não é necessário inventar uma prática.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1250,17 +1226,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>select_one papel_estud</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>q2_16</t>
+          <t>q2_11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Q2.16. Qual foi o papel dos estudantes?</t>
+          <t>Q2.11. Quando ocorreu?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1278,17 +1254,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>q2_17</t>
+          <t>q2_12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Q2.17. Essa atividade teve relação com o território?</t>
+          <t>Q2.12. Qual foi o tema?</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1311,19 +1287,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>q2_18</t>
+          <t>q2_13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Q2.18. Que problema territorial foi abordado?</t>
+          <t>Q2.13. O que motivou essa atividade?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>(${q2_10}='sim') and ${q2_17}='sim'</t>
+          <t>${q2_10}='sim'</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1338,17 +1314,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_one continuidade_ativ</t>
+          <t>select_multiple quem_planejou</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>q2_19</t>
+          <t>q2_14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Q2.19. Essa atividade tem perspectiva de continuidade?</t>
+          <t>Q2.14. Quem planejou essa atividade?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1371,26 +1347,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>q2_20</t>
+          <t>q2_14_outro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Q2.20. O que essa atividade mudou ou gerou?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>${q2_10}='sim'</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+          <t>(${q2_10}='sim') and selected(${q2_14}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
@@ -1398,27 +1370,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>t2_21</t>
+          <t>q2_15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Q2.21. Com que frequência cada tema é trabalhado?</t>
+          <t>Q2.15. Qual foi a duração?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>table-list</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>${q2_10}='sim'</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -1426,22 +1398,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>select_one freq5</t>
+          <t>select_one papel_estud</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>q2_21_01</t>
+          <t>q2_16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Q2.16. Qual foi o papel dos estudantes?</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>${q2_10}='sim'</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1450,22 +1426,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>select_one freq5</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>q2_21_02</t>
+          <t>q2_17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Biodiversidade</t>
+          <t>Q2.17. Essa atividade teve relação com o território?</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>${q2_10}='sim'</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -1474,23 +1454,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>select_one freq5</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>q2_21_03</t>
+          <t>q2_18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Resíduos</t>
+          <t>Q2.18. Que problema territorial foi abordado?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>(${q2_10}='sim') and ${q2_17}='sim'</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -1498,22 +1486,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>select_one freq5</t>
+          <t>select_one continuidade_ativ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>q2_21_04</t>
+          <t>q2_19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mudanças climáticas</t>
+          <t>Q2.19. Essa atividade tem perspectiva de continuidade?</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>${q2_10}='sim'</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1522,23 +1514,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>select_one freq5</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>q2_21_05</t>
+          <t>q2_20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Q2.20. O que essa atividade mudou ou gerou?</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>${q2_10}='sim'</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
@@ -1546,23 +1546,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>select_one freq5</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>q2_21_06</t>
+          <t>t2_21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Q2.21. Com que frequência cada tema é trabalhado?</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>table-list</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -1575,12 +1579,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>q2_21_07</t>
+          <t>q2_21_01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1599,12 +1603,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>q2_21_08</t>
+          <t>q2_21_02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saneamento</t>
+          <t>Biodiversidade</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1623,12 +1627,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>q2_21_09</t>
+          <t>q2_21_03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>Resíduos</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1647,12 +1651,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>q2_21_10</t>
+          <t>q2_21_04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Riscos/desastres</t>
+          <t>Mudanças climáticas</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1671,12 +1675,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>q2_21_11</t>
+          <t>q2_21_05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Justiça socioambiental</t>
+          <t>Energia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1695,12 +1699,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>q2_21_12</t>
+          <t>q2_21_06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Território</t>
+          <t>Alimentação</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1719,12 +1723,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>q2_21_13</t>
+          <t>q2_21_07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Conflitos</t>
+          <t>Consumo</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1743,12 +1747,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>q2_21_14</t>
+          <t>q2_21_08</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Povos e comunidades tradicionais</t>
+          <t>Saneamento</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1767,12 +1771,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>q2_21_15</t>
+          <t>q2_21_09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Saúde</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1786,11 +1790,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
+          <t>select_one freq5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>q2_21_10</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Riscos/desastres</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
@@ -1802,31 +1814,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one freq5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>q2_21a</t>
+          <t>q2_21_11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Q2.21a. Você marcou uma frequência para "Outros" temas acima — quais temas são esses?</t>
+          <t>Justiça socioambiental</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>${q2_21_15} != ''</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -1834,17 +1838,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>select_multiple temas</t>
+          <t>select_one freq5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>q2_22</t>
+          <t>q2_21_12</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Q2.22. Quais temas são mais difíceis de trabalhar?</t>
+          <t>Território</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1858,26 +1862,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one freq5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>q2_22_outro</t>
+          <t>q2_21_13</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Conflitos</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>selected(${q2_22}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -1886,26 +1886,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>select_multiple causa_dif</t>
+          <t>select_one freq5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>q2_23</t>
+          <t>q2_21_14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Q2.23. O que causa essa dificuldade?</t>
+          <t>Povos e comunidades tradicionais</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>${q2_22} != ''</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -1914,26 +1910,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one freq5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>q2_23_outro</t>
+          <t>q2_21_15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>(${q2_22} != '') and selected(${q2_23}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -1942,24 +1934,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>select_multiple metodos</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>q2_24</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Q2.24. Quais métodos/estratégias o local já utilizou em práticas de Educação Ambiental?</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Marque todos os que já foram usados, mesmo que raramente.</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
@@ -1975,22 +1955,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>q2_24_outro</t>
+          <t>q2_21a</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q2.21a. Você marcou uma frequência para "Outros" temas acima — quais temas são esses?</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>selected(${q2_24}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>${q2_21_15} != ''</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -1998,24 +1982,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>select_one metodos</t>
+          <t>select_multiple temas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>q2_25</t>
+          <t>q2_22</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Q2.25. Qual método/estratégia é o mais utilizado no dia a dia?</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Diferente da pergunta anterior (que pedia todos os já usados, mesmo raramente), esta pede só UM — o predominante. A lista de opções é a mesma da pergunta anterior.</t>
-        </is>
-      </c>
+          <t>Q2.22. Quais temas são mais difíceis de trabalhar?</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
@@ -2031,7 +2011,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>q2_25_outro</t>
+          <t>q2_22_outro</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2043,7 +2023,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>${q2_25}='outro'</t>
+          <t>selected(${q2_22}, 'outro')</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -2054,26 +2034,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>select_one freq5</t>
+          <t>select_multiple causa_dif</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>q2_26</t>
+          <t>q2_23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Q2.26. Frequência de uso do território como espaço pedagógico</t>
+          <t>Q2.23. O que causa essa dificuldade?</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>${q2_22} != ''</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -2082,22 +2062,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>q2_27</t>
+          <t>q2_23_outro</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Q2.27. Problemas locais/territoriais são abordados nas práticas de EA?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>(${q2_22} != '') and selected(${q2_23}, 'outro')</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -2106,20 +2090,24 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>select_multiple metodos</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>q2_28</t>
+          <t>q2_24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Q2.28. Houve formação recente em Educação Ambiental?</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Q2.24. Quais métodos/estratégias o local já utilizou em práticas de Educação Ambiental?</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Marque todos os que já foram usados, mesmo que raramente.</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
@@ -2135,19 +2123,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>q2_29</t>
+          <t>q2_24_outro</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Q2.29. Quem ofereceu a formação?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>${q2_28}='sim'</t>
+          <t>selected(${q2_24}, 'outro')</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -2158,31 +2146,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one metodos</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>q2_30</t>
+          <t>q2_25</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Q2.30. Quais temas foram abordados?</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Q2.25. Qual método/estratégia é o mais utilizado no dia a dia?</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Diferente da pergunta anterior (que pedia todos os já usados, mesmo raramente), esta pede só UM — o predominante. A lista de opções é a mesma da pergunta anterior.</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>${q2_28}='sim'</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
@@ -2190,24 +2174,24 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>select_one impacto_form</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>q2_31</t>
+          <t>q2_25_outro</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Q2.31. Qual o impacto dessa formação na prática?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>${q2_28}='sim'</t>
+          <t>${q2_25}='outro'</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -2218,31 +2202,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one freq5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>q2_32</t>
+          <t>q2_26</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Q2.32. Dê um exemplo desse impacto</t>
+          <t>Q2.26. Frequência de uso do território como espaço pedagógico</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>${q2_28}='sim'</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
@@ -2250,31 +2230,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>select_one confianca</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>q2_33</t>
+          <t>q2_27</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Q2.33. Quão confiante você se sente, como gestor(a), para liderar e apoiar a Educação Ambiental neste local hoje?</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Escala de 1 (nada confiante) a 5 (muito confiante).</t>
-        </is>
-      </c>
+          <t>Q2.27. Problemas locais/territoriais são abordados nas práticas de EA?</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>horizontal-compact</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
@@ -2282,17 +2254,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>select_multiple apoio</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>q2_34</t>
+          <t>q2_28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Q2.34. Que tipo de apoio faria diferença?</t>
+          <t>Q2.28. Houve formação recente em Educação Ambiental?</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -2311,19 +2283,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>q2_34_outro</t>
+          <t>q2_29</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q2.29. Quem ofereceu a formação?</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>selected(${q2_34}, 'outro')</t>
+          <t>${q2_28}='sim'</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2334,25 +2306,29 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>t2_35</t>
+          <t>q2_30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Q2.35. Intensidade de cada barreira percebida</t>
+          <t>Q2.30. Quais temas foram abordados?</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>${q2_28}='sim'</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>table-list</t>
+          <t>multiline</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -2362,22 +2338,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>select_one intensidade</t>
+          <t>select_one impacto_form</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>q2_35_01</t>
+          <t>q2_31</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Q2.31. Qual o impacto dessa formação na prática?</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>${q2_28}='sim'</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -2386,23 +2366,31 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>select_one intensidade</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>q2_35_02</t>
+          <t>q2_32</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Currículo sobrecarregado</t>
+          <t>Q2.32. Dê um exemplo desse impacto</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>${q2_28}='sim'</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
@@ -2410,23 +2398,31 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>select_one intensidade</t>
+          <t>select_one confianca</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>q2_35_03</t>
+          <t>q2_33</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Formação</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Q2.33. Quão confiante você se sente, como gestor(a), para liderar e apoiar a Educação Ambiental neste local hoje?</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Escala de 1 (nada confiante) a 5 (muito confiante).</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>horizontal-compact</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
@@ -2434,17 +2430,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>select_one intensidade</t>
+          <t>select_multiple apoio</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>q2_35_04</t>
+          <t>q2_34</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Materiais</t>
+          <t>Q2.34. Que tipo de apoio faria diferença?</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2458,22 +2454,26 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>select_one intensidade</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>q2_35_05</t>
+          <t>q2_34_outro</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>selected(${q2_34}, 'outro')</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -2482,23 +2482,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>select_one intensidade</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>q2_35_06</t>
+          <t>t2_35</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Q2.35. Intensidade de cada barreira percebida</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>table-list</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
@@ -2511,12 +2515,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>q2_35_07</t>
+          <t>q2_35_01</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Planejamento coletivo</t>
+          <t>Tempo</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2535,12 +2539,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>q2_35_08</t>
+          <t>q2_35_02</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Interdisciplinaridade</t>
+          <t>Currículo sobrecarregado</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2559,12 +2563,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>q2_35_09</t>
+          <t>q2_35_03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Informações territoriais</t>
+          <t>Formação</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -2583,12 +2587,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>q2_35_10</t>
+          <t>q2_35_04</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Descontinuidade</t>
+          <t>Materiais</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2607,12 +2611,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>q2_35_11</t>
+          <t>q2_35_05</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Rotatividade de profissionais</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2631,12 +2635,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>q2_35_12</t>
+          <t>q2_35_06</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2650,11 +2654,19 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
+          <t>select_one intensidade</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>q2_35_07</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Planejamento coletivo</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
@@ -2666,31 +2678,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one intensidade</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>q2_35a</t>
+          <t>q2_35_08</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Q2.35a. Você marcou uma intensidade para "Outras" barreiras acima — quais são elas?</t>
+          <t>Interdisciplinaridade</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>${q2_35_12} != ''</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
@@ -2698,17 +2702,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>select_one barreiras</t>
+          <t>select_one intensidade</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>q2_36</t>
+          <t>q2_35_09</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Q2.36. Principal barreira hoje</t>
+          <t>Informações territoriais</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -2722,26 +2726,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one intensidade</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>q2_36_outro</t>
+          <t>q2_35_10</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Descontinuidade</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>${q2_36}='outro'</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -2750,17 +2750,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>select_multiple materiais</t>
+          <t>select_one intensidade</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>q2_37</t>
+          <t>q2_35_11</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Q2.37. Materiais didáticos utilizados</t>
+          <t>Rotatividade de profissionais</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -2774,26 +2774,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one intensidade</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>q2_37_outro</t>
+          <t>q2_35_12</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>selected(${q2_37}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -2802,19 +2798,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>select_one acesso_mat</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>q2_38</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Q2.38. Facilidade de acesso a esses materiais</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
@@ -2831,17 +2819,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>q2_39</t>
+          <t>q2_35a</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Q2.39. Que materiais fazem falta?</t>
+          <t>Q2.35a. Você marcou uma intensidade para "Outras" barreiras acima — quais são elas?</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>${q2_35_12} != ''</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
           <t>multiline</t>
@@ -2854,25 +2846,21 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>select_one part_estud</t>
+          <t>select_one barreiras</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>q2_40</t>
+          <t>q2_36</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Q2.40. Como caracterizar, de modo geral, a participação dos estudantes nas ações de EA?</t>
+          <t>Q2.36. Principal barreira hoje</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
@@ -2882,22 +2870,26 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>select_one continuidade_proj</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>q2_41</t>
+          <t>q2_36_outro</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Q2.41. De modo geral, a continuidade dos projetos de EA está...</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>${q2_36}='outro'</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -2906,37 +2898,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>select_multiple apoio_gestao</t>
+          <t>select_multiple materiais</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>q2_41a</t>
+          <t>q2_37</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Q2.41a. Como a gestão escolar apoia a Educação Ambiental hoje?</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Pense no que a gestão efetivamente faz, não no que deveria fazer.</t>
-        </is>
-      </c>
+          <t>Q2.37. Materiais didáticos utilizados</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>not(selected(., 'nenhum') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>"Nenhum apoio sistemático" não pode ser combinado com outras opções.</t>
-        </is>
-      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
@@ -2947,7 +2927,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>q2_41a_outro</t>
+          <t>q2_37_outro</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2959,7 +2939,7 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>selected(${q2_41a}, 'outro')</t>
+          <t>selected(${q2_37}, 'outro')</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -2970,17 +2950,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one acesso_mat</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>e2_leitura</t>
+          <t>q2_38</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Como o sistema está lendo suas respostas (revise e confirme) — no Kobo não há leitura automática: a tutoria/quem aplica o formulário deve revisar as respostas desta etapa antes de responder abaixo.</t>
+          <t>Q2.38. Facilidade de acesso a esses materiais</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2994,23 +2974,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>q2_42</t>
+          <t>q2_39</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Q2.42. Essa leitura reflete a realidade do local?</t>
+          <t>Q2.39. Que materiais fazem falta?</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
@@ -3018,31 +3002,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one part_estud</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>q2_43</t>
+          <t>q2_40</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Q2.43. O que precisa ser corrigido ou complementado?</t>
+          <t>Q2.40. Como caracterizar, de modo geral, a participação dos estudantes nas ações de EA?</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>${q2_42}='nao' or ${q2_42}='nao_sabemos'</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
@@ -3050,17 +3030,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>select_one continuidade_proj</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>evid_e2</t>
+          <t>q2_41</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Evidências — Evidências sobre Educação Ambiental</t>
+          <t>Q2.41. De modo geral, a continuidade dos projetos de EA está...</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -3074,46 +3054,62 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple apoio_gestao</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>evid_e2_nota</t>
+          <t>q2_41a</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Q2.41a. Como a gestão escolar apoia a Educação Ambiental hoje?</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Pense no que a gestão efetivamente faz, não no que deveria fazer.</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nenhum') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>"Nenhum apoio sistemático" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>select_one tipo_evid</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>evid_e2_tipo</t>
+          <t>q2_41a_outro</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tipo de evidência</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>selected(${q2_41a}, 'outro')</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
@@ -3122,26 +3118,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>evid_e2_tipo_outro</t>
+          <t>e2_leitura</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Como o sistema está lendo suas respostas (revise e confirme) — no Kobo não há leitura automática: a tutoria/quem aplica o formulário deve revisar as respostas desta etapa antes de responder abaixo.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>${evid_e2_tipo}='outro'</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
@@ -3150,27 +3142,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>evid_e2_desc</t>
+          <t>q2_42</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Descreva a evidência</t>
+          <t>Q2.42. Essa leitura reflete a realidade do local?</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
@@ -3178,23 +3166,31 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>evid_e2_anexo</t>
+          <t>q2_43</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Anexo (foto/documento) — opcional</t>
+          <t>Q2.43. O que precisa ser corrigido ou complementado?</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>${q2_42}='nao' or ${q2_42}='nao_sabemos'</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
@@ -3202,11 +3198,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
+          <t>begin_repeat</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>evid_e2</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Evidências — Evidências sobre Educação Ambiental</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
@@ -3218,11 +3222,19 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>evid_e2_nota</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
@@ -3234,17 +3246,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one tipo_evid</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>etapa3</t>
+          <t>evid_e2_tipo</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Etapa 3 — Participação e Redes</t>
+          <t>Tipo de evidência</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -3258,22 +3270,26 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>select_multiple quem_part</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>q3_1</t>
+          <t>evid_e2_tipo_outro</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Q3.1. Quem participa das ações de Educação Ambiental hoje?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>${evid_e2_tipo}='outro'</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
@@ -3287,22 +3303,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>q3_1_outro</t>
+          <t>evid_e2_desc</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Descreva a evidência</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>selected(${q3_1}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
@@ -3310,24 +3326,20 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>select_one nivel_part</t>
+          <t>file</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>q3_2</t>
+          <t>evid_e2_anexo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Q3.2. Como essa participação costuma acontecer?</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Participação não é sinônimo de presença — o que importa é o nível de envolvimento na decisão.</t>
-        </is>
-      </c>
+          <t>Anexo (foto/documento) — opcional</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
@@ -3338,58 +3350,30 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>select_multiple esp_estud</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>q3_3</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Q3.3. Espaços de participação estudantil existentes</t>
-        </is>
-      </c>
+          <t>end_repeat</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>not(selected(., 'nenhum') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>"Nenhum" não pode ser combinado com outras opções.</t>
-        </is>
-      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>q3_3_outro</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>selected(${q3_3}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
@@ -3398,27 +3382,23 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>q3_4</t>
+          <t>etapa3</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Q3.4. Descreva práticas concretas de participação estudantil (se houver)</t>
+          <t>Etapa 3 — Participação e Redes</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
@@ -3426,17 +3406,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>select_multiple quem_part</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>q3_5</t>
+          <t>q3_1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Q3.5. O nível de participação estudantil descrito na Etapa 2 continua condizente?</t>
+          <t>Q3.1. Quem participa das ações de Educação Ambiental hoje?</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -3450,22 +3430,26 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>select_one env_fam</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>q3_6</t>
+          <t>q3_1_outro</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Q3.6. Nível de envolvimento das famílias com o local</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>selected(${q3_1}, 'outro')</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
@@ -3474,20 +3458,24 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>select_multiple barr_fam</t>
+          <t>select_one nivel_part</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>q3_7</t>
+          <t>q3_2</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Q3.7. Barreiras à participação das famílias</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>Q3.2. Como essa participação costuma acontecer?</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Participação não é sinônimo de presença — o que importa é o nível de envolvimento na decisão.</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
@@ -3498,50 +3486,58 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple esp_estud</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>q3_7_outro</t>
+          <t>q3_3</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q3.3. Espaços de participação estudantil existentes</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>selected(${q3_7}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nenhum') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>"Nenhum" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>select_one freq5</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>q3_8</t>
+          <t>q3_3_outro</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Q3.8. Frequência de atividades do local com o território/comunidade</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>selected(${q3_3}, 'outro')</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
@@ -3555,12 +3551,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>q3_9</t>
+          <t>q3_4</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Q3.9. Quais atividades com o território/comunidade já ocorreram?</t>
+          <t>Q3.4. Descreva práticas concretas de participação estudantil (se houver)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3583,12 +3579,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>q3_10</t>
+          <t>q3_5</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Q3.10. O local tem mecanismos de escuta da comunidade?</t>
+          <t>Q3.5. O nível de participação estudantil descrito na Etapa 2 continua condizente?</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3602,58 +3598,46 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>select_multiple instancias</t>
+          <t>select_one env_fam</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>q3_10a</t>
+          <t>q3_6</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Q3.10a. Quais instâncias de decisão colegiada existem e funcionam neste local?</t>
+          <t>Q3.6. Nível de envolvimento das famílias com o local</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>not(selected(., 'nenhuma') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>"Nenhuma" não pode ser combinada com outras opções.</t>
-        </is>
-      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple barr_fam</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>q3_10a_outro</t>
+          <t>q3_7</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q3.7. Barreiras à participação das famílias</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>selected(${q3_10a}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
@@ -3662,22 +3646,26 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>q3_10b</t>
+          <t>q3_7_outro</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Q3.10b. A gestão tem autonomia para decidir e destinar recursos a ações de Educação Ambiental?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>selected(${q3_7}, 'outro')</t>
+        </is>
+      </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
@@ -3686,17 +3674,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>select_one freq5</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>net_actors</t>
+          <t>q3_8</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Atores do território (NET_ACTORS)</t>
+          <t>Q3.8. Frequência de atividades do local com o território/comunidade</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3710,23 +3698,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>net_nota</t>
+          <t>q3_9</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Existência, contato, parceria e articulação permanente são níveis diferentes — não confunda um com o outro. Só marque "Parceria" ou "Articulação permanente" se o local já colabora de fato com esse ator; se ele apenas existe no território ou já houve um contato pontual, isso ainda NÃO é parceria. Use "Adicionar" para registrar um ator por vez.</t>
+          <t>Q3.9. Quais atividades com o território/comunidade já ocorreram?</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
@@ -3734,17 +3726,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>select_one cat_ator</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>net_cat</t>
+          <t>q3_10</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Categoria do ator</t>
+          <t>Q3.10. O local tem mecanismos de escuta da comunidade?</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -3758,46 +3750,58 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple instancias</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>net_nome</t>
+          <t>q3_10a</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Nome do ator (ex.: UBS Vila Nova)</t>
+          <t>Q3.10a. Quais instâncias de decisão colegiada existem e funcionam neste local?</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nenhuma') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>"Nenhuma" não pode ser combinada com outras opções.</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>select_one sim_nao_nsabe</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>net_existe</t>
+          <t>q3_10a_outro</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Existe no território?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>selected(${q3_10a}, 'outro')</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
@@ -3806,17 +3810,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>select_one nivel_rel</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>net_nivel</t>
+          <t>q3_10b</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Nível de relação</t>
+          <t>Q3.10b. A gestão tem autonomia para decidir e destinar recursos a ações de Educação Ambiental?</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -3830,17 +3834,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>net_contrib_atual</t>
+          <t>net_actors</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Contribuições atuais</t>
+          <t>Atores do território (NET_ACTORS)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -3854,26 +3858,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>net_contrib_atual_outro</t>
+          <t>net_nota</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Existência, contato, parceria e articulação permanente são níveis diferentes — não confunda um com o outro. Só marque "Parceria" ou "Articulação permanente" se o local já colabora de fato com esse ator; se ele apenas existe no território ou já houve um contato pontual, isso ainda NÃO é parceria. Use "Adicionar" para registrar um ator por vez.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>selected(${net_contrib_atual}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
@@ -3882,17 +3882,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one cat_ator</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>net_contrib_pot</t>
+          <t>net_cat</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Contribuições potenciais</t>
+          <t>Categoria do ator</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -3911,21 +3911,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>net_contrib_pot_outro</t>
+          <t>net_nome</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Nome do ator (ex.: UBS Vila Nova)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>selected(${net_contrib_pot}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
@@ -3934,17 +3930,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>select_one sim_nao</t>
+          <t>select_one sim_nao_nsabe</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>net_prioridade</t>
+          <t>net_existe</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Prioridade para fortalecimento (NET_PRIORITY_ACTORS) — é um ator prioritário a fortalecer?</t>
+          <t>Existe no território?</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -3958,11 +3954,19 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
+          <t>select_one nivel_rel</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>net_nivel</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Nível de relação</t>
+        </is>
+      </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
@@ -3974,25 +3978,21 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>select_multiple contrib</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>q3_11</t>
+          <t>net_contrib_atual</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Q3.11. O local sabe a quem contatar em uma emergência climática?</t>
+          <t>Contribuições atuais</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
@@ -4007,26 +4007,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>q3_12</t>
+          <t>net_contrib_atual_outro</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Q3.12. Quais são esses contatos?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>${q3_11}='sim'</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+          <t>selected(${net_contrib_atual}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
@@ -4034,25 +4030,21 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>select_multiple contrib</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>q3_13</t>
+          <t>net_contrib_pot</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Q3.13. Existe um procedimento de emergência definido para eventos climáticos?</t>
+          <t>Contribuições potenciais</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
@@ -4062,24 +4054,24 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>q3_14</t>
+          <t>net_contrib_pot_outro</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Q3.14. Esse procedimento está documentado/formalizado?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>${q3_13}='sim'</t>
+          <t>selected(${net_contrib_pot}, 'outro')</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -4090,27 +4082,23 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>q3_15</t>
+          <t>net_prioridade</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Q3.15. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
+          <t>Prioridade para fortalecimento (NET_PRIORITY_ACTORS) — é um ator prioritário a fortalecer?</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
@@ -4118,19 +4106,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>select_multiple canais</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>q3_16</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Q3.16. Canais de comunicação do local com a comunidade</t>
-        </is>
-      </c>
+          <t>end_repeat</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
@@ -4142,26 +4122,26 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>q3_16_outro</t>
+          <t>q3_11</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q3.11. O local sabe a quem contatar em uma emergência climática?</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>selected(${q3_16}, 'outro')</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
@@ -4170,23 +4150,31 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>select_one suficiente</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>q3_17</t>
+          <t>q3_12</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Q3.17. Esses canais seriam suficientes numa emergência?</t>
+          <t>Q3.12. Quais são esses contatos?</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>${q3_11}='sim'</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
@@ -4194,27 +4182,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>q3_18</t>
+          <t>q3_13</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Q3.18. Algum grupo fica de fora desses canais de comunicação?</t>
+          <t>Q3.13. Existe um procedimento de emergência definido para eventos climáticos?</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
@@ -4222,31 +4210,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>q3_19</t>
+          <t>q3_14</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Q3.19. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
-        </is>
-      </c>
+          <t>Q3.14. Esse procedimento está documentado/formalizado?</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>${q3_13}='sim'</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
@@ -4259,12 +4243,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>q3_20</t>
+          <t>q3_15</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Q3.20. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
+          <t>Q3.15. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4282,17 +4266,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>select_multiple barr_artic</t>
+          <t>select_multiple canais</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>q3_21</t>
+          <t>q3_16</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Q3.21. Barreiras para articular com atores do território</t>
+          <t>Q3.16. Canais de comunicação do local com a comunidade</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -4311,7 +4295,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>q3_21_outro</t>
+          <t>q3_16_outro</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4323,7 +4307,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>selected(${q3_21}, 'outro')</t>
+          <t>selected(${q3_16}, 'outro')</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -4334,27 +4318,23 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one suficiente</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>q3_22</t>
+          <t>q3_17</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Q3.22. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
+          <t>Q3.17. Esses canais seriam suficientes numa emergência?</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
@@ -4367,21 +4347,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>q3_23</t>
+          <t>q3_18</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Q3.23. Quem participou desse caso?</t>
+          <t>Q3.18. Algum grupo fica de fora desses canais de comunicação?</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>${q3_22} != ''</t>
-        </is>
-      </c>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
           <t>multiline</t>
@@ -4399,21 +4375,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>q3_24</t>
+          <t>q3_19</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Q3.24. O que funcionou bem?</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Q3.19. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>${q3_22} != ''</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
           <t>multiline</t>
@@ -4431,21 +4407,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>q3_25</t>
+          <t>q3_20</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Q3.25. Quais foram as dificuldades?</t>
+          <t>Q3.20. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>${q3_22} != ''</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
           <t>multiline</t>
@@ -4458,31 +4430,23 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple barr_artic</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>q3_26</t>
+          <t>q3_21</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Q3.26. O que essa experiência ensinou?</t>
+          <t>Q3.21. Barreiras para articular com atores do território</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>${q3_22} != ''</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
@@ -4495,22 +4459,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>q3_27</t>
+          <t>q3_21_outro</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Q3.27. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>selected(${q3_21}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
@@ -4523,21 +4487,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>q3_28</t>
+          <t>q3_22</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Q3.28. Por quê?</t>
+          <t>Q3.22. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>${q3_27} != ''</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
           <t>multiline</t>
@@ -4550,23 +4510,31 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>evid_e3</t>
+          <t>q3_23</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Evidências — Evidências sobre participação e redes</t>
+          <t>Q3.23. Quem participou desse caso?</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>${q3_22} != ''</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
@@ -4574,23 +4542,31 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>evid_e3_nota</t>
+          <t>q3_24</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
+          <t>Q3.24. O que funcionou bem?</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>${q3_22} != ''</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
@@ -4598,23 +4574,31 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>select_one tipo_evid</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>evid_e3_tipo</t>
+          <t>q3_25</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Tipo de evidência</t>
+          <t>Q3.25. Quais foram as dificuldades?</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>${q3_22} != ''</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
@@ -4627,22 +4611,26 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>evid_e3_tipo_outro</t>
+          <t>q3_26</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q3.26. O que essa experiência ensinou?</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>${evid_e3_tipo}='outro'</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr"/>
+          <t>${q3_22} != ''</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
@@ -4655,12 +4643,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>evid_e3_desc</t>
+          <t>q3_27</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Descreva a evidência</t>
+          <t>Q3.27. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4678,23 +4666,31 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>evid_e3_anexo</t>
+          <t>q3_28</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Anexo (foto/documento) — opcional</t>
+          <t>Q3.28. Por quê?</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>${q3_27} != ''</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
@@ -4702,11 +4698,19 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr"/>
-      <c r="C163" t="inlineStr"/>
+          <t>begin_repeat</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>evid_e3</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Evidências — Evidências sobre participação e redes</t>
+        </is>
+      </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
@@ -4718,11 +4722,19 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
-      <c r="C164" t="inlineStr"/>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>evid_e3_nota</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
+        </is>
+      </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
@@ -4730,6 +4742,158 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>select_one tipo_evid</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>evid_e3_tipo</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Tipo de evidência</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>evid_e3_tipo_outro</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>${evid_e3_tipo}='outro'</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>evid_e3_desc</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Descreva a evidência</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>evid_e3_anexo</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Anexo (foto/documento) — opcional</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>end_repeat</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4742,7 +4906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C279"/>
+  <dimension ref="A1:C281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4765,34 +4929,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sim_nao_ns</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Sim, concordo em participar</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sim_nao_ns</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>nao_concordo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Não concordo</t>
         </is>
       </c>
     </row>
@@ -4804,46 +4968,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nao_sabemos</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Não sabemos</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sim_nao_nsabe</t>
+          <t>sim_nao_ns</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sim_nao_nsabe</t>
+          <t>sim_nao_ns</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>nao_sabemos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Não sabemos</t>
         </is>
       </c>
     </row>
@@ -4855,80 +5019,80 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sim_nao</t>
+          <t>sim_nao_nsabe</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sim_nao</t>
+          <t>sim_nao_nsabe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tipo_evid</t>
+          <t>sim_nao</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>observacao_direta</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Observação direta</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tipo_evid</t>
+          <t>sim_nao</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>documento</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -4940,12 +5104,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>foto</t>
+          <t>observacao_direta</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Foto</t>
+          <t>Observação direta</t>
         </is>
       </c>
     </row>
@@ -4957,12 +5121,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>depoimento</t>
+          <t>documento</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Depoimento</t>
+          <t>Documento</t>
         </is>
       </c>
     </row>
@@ -4974,12 +5138,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>registro_historico</t>
+          <t>foto</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Registro histórico</t>
+          <t>Foto</t>
         </is>
       </c>
     </row>
@@ -4991,46 +5155,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>depoimento</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Depoimento</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>onde_ea</t>
+          <t>tipo_evid</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>aulas_regulares</t>
+          <t>registro_historico</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aulas regulares</t>
+          <t>Registro histórico</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>onde_ea</t>
+          <t>tipo_evid</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>projetos_interdisciplinares</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Projetos interdisciplinares</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5206,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>feiras_mostras</t>
+          <t>aulas_regulares</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Feiras/mostras</t>
+          <t>Aulas regulares</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5223,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>momentos_civicos</t>
+          <t>projetos_interdisciplinares</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Momentos cívicos</t>
+          <t>Projetos interdisciplinares</t>
         </is>
       </c>
     </row>
@@ -5076,12 +5240,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>em_datas_comemorativas</t>
+          <t>feiras_mostras</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Em datas comemorativas</t>
+          <t>Feiras/mostras</t>
         </is>
       </c>
     </row>
@@ -5093,12 +5257,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>clube_gremio_estudantil</t>
+          <t>momentos_civicos</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Clube/grêmio estudantil</t>
+          <t>Momentos cívicos</t>
         </is>
       </c>
     </row>
@@ -5110,12 +5274,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>iniciativas_de_estudantes</t>
+          <t>em_datas_comemorativas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iniciativas de estudantes</t>
+          <t>Em datas comemorativas</t>
         </is>
       </c>
     </row>
@@ -5127,12 +5291,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>parcerias_externas</t>
+          <t>clube_gremio_estudantil</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Parcerias externas</t>
+          <t>Clube/grêmio estudantil</t>
         </is>
       </c>
     </row>
@@ -5144,46 +5308,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>iniciativas_de_estudantes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Iniciativas de estudantes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>instit_ea</t>
+          <t>onde_ea</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>parcerias_externas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Parcerias externas</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>instit_ea</t>
+          <t>onde_ea</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>isolada_ocasional</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Isolada/ocasional</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5359,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>recorrente_dependente_de_algumas</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Recorrente, dependente de algumas pessoas</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
@@ -5212,12 +5376,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>presente_em_diferentes_component</t>
+          <t>isolada_ocasional</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Presente em diferentes componentes/projetos</t>
+          <t>Isolada/ocasional</t>
         </is>
       </c>
     </row>
@@ -5229,12 +5393,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>integrada_ao_planejamento</t>
+          <t>recorrente_dependente_de_algumas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Integrada ao planejamento</t>
+          <t>Recorrente, dependente de algumas pessoas</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5410,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>institucionalizada_e_continua</t>
+          <t>presente_em_diferentes_component</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Institucionalizada e contínua</t>
+          <t>Presente em diferentes componentes/projetos</t>
         </is>
       </c>
     </row>
@@ -5263,46 +5427,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>integrada_ao_planejamento</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Integrada ao planejamento</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ppp_sit</t>
+          <t>instit_ea</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>presente_e_detalhada</t>
+          <t>institucionalizada_e_continua</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Presente e detalhada</t>
+          <t>Institucionalizada e contínua</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ppp_sit</t>
+          <t>instit_ea</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>presente_de_forma_generica</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Presente de forma genérica</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5314,12 +5478,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ausente</t>
+          <t>presente_e_detalhada</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Presente e detalhada</t>
         </is>
       </c>
     </row>
@@ -5331,46 +5495,46 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>presente_de_forma_generica</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Presente de forma genérica</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ppp_pratica</t>
+          <t>ppp_sit</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>totalmente</t>
+          <t>ausente</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Totalmente</t>
+          <t>Ausente</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ppp_pratica</t>
+          <t>ppp_sit</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5382,12 +5546,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>pouco</t>
+          <t>totalmente</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pouco</t>
+          <t>Totalmente</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5563,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
@@ -5416,46 +5580,46 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>pouco</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Pouco</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>areas_curr</t>
+          <t>ppp_pratica</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ciencias</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ciências</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>areas_curr</t>
+          <t>ppp_pratica</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>geografia</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Geografia</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5467,12 +5631,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>historia</t>
+          <t>ciencias</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>História</t>
+          <t>Ciências</t>
         </is>
       </c>
     </row>
@@ -5484,12 +5648,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>lingua_portuguesa</t>
+          <t>geografia</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Língua Portuguesa</t>
+          <t>Geografia</t>
         </is>
       </c>
     </row>
@@ -5501,12 +5665,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>matematica</t>
+          <t>historia</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Matemática</t>
+          <t>História</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5682,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>artes</t>
+          <t>lingua_portuguesa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Língua Portuguesa</t>
         </is>
       </c>
     </row>
@@ -5535,12 +5699,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>educacao_fisica</t>
+          <t>matematica</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Educação Física</t>
+          <t>Matemática</t>
         </is>
       </c>
     </row>
@@ -5552,46 +5716,46 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>artes</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Artes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>areas_curr</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>disciplinas_separadas</t>
+          <t>educacao_fisica</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Disciplinas separadas</t>
+          <t>Educação Física</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>areas_curr</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>mesmo_tema_sem_planejamento_conj</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mesmo tema, sem planejamento conjunto</t>
+          <t>Outras</t>
         </is>
       </c>
     </row>
@@ -5603,12 +5767,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>algum_planejamento_conjunto</t>
+          <t>disciplinas_separadas</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algum planejamento conjunto</t>
+          <t>Disciplinas separadas</t>
         </is>
       </c>
     </row>
@@ -5620,12 +5784,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>investigacao_conjunta</t>
+          <t>mesmo_tema_sem_planejamento_conj</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Investigação conjunta</t>
+          <t>Mesmo tema, sem planejamento conjunto</t>
         </is>
       </c>
     </row>
@@ -5637,12 +5801,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>objetivos_comuns</t>
+          <t>algum_planejamento_conjunto</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Objetivos comuns</t>
+          <t>Algum planejamento conjunto</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5818,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>intervencao_territorial_coletiva</t>
+          <t>investigacao_conjunta</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Intervenção territorial coletiva</t>
+          <t>Investigação conjunta</t>
         </is>
       </c>
     </row>
@@ -5671,12 +5835,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>sem_articulacao</t>
+          <t>objetivos_comuns</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sem articulação</t>
+          <t>Objetivos comuns</t>
         </is>
       </c>
     </row>
@@ -5688,46 +5852,46 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>intervencao_territorial_coletiva</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Intervenção territorial coletiva</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>freq_ea</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>diaria</t>
+          <t>sem_articulacao</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Diária</t>
+          <t>Sem articulação</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>freq_ea</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Semanal</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5903,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>diaria</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Diária</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5920,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>esporadica</t>
+          <t>semanal</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Esporádica</t>
+          <t>Semanal</t>
         </is>
       </c>
     </row>
@@ -5773,12 +5937,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>anual</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Anual</t>
+          <t>Mensal</t>
         </is>
       </c>
     </row>
@@ -5790,12 +5954,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nao_ocorre</t>
+          <t>esporadica</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Não ocorre</t>
+          <t>Esporádica</t>
         </is>
       </c>
     </row>
@@ -5807,46 +5971,46 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>anual</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Anual</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>contexto_ea</t>
+          <t>freq_ea</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>sala_de_aula</t>
+          <t>nao_ocorre</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sala de aula</t>
+          <t>Não ocorre</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>contexto_ea</t>
+          <t>freq_ea</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>patio_area_externa</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pátio/área externa</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5858,12 +6022,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>visita_de_campo</t>
+          <t>sala_de_aula</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Visita de campo</t>
+          <t>Sala de aula</t>
         </is>
       </c>
     </row>
@@ -5875,12 +6039,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>projeto_especial</t>
+          <t>patio_area_externa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Projeto especial</t>
+          <t>Pátio/área externa</t>
         </is>
       </c>
     </row>
@@ -5892,12 +6056,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>feira</t>
+          <t>visita_de_campo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Feira</t>
+          <t>Visita de campo</t>
         </is>
       </c>
     </row>
@@ -5909,46 +6073,46 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>projeto_especial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Projeto especial</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>professor_individualmente</t>
+          <t>feira</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Professor(a) individualmente</t>
+          <t>Feira</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>grupo_de_professores</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Grupo de professores(as)</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -5960,12 +6124,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>coordenacao_pedagogica</t>
+          <t>professor_individualmente</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Coordenação pedagógica</t>
+          <t>Professor(a) individualmente</t>
         </is>
       </c>
     </row>
@@ -5977,12 +6141,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>grupo_de_professores</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Grupo de professores(as)</t>
         </is>
       </c>
     </row>
@@ -5994,12 +6158,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>coordenacao_pedagogica</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Coordenação pedagógica</t>
         </is>
       </c>
     </row>
@@ -6011,46 +6175,46 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>espectador</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Espectador</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>participante_pontual</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Participante pontual</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6226,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>espectador</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Protagonista</t>
+          <t>Espectador</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6243,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>coprodutor</t>
+          <t>participante_pontual</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Coprodutor</t>
+          <t>Participante pontual</t>
         </is>
       </c>
     </row>
@@ -6096,46 +6260,46 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonista</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>continuidade_ativ</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>depende_da_permanencia_de_profes</t>
+          <t>coprodutor</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Depende da permanência de professor(a) específico(a)</t>
+          <t>Coprodutor</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>continuidade_ativ</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tem continuidade institucional garantida</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6147,12 +6311,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>depende_da_permanencia_de_profes</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Depende da permanência de professor(a) específico(a)</t>
         </is>
       </c>
     </row>
@@ -6164,46 +6328,46 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Tem continuidade institucional garantida</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>continuidade_ativ</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nunca</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Nunca</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>continuidade_ativ</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>raramente</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Raramente</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6215,12 +6379,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>as_vezes</t>
+          <t>nunca</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Às vezes</t>
+          <t>Nunca</t>
         </is>
       </c>
     </row>
@@ -6232,12 +6396,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>frequentemente</t>
+          <t>raramente</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Frequentemente</t>
+          <t>Raramente</t>
         </is>
       </c>
     </row>
@@ -6249,46 +6413,46 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>as_vezes</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Às vezes</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>agua</t>
+          <t>frequentemente</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Frequentemente</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>biodiversidade</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Biodiversidade</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6464,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>residuos</t>
+          <t>agua</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Resíduos</t>
+          <t>Água</t>
         </is>
       </c>
     </row>
@@ -6317,12 +6481,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>mudancas_climaticas</t>
+          <t>biodiversidade</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mudanças climáticas</t>
+          <t>Biodiversidade</t>
         </is>
       </c>
     </row>
@@ -6334,12 +6498,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>residuos</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Resíduos</t>
         </is>
       </c>
     </row>
@@ -6351,12 +6515,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>alimentacao</t>
+          <t>mudancas_climaticas</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Mudanças climáticas</t>
         </is>
       </c>
     </row>
@@ -6368,12 +6532,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>consumo</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Energia</t>
         </is>
       </c>
     </row>
@@ -6385,12 +6549,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>saneamento</t>
+          <t>alimentacao</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Saneamento</t>
+          <t>Alimentação</t>
         </is>
       </c>
     </row>
@@ -6402,12 +6566,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>saude</t>
+          <t>consumo</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>Consumo</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6583,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>riscos_desastres</t>
+          <t>saneamento</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Riscos/desastres</t>
+          <t>Saneamento</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6600,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>justica_socioambiental</t>
+          <t>saude</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Justiça socioambiental</t>
+          <t>Saúde</t>
         </is>
       </c>
     </row>
@@ -6453,12 +6617,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>territorio</t>
+          <t>riscos_desastres</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Território</t>
+          <t>Riscos/desastres</t>
         </is>
       </c>
     </row>
@@ -6470,12 +6634,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>conflitos</t>
+          <t>justica_socioambiental</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Conflitos</t>
+          <t>Justiça socioambiental</t>
         </is>
       </c>
     </row>
@@ -6487,12 +6651,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>povos_e_comunidades_tradicionais</t>
+          <t>territorio</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Povos e comunidades tradicionais</t>
+          <t>Território</t>
         </is>
       </c>
     </row>
@@ -6504,46 +6668,46 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>conflitos</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Conflitos</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>falta_de_formacao</t>
+          <t>povos_e_comunidades_tradicionais</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Falta de formação</t>
+          <t>Povos e comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>falta_de_material</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Falta de material</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
@@ -6555,12 +6719,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>tema_sensivel_delicado</t>
+          <t>falta_de_formacao</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tema sensível/delicado</t>
+          <t>Falta de formação</t>
         </is>
       </c>
     </row>
@@ -6572,12 +6736,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>falta_de_material</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Falta de material</t>
         </is>
       </c>
     </row>
@@ -6589,12 +6753,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>curriculo</t>
+          <t>tema_sensivel_delicado</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Currículo</t>
+          <t>Tema sensível/delicado</t>
         </is>
       </c>
     </row>
@@ -6606,46 +6770,46 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>aula_expositiva</t>
+          <t>curriculo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Aula expositiva</t>
+          <t>Currículo</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>projeto</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6821,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>oficina</t>
+          <t>aula_expositiva</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Oficina</t>
+          <t>Aula expositiva</t>
         </is>
       </c>
     </row>
@@ -6674,12 +6838,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>saida_de_campo</t>
+          <t>projeto</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Saída de campo</t>
+          <t>Projeto</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6855,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>horta_experimentacao</t>
+          <t>oficina</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Horta/experimentação</t>
+          <t>Oficina</t>
         </is>
       </c>
     </row>
@@ -6708,12 +6872,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>rodas_de_conversa</t>
+          <t>saida_de_campo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Rodas de conversa</t>
+          <t>Saída de campo</t>
         </is>
       </c>
     </row>
@@ -6725,12 +6889,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>producao_audiovisual</t>
+          <t>horta_experimentacao</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Produção audiovisual</t>
+          <t>Horta/experimentação</t>
         </is>
       </c>
     </row>
@@ -6742,12 +6906,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>cartografia</t>
+          <t>rodas_de_conversa</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cartografia</t>
+          <t>Rodas de conversa</t>
         </is>
       </c>
     </row>
@@ -6759,46 +6923,46 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>producao_audiovisual</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Produção audiovisual</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>cartografia</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Cartografia</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>pouco</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pouco</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -6810,12 +6974,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
@@ -6827,12 +6991,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>significativo</t>
+          <t>pouco</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Significativo</t>
+          <t>Pouco</t>
         </is>
       </c>
     </row>
@@ -6844,46 +7008,46 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>significativo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>1 — Nada confiante(a)</t>
+          <t>Significativo</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2 — Pouco confiante</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6895,12 +7059,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>3 — Moderadamente confiante</t>
+          <t>1 — Nada confiante(a)</t>
         </is>
       </c>
     </row>
@@ -6912,12 +7076,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>4 — Confiante</t>
+          <t>2 — Pouco confiante</t>
         </is>
       </c>
     </row>
@@ -6929,46 +7093,46 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>5 — Muito confiante</t>
+          <t>3 — Moderadamente confiante</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>4 — Confiante</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>material_didatico</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Material didático</t>
+          <t>5 — Muito confiante</t>
         </is>
       </c>
     </row>
@@ -6980,12 +7144,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>tempo_de_planejamento</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tempo de planejamento</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -6997,12 +7161,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>material_didatico</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Material didático</t>
         </is>
       </c>
     </row>
@@ -7014,12 +7178,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>parcerias</t>
+          <t>tempo_de_planejamento</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Parcerias</t>
+          <t>Tempo de planejamento</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7195,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
@@ -7048,46 +7212,46 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>parcerias</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Parcerias</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>curriculo_sobrecarregado</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Currículo sobrecarregado</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -7099,12 +7263,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -7116,12 +7280,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>curriculo_sobrecarregado</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Materiais</t>
+          <t>Currículo sobrecarregado</t>
         </is>
       </c>
     </row>
@@ -7133,12 +7297,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -7150,12 +7314,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Materiais</t>
         </is>
       </c>
     </row>
@@ -7167,12 +7331,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>planejamento_coletivo</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Planejamento coletivo</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -7184,12 +7348,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>interdisciplinaridade</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Interdisciplinaridade</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
@@ -7201,12 +7365,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>informacoes_territoriais</t>
+          <t>planejamento_coletivo</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Informações territoriais</t>
+          <t>Planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7382,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>descontinuidade</t>
+          <t>interdisciplinaridade</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Descontinuidade</t>
+          <t>Interdisciplinaridade</t>
         </is>
       </c>
     </row>
@@ -7235,12 +7399,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>rotatividade_de_profissionais</t>
+          <t>informacoes_territoriais</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Rotatividade de profissionais</t>
+          <t>Informações territoriais</t>
         </is>
       </c>
     </row>
@@ -7252,46 +7416,46 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>descontinuidade</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Descontinuidade</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>rotatividade_de_profissionais</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Rotatividade de profissionais</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Outras</t>
         </is>
       </c>
     </row>
@@ -7303,12 +7467,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
@@ -7320,46 +7484,46 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>reserva_tempo_para_planejamento_</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Reserva tempo para planejamento coletivo</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>inclui_a_ea_no_ppp_planejamento_</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Inclui a EA no PPP/planejamento anual</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -7371,12 +7535,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>viabiliza_recursos_e_materiais</t>
+          <t>reserva_tempo_para_planejamento_</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Viabiliza recursos e materiais</t>
+          <t>Reserva tempo para planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -7388,12 +7552,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>articula_parcerias_externas</t>
+          <t>inclui_a_ea_no_ppp_planejamento_</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Articula parcerias externas</t>
+          <t>Inclui a EA no PPP/planejamento anual</t>
         </is>
       </c>
     </row>
@@ -7405,12 +7569,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>apoia_projetos_de_estudantes</t>
+          <t>viabiliza_recursos_e_materiais</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Apoia projetos de estudantes</t>
+          <t>Viabiliza recursos e materiais</t>
         </is>
       </c>
     </row>
@@ -7422,12 +7586,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>participa_de_formacoes_sobre_o_t</t>
+          <t>articula_parcerias_externas</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Participa de formações sobre o tema</t>
+          <t>Articula parcerias externas</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7603,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>acompanha_e_valoriza_as_praticas</t>
+          <t>apoia_projetos_de_estudantes</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Acompanha e valoriza as práticas da equipe</t>
+          <t>Apoia projetos de estudantes</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7620,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>participa_de_formacoes_sobre_o_t</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Nenhum apoio sistemático</t>
+          <t>Participa de formações sobre o tema</t>
         </is>
       </c>
     </row>
@@ -7473,46 +7637,46 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>acompanha_e_valoriza_as_praticas</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Acompanha e valoriza as práticas da equipe</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>conselho_escolar</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Conselho escolar</t>
+          <t>Nenhum apoio sistemático</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>apm_caixa_escolar</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>APM / caixa escolar</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -7524,12 +7688,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>conselho_escolar</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>Conselho escolar</t>
         </is>
       </c>
     </row>
@@ -7541,12 +7705,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>conselho_de_classe</t>
+          <t>apm_caixa_escolar</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Conselho de classe</t>
+          <t>APM / caixa escolar</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7722,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>reuniao_pedagogica_planejamento_</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Reunião pedagógica/planejamento coletivo</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
@@ -7575,12 +7739,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>associacao_de_pais_e_mestres</t>
+          <t>conselho_de_classe</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Associação de pais e mestres</t>
+          <t>Conselho de classe</t>
         </is>
       </c>
     </row>
@@ -7592,12 +7756,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>reuniao_pedagogica_planejamento_</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Reunião pedagógica/planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -7609,46 +7773,46 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>associacao_de_pais_e_mestres</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Associação de pais e mestres</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>livros_didaticos</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Livros didáticos</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Vídeos</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -7660,12 +7824,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>jogos</t>
+          <t>livros_didaticos</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Jogos</t>
+          <t>Livros didáticos</t>
         </is>
       </c>
     </row>
@@ -7677,12 +7841,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>kits_cientificos</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Kits científicos</t>
+          <t>Vídeos</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7858,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>materiais_produzidos_pela_escola</t>
+          <t>jogos</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Materiais produzidos pelo local</t>
+          <t>Jogos</t>
         </is>
       </c>
     </row>
@@ -7711,12 +7875,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>recursos_digitais</t>
+          <t>kits_cientificos</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Recursos digitais</t>
+          <t>Kits científicos</t>
         </is>
       </c>
     </row>
@@ -7728,46 +7892,46 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>materiais_produzidos_pela_escola</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Materiais produzidos pelo local</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>recursos_digitais</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Recursos digitais</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -7779,12 +7943,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>dificil</t>
+          <t>facil</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Fácil</t>
         </is>
       </c>
     </row>
@@ -7796,12 +7960,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
@@ -7813,46 +7977,46 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>dificil</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Difícil</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>espectadores</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Espectadores</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>colaboradores_pontuais</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Colaboradores pontuais</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7864,12 +8028,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>protagonistas_em_alguns_momentos</t>
+          <t>espectadores</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Protagonistas em alguns momentos</t>
+          <t>Espectadores</t>
         </is>
       </c>
     </row>
@@ -7881,12 +8045,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>protagonistas_continuos</t>
+          <t>colaboradores_pontuais</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Protagonistas contínuos</t>
+          <t>Colaboradores pontuais</t>
         </is>
       </c>
     </row>
@@ -7898,46 +8062,46 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonistas_em_alguns_momentos</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonistas em alguns momentos</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>garantida_institucionalmente</t>
+          <t>protagonistas_continuos</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Garantida institucionalmente</t>
+          <t>Protagonistas contínuos</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>dependente_de_pessoas_especifica</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Dependente de pessoas específicas</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7949,12 +8113,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>garantida_institucionalmente</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Garantida institucionalmente</t>
         </is>
       </c>
     </row>
@@ -7966,46 +8130,46 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>dependente_de_pessoas_especifica</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Dependente de pessoas específicas</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8181,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8198,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>funcionarios</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Funcionários(as)</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -8051,12 +8215,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
@@ -8068,12 +8232,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>funcionarios</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Funcionários(as)</t>
         </is>
       </c>
     </row>
@@ -8085,46 +8249,46 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>informativa</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Informativa (recebem informação)</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>consultiva</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Consultiva (são ouvidos)</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
@@ -8136,12 +8300,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>colaborativa</t>
+          <t>informativa</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Colaborativa (constroem junto)</t>
+          <t>Informativa (recebem informação)</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8317,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>consultiva</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Protagonista (decidem e conduzem)</t>
+          <t>Consultiva (são ouvidos)</t>
         </is>
       </c>
     </row>
@@ -8170,46 +8334,46 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>colaborativa</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Colaborativa (constroem junto)</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>Protagonista (decidem e conduzem)</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>assembleias</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Assembleias</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -8221,12 +8385,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>projetos_protagonizados_por_estu</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Projetos protagonizados por estudantes</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8402,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>conselhos</t>
+          <t>assembleias</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Conselhos</t>
+          <t>Assembleias</t>
         </is>
       </c>
     </row>
@@ -8255,12 +8419,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>projetos_protagonizados_por_estu</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Projetos protagonizados por estudantes</t>
         </is>
       </c>
     </row>
@@ -8272,46 +8436,46 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>conselhos</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Conselhos</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ausente</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>esporadico</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Esporádico</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -8323,12 +8487,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>ausente</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Ausente</t>
         </is>
       </c>
     </row>
@@ -8340,12 +8504,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ativo_protagonista</t>
+          <t>esporadico</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Ativo/protagonista</t>
+          <t>Esporádico</t>
         </is>
       </c>
     </row>
@@ -8357,46 +8521,46 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>horario_de_trabalho</t>
+          <t>ativo_protagonista</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Horário de trabalho</t>
+          <t>Ativo/protagonista</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>distancia</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Distância</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8572,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>comunicacao_inadequada</t>
+          <t>horario_de_trabalho</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Comunicação inadequada</t>
+          <t>Horário de trabalho</t>
         </is>
       </c>
     </row>
@@ -8425,12 +8589,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>falta_de_convite_convocacao</t>
+          <t>distancia</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Falta de convite/convocação</t>
+          <t>Distância</t>
         </is>
       </c>
     </row>
@@ -8442,46 +8606,46 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunicacao_inadequada</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Comunicação inadequada</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>sec_educacao</t>
+          <t>falta_de_convite_convocacao</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
+          <t>Falta de convite/convocação</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>sec_meio_amb</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -8493,12 +8657,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>defesa_civil</t>
+          <t>sec_educacao</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Secretaria de Educação</t>
         </is>
       </c>
     </row>
@@ -8510,12 +8674,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>sec_saude</t>
+          <t>sec_meio_amb</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
+          <t>Secretaria de Meio Ambiente</t>
         </is>
       </c>
     </row>
@@ -8527,12 +8691,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>assist_social</t>
+          <t>defesa_civil</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
     </row>
@@ -8544,12 +8708,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>obras</t>
+          <t>sec_saude</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
     </row>
@@ -8561,12 +8725,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>bombeiros</t>
+          <t>assist_social</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
+          <t>Assistência Social</t>
         </is>
       </c>
     </row>
@@ -8578,12 +8742,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ubs</t>
+          <t>obras</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Obras</t>
         </is>
       </c>
     </row>
@@ -8595,12 +8759,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>vigilancia</t>
+          <t>bombeiros</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Vigilância</t>
+          <t>Bombeiros</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8776,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>outro_publico</t>
+          <t>ubs</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
+          <t>UBS</t>
         </is>
       </c>
     </row>
@@ -8629,12 +8793,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>universidade</t>
+          <t>vigilancia</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Vigilância</t>
         </is>
       </c>
     </row>
@@ -8646,12 +8810,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>inst_federal</t>
+          <t>outro_publico</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
+          <t>Outro (poder público)</t>
         </is>
       </c>
     </row>
@@ -8663,12 +8827,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>escola_tecnica</t>
+          <t>universidade</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Escola técnica</t>
+          <t>Universidade</t>
         </is>
       </c>
     </row>
@@ -8680,12 +8844,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>centro_pesquisa</t>
+          <t>inst_federal</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>Instituto Federal</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8861,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>museu</t>
+          <t>escola_tecnica</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Museu</t>
+          <t>Escola técnica</t>
         </is>
       </c>
     </row>
@@ -8714,12 +8878,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>jardim_botanico</t>
+          <t>centro_pesquisa</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Centro de pesquisa</t>
         </is>
       </c>
     </row>
@@ -8731,12 +8895,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>outro_educ_ciencia</t>
+          <t>museu</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>Museu</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8912,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>assoc_moradores</t>
+          <t>jardim_botanico</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Jardim botânico</t>
         </is>
       </c>
     </row>
@@ -8765,12 +8929,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>outro_educ_ciencia</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Outro (educação/ciência)</t>
         </is>
       </c>
     </row>
@@ -8782,12 +8946,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>cooperativa</t>
+          <t>assoc_moradores</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -8799,12 +8963,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>catadores</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>ONG</t>
         </is>
       </c>
     </row>
@@ -8816,12 +8980,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>mov_sociais</t>
+          <t>cooperativa</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
+          <t>Cooperativa</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8997,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>coletivos</t>
+          <t>catadores</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Coletivos</t>
+          <t>Catadores</t>
         </is>
       </c>
     </row>
@@ -8850,12 +9014,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>grupos_culturais</t>
+          <t>mov_sociais</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
+          <t>Movimentos sociais</t>
         </is>
       </c>
     </row>
@@ -8867,12 +9031,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>org_comunit_relig</t>
+          <t>coletivos</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Coletivos</t>
         </is>
       </c>
     </row>
@@ -8884,12 +9048,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>outro_soc_civil</t>
+          <t>grupos_culturais</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
+          <t>Grupos culturais</t>
         </is>
       </c>
     </row>
@@ -8901,12 +9065,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>povos_indigenas</t>
+          <t>org_comunit_relig</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
+          <t>Organizações comunitárias/religiosas</t>
         </is>
       </c>
     </row>
@@ -8918,12 +9082,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>quilombolas</t>
+          <t>outro_soc_civil</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Quilombolas</t>
+          <t>Outro (sociedade civil)</t>
         </is>
       </c>
     </row>
@@ -8935,12 +9099,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>agric_familiares</t>
+          <t>povos_indigenas</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Agricultores familiares</t>
+          <t>Povos indígenas</t>
         </is>
       </c>
     </row>
@@ -8952,12 +9116,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>pescadores</t>
+          <t>quilombolas</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Pescadores</t>
+          <t>Quilombolas</t>
         </is>
       </c>
     </row>
@@ -8969,12 +9133,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>com_tradicionais</t>
+          <t>agric_familiares</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
+          <t>Agricultores familiares</t>
         </is>
       </c>
     </row>
@@ -8986,12 +9150,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>liderancas</t>
+          <t>pescadores</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Pescadores</t>
         </is>
       </c>
     </row>
@@ -9003,12 +9167,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>detentores_saberes</t>
+          <t>com_tradicionais</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Detentores de conhecimentos locais</t>
+          <t>Comunidades tradicionais</t>
         </is>
       </c>
     </row>
@@ -9020,46 +9184,46 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>outro_comunidades</t>
+          <t>liderancas</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Outro (comunidades e conhecimentos)</t>
+          <t>Lideranças</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>nivel_rel</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>nao_existe</t>
+          <t>detentores_saberes</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Não existe relação — não é parceiro(a)</t>
+          <t>Detentores de conhecimentos locais</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>nivel_rel</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>sabe_existe</t>
+          <t>outro_comunidades</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Sabe que existe, mas nunca houve contato — não é parceiro(a)</t>
+          <t>Outro (comunidades e conhecimentos)</t>
         </is>
       </c>
     </row>
@@ -9071,12 +9235,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>contato_pontual</t>
+          <t>nao_existe</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Já houve contato pontual, sem combinação formal — ainda não é parceiro(a)</t>
+          <t>Não existe relação — não é parceiro(a)</t>
         </is>
       </c>
     </row>
@@ -9088,12 +9252,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>parceria</t>
+          <t>sabe_existe</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Parceria — já colaboram em ações combinadas</t>
+          <t>Sabe que existe, mas nunca houve contato — não é parceiro(a)</t>
         </is>
       </c>
     </row>
@@ -9105,46 +9269,46 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>contato_pontual</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Articulação permanente — parceria contínua e estruturada</t>
+          <t>Já houve contato pontual, sem combinação formal — ainda não é parceiro(a)</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>nivel_rel</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>recursos</t>
+          <t>parceria</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Recursos</t>
+          <t>Parceria — já colaboram em ações combinadas</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>nivel_rel</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Articulação permanente — parceria contínua e estruturada</t>
         </is>
       </c>
     </row>
@@ -9156,12 +9320,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>articulacao_institucional</t>
+          <t>recursos</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Articulação institucional</t>
+          <t>Recursos</t>
         </is>
       </c>
     </row>
@@ -9173,12 +9337,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>apoio_tecnico</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Apoio técnico</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -9190,12 +9354,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>mobilizacao_comunitaria</t>
+          <t>articulacao_institucional</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Mobilização comunitária</t>
+          <t>Articulação institucional</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9371,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>conhecimentos_tradicionais_locai</t>
+          <t>apoio_tecnico</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Conhecimentos tradicionais/locais</t>
+          <t>Apoio técnico</t>
         </is>
       </c>
     </row>
@@ -9224,46 +9388,46 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>mobilizacao_comunitaria</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Mobilização comunitária</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>contrib</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>conhecimentos_tradicionais_locai</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Conhecimentos tradicionais/locais</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>contrib</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>comunicados_impressos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Comunicados impressos</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9439,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>reunioes</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
@@ -9292,12 +9456,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>comunicados_impressos</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Comunicados impressos</t>
         </is>
       </c>
     </row>
@@ -9309,12 +9473,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>alto_falante_radio_local</t>
+          <t>reunioes</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Alto-falante/rádio local</t>
+          <t>Reuniões</t>
         </is>
       </c>
     </row>
@@ -9326,46 +9490,46 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>alto_falante_radio_local</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Alto-falante/rádio local</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9541,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -9394,46 +9558,46 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>falta_de_contato</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Falta de contato</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>burocracia</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Burocracia</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -9445,12 +9609,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>desconfianca_historico_de_relaca</t>
+          <t>falta_de_contato</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Desconfiança/histórico de relação</t>
+          <t>Falta de contato</t>
         </is>
       </c>
     </row>
@@ -9462,12 +9626,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>burocracia</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Burocracia</t>
         </is>
       </c>
     </row>
@@ -9479,10 +9643,44 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
+          <t>desconfianca_historico_de_relaca</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Desconfiança/histórico de relação</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>barr_artic</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>falta_de_tempo</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Falta de tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>barr_artic</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
           <t>outro</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
+      <c r="C281" t="inlineStr">
         <is>
           <t>Outra</t>
         </is>
@@ -9552,7 +9750,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>pages</t>
+          <t>theme-grid no-text-transform</t>
         </is>
       </c>
     </row>

--- a/kobo/gestores_semana2_diagnostico.xlsx
+++ b/kobo/gestores_semana2_diagnostico.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J171"/>
+  <dimension ref="A1:J175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4882,11 +4882,19 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr"/>
-      <c r="C171" t="inlineStr"/>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>confirmacao</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Confirmação final</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
@@ -4894,6 +4902,90 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>confirmacao_msg</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir.</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>select_one confirmo</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>confirmacao_envio</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Revisei minhas respostas e confirmo o envio.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4906,7 +4998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C281"/>
+  <dimension ref="A1:C282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4929,17 +5021,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>concordo</t>
+          <t>confirmo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>concordo</t>
+          <t>confirmo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sim, concordo em participar</t>
+          <t>Sim, confirmo o envio</t>
         </is>
       </c>
     </row>
@@ -4951,29 +5043,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nao_concordo</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Não concordo</t>
+          <t>Sim, concordo em participar</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sim_nao_ns</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao_concordo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não concordo</t>
         </is>
       </c>
     </row>
@@ -4985,12 +5077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -5002,29 +5094,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nao_sabemos</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Não sabemos</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sim_nao_nsabe</t>
+          <t>sim_nao_ns</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao_sabemos</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não sabemos</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5128,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -5053,29 +5145,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sim_nao</t>
+          <t>sim_nao_nsabe</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5087,29 +5179,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tipo_evid</t>
+          <t>sim_nao</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>observacao_direta</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Observação direta</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -5121,12 +5213,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>documento</t>
+          <t>observacao_direta</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Observação direta</t>
         </is>
       </c>
     </row>
@@ -5138,12 +5230,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>foto</t>
+          <t>documento</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Foto</t>
+          <t>Documento</t>
         </is>
       </c>
     </row>
@@ -5155,12 +5247,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>depoimento</t>
+          <t>foto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Depoimento</t>
+          <t>Foto</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5264,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>registro_historico</t>
+          <t>depoimento</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Registro histórico</t>
+          <t>Depoimento</t>
         </is>
       </c>
     </row>
@@ -5189,29 +5281,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>registro_historico</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Registro histórico</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>onde_ea</t>
+          <t>tipo_evid</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>aulas_regulares</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Aulas regulares</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -5223,12 +5315,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>projetos_interdisciplinares</t>
+          <t>aulas_regulares</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Projetos interdisciplinares</t>
+          <t>Aulas regulares</t>
         </is>
       </c>
     </row>
@@ -5240,12 +5332,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>feiras_mostras</t>
+          <t>projetos_interdisciplinares</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Feiras/mostras</t>
+          <t>Projetos interdisciplinares</t>
         </is>
       </c>
     </row>
@@ -5257,12 +5349,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>momentos_civicos</t>
+          <t>feiras_mostras</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Momentos cívicos</t>
+          <t>Feiras/mostras</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5366,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>em_datas_comemorativas</t>
+          <t>momentos_civicos</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Em datas comemorativas</t>
+          <t>Momentos cívicos</t>
         </is>
       </c>
     </row>
@@ -5291,12 +5383,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>clube_gremio_estudantil</t>
+          <t>em_datas_comemorativas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Clube/grêmio estudantil</t>
+          <t>Em datas comemorativas</t>
         </is>
       </c>
     </row>
@@ -5308,12 +5400,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>iniciativas_de_estudantes</t>
+          <t>clube_gremio_estudantil</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iniciativas de estudantes</t>
+          <t>Clube/grêmio estudantil</t>
         </is>
       </c>
     </row>
@@ -5325,12 +5417,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>parcerias_externas</t>
+          <t>iniciativas_de_estudantes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Parcerias externas</t>
+          <t>Iniciativas de estudantes</t>
         </is>
       </c>
     </row>
@@ -5342,29 +5434,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>parcerias_externas</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Parcerias externas</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>instit_ea</t>
+          <t>onde_ea</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -5376,12 +5468,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>isolada_ocasional</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Isolada/ocasional</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5485,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>recorrente_dependente_de_algumas</t>
+          <t>isolada_ocasional</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Recorrente, dependente de algumas pessoas</t>
+          <t>Isolada/ocasional</t>
         </is>
       </c>
     </row>
@@ -5410,12 +5502,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>presente_em_diferentes_component</t>
+          <t>recorrente_dependente_de_algumas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Presente em diferentes componentes/projetos</t>
+          <t>Recorrente, dependente de algumas pessoas</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5519,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>integrada_ao_planejamento</t>
+          <t>presente_em_diferentes_component</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Integrada ao planejamento</t>
+          <t>Presente em diferentes componentes/projetos</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5536,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>institucionalizada_e_continua</t>
+          <t>integrada_ao_planejamento</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Institucionalizada e contínua</t>
+          <t>Integrada ao planejamento</t>
         </is>
       </c>
     </row>
@@ -5461,29 +5553,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>institucionalizada_e_continua</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Institucionalizada e contínua</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ppp_sit</t>
+          <t>instit_ea</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>presente_e_detalhada</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Presente e detalhada</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5495,12 +5587,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>presente_de_forma_generica</t>
+          <t>presente_e_detalhada</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Presente de forma genérica</t>
+          <t>Presente e detalhada</t>
         </is>
       </c>
     </row>
@@ -5512,12 +5604,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ausente</t>
+          <t>presente_de_forma_generica</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Presente de forma genérica</t>
         </is>
       </c>
     </row>
@@ -5529,29 +5621,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>ausente</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Ausente</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ppp_pratica</t>
+          <t>ppp_sit</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>totalmente</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Totalmente</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5563,12 +5655,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>totalmente</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Totalmente</t>
         </is>
       </c>
     </row>
@@ -5580,12 +5672,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>pouco</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pouco</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
@@ -5597,12 +5689,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>pouco</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pouco</t>
         </is>
       </c>
     </row>
@@ -5614,29 +5706,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>areas_curr</t>
+          <t>ppp_pratica</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ciencias</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ciências</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5648,12 +5740,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>geografia</t>
+          <t>ciencias</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Geografia</t>
+          <t>Ciências</t>
         </is>
       </c>
     </row>
@@ -5665,12 +5757,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>historia</t>
+          <t>geografia</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>História</t>
+          <t>Geografia</t>
         </is>
       </c>
     </row>
@@ -5682,12 +5774,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>lingua_portuguesa</t>
+          <t>historia</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Língua Portuguesa</t>
+          <t>História</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5791,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>matematica</t>
+          <t>lingua_portuguesa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Matemática</t>
+          <t>Língua Portuguesa</t>
         </is>
       </c>
     </row>
@@ -5716,12 +5808,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>artes</t>
+          <t>matematica</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Matemática</t>
         </is>
       </c>
     </row>
@@ -5733,12 +5825,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>educacao_fisica</t>
+          <t>artes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Educação Física</t>
+          <t>Artes</t>
         </is>
       </c>
     </row>
@@ -5750,29 +5842,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>educacao_fisica</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Educação Física</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>areas_curr</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>disciplinas_separadas</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Disciplinas separadas</t>
+          <t>Outras</t>
         </is>
       </c>
     </row>
@@ -5784,12 +5876,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>mesmo_tema_sem_planejamento_conj</t>
+          <t>disciplinas_separadas</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mesmo tema, sem planejamento conjunto</t>
+          <t>Disciplinas separadas</t>
         </is>
       </c>
     </row>
@@ -5801,12 +5893,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>algum_planejamento_conjunto</t>
+          <t>mesmo_tema_sem_planejamento_conj</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algum planejamento conjunto</t>
+          <t>Mesmo tema, sem planejamento conjunto</t>
         </is>
       </c>
     </row>
@@ -5818,12 +5910,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>investigacao_conjunta</t>
+          <t>algum_planejamento_conjunto</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Investigação conjunta</t>
+          <t>Algum planejamento conjunto</t>
         </is>
       </c>
     </row>
@@ -5835,12 +5927,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>objetivos_comuns</t>
+          <t>investigacao_conjunta</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Objetivos comuns</t>
+          <t>Investigação conjunta</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5944,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>intervencao_territorial_coletiva</t>
+          <t>objetivos_comuns</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Intervenção territorial coletiva</t>
+          <t>Objetivos comuns</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5961,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>sem_articulacao</t>
+          <t>intervencao_territorial_coletiva</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sem articulação</t>
+          <t>Intervenção territorial coletiva</t>
         </is>
       </c>
     </row>
@@ -5886,29 +5978,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>sem_articulacao</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Sem articulação</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>freq_ea</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>diaria</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Diária</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5920,12 +6012,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>diaria</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Semanal</t>
+          <t>Diária</t>
         </is>
       </c>
     </row>
@@ -5937,12 +6029,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>semanal</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Semanal</t>
         </is>
       </c>
     </row>
@@ -5954,12 +6046,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>esporadica</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Esporádica</t>
+          <t>Mensal</t>
         </is>
       </c>
     </row>
@@ -5971,12 +6063,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>anual</t>
+          <t>esporadica</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Anual</t>
+          <t>Esporádica</t>
         </is>
       </c>
     </row>
@@ -5988,12 +6080,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nao_ocorre</t>
+          <t>anual</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Não ocorre</t>
+          <t>Anual</t>
         </is>
       </c>
     </row>
@@ -6005,29 +6097,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nao_ocorre</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Não ocorre</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>contexto_ea</t>
+          <t>freq_ea</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>sala_de_aula</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sala de aula</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6039,12 +6131,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>patio_area_externa</t>
+          <t>sala_de_aula</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pátio/área externa</t>
+          <t>Sala de aula</t>
         </is>
       </c>
     </row>
@@ -6056,12 +6148,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>visita_de_campo</t>
+          <t>patio_area_externa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Visita de campo</t>
+          <t>Pátio/área externa</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6165,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>projeto_especial</t>
+          <t>visita_de_campo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Projeto especial</t>
+          <t>Visita de campo</t>
         </is>
       </c>
     </row>
@@ -6090,12 +6182,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>feira</t>
+          <t>projeto_especial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Feira</t>
+          <t>Projeto especial</t>
         </is>
       </c>
     </row>
@@ -6107,29 +6199,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>feira</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Feira</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>professor_individualmente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Professor(a) individualmente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -6141,12 +6233,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>grupo_de_professores</t>
+          <t>professor_individualmente</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Grupo de professores(as)</t>
+          <t>Professor(a) individualmente</t>
         </is>
       </c>
     </row>
@@ -6158,12 +6250,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>coordenacao_pedagogica</t>
+          <t>grupo_de_professores</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Coordenação pedagógica</t>
+          <t>Grupo de professores(as)</t>
         </is>
       </c>
     </row>
@@ -6175,12 +6267,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>coordenacao_pedagogica</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Coordenação pedagógica</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6284,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -6209,29 +6301,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>espectador</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Espectador</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -6243,12 +6335,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>participante_pontual</t>
+          <t>espectador</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Participante pontual</t>
+          <t>Espectador</t>
         </is>
       </c>
     </row>
@@ -6260,12 +6352,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>participante_pontual</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Protagonista</t>
+          <t>Participante pontual</t>
         </is>
       </c>
     </row>
@@ -6277,12 +6369,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>coprodutor</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Coprodutor</t>
+          <t>Protagonista</t>
         </is>
       </c>
     </row>
@@ -6294,29 +6386,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>coprodutor</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Coprodutor</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>continuidade_ativ</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>depende_da_permanencia_de_profes</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Depende da permanência de professor(a) específico(a)</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6328,12 +6420,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>depende_da_permanencia_de_profes</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tem continuidade institucional garantida</t>
+          <t>Depende da permanência de professor(a) específico(a)</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6437,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Tem continuidade institucional garantida</t>
         </is>
       </c>
     </row>
@@ -6362,29 +6454,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>continuidade_ativ</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nunca</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Nunca</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6396,12 +6488,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>raramente</t>
+          <t>nunca</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Raramente</t>
+          <t>Nunca</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6505,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>as_vezes</t>
+          <t>raramente</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Às vezes</t>
+          <t>Raramente</t>
         </is>
       </c>
     </row>
@@ -6430,12 +6522,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>frequentemente</t>
+          <t>as_vezes</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Frequentemente</t>
+          <t>Às vezes</t>
         </is>
       </c>
     </row>
@@ -6447,29 +6539,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>frequentemente</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Frequentemente</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>agua</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6481,12 +6573,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>biodiversidade</t>
+          <t>agua</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Biodiversidade</t>
+          <t>Água</t>
         </is>
       </c>
     </row>
@@ -6498,12 +6590,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>residuos</t>
+          <t>biodiversidade</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Resíduos</t>
+          <t>Biodiversidade</t>
         </is>
       </c>
     </row>
@@ -6515,12 +6607,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>mudancas_climaticas</t>
+          <t>residuos</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mudanças climáticas</t>
+          <t>Resíduos</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6624,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>mudancas_climaticas</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Mudanças climáticas</t>
         </is>
       </c>
     </row>
@@ -6549,12 +6641,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>alimentacao</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Energia</t>
         </is>
       </c>
     </row>
@@ -6566,12 +6658,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>consumo</t>
+          <t>alimentacao</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Alimentação</t>
         </is>
       </c>
     </row>
@@ -6583,12 +6675,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>saneamento</t>
+          <t>consumo</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Saneamento</t>
+          <t>Consumo</t>
         </is>
       </c>
     </row>
@@ -6600,12 +6692,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>saude</t>
+          <t>saneamento</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>Saneamento</t>
         </is>
       </c>
     </row>
@@ -6617,12 +6709,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>riscos_desastres</t>
+          <t>saude</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Riscos/desastres</t>
+          <t>Saúde</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6726,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>justica_socioambiental</t>
+          <t>riscos_desastres</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Justiça socioambiental</t>
+          <t>Riscos/desastres</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6743,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>territorio</t>
+          <t>justica_socioambiental</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Território</t>
+          <t>Justiça socioambiental</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6760,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>conflitos</t>
+          <t>territorio</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Conflitos</t>
+          <t>Território</t>
         </is>
       </c>
     </row>
@@ -6685,12 +6777,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>povos_e_comunidades_tradicionais</t>
+          <t>conflitos</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Povos e comunidades tradicionais</t>
+          <t>Conflitos</t>
         </is>
       </c>
     </row>
@@ -6702,29 +6794,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>povos_e_comunidades_tradicionais</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Povos e comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>falta_de_formacao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Falta de formação</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
@@ -6736,12 +6828,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>falta_de_material</t>
+          <t>falta_de_formacao</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Falta de material</t>
+          <t>Falta de formação</t>
         </is>
       </c>
     </row>
@@ -6753,12 +6845,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>tema_sensivel_delicado</t>
+          <t>falta_de_material</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tema sensível/delicado</t>
+          <t>Falta de material</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6862,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>tema_sensivel_delicado</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Tema sensível/delicado</t>
         </is>
       </c>
     </row>
@@ -6787,12 +6879,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>curriculo</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Currículo</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
@@ -6804,29 +6896,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>curriculo</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Currículo</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>aula_expositiva</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Aula expositiva</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -6838,12 +6930,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>projeto</t>
+          <t>aula_expositiva</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Aula expositiva</t>
         </is>
       </c>
     </row>
@@ -6855,12 +6947,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>oficina</t>
+          <t>projeto</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Oficina</t>
+          <t>Projeto</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6964,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>saida_de_campo</t>
+          <t>oficina</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Saída de campo</t>
+          <t>Oficina</t>
         </is>
       </c>
     </row>
@@ -6889,12 +6981,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>horta_experimentacao</t>
+          <t>saida_de_campo</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Horta/experimentação</t>
+          <t>Saída de campo</t>
         </is>
       </c>
     </row>
@@ -6906,12 +6998,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>rodas_de_conversa</t>
+          <t>horta_experimentacao</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Rodas de conversa</t>
+          <t>Horta/experimentação</t>
         </is>
       </c>
     </row>
@@ -6923,12 +7015,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>producao_audiovisual</t>
+          <t>rodas_de_conversa</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Produção audiovisual</t>
+          <t>Rodas de conversa</t>
         </is>
       </c>
     </row>
@@ -6940,12 +7032,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>cartografia</t>
+          <t>producao_audiovisual</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cartografia</t>
+          <t>Produção audiovisual</t>
         </is>
       </c>
     </row>
@@ -6957,29 +7049,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>cartografia</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Cartografia</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -6991,12 +7083,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>pouco</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Pouco</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7100,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>pouco</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Pouco</t>
         </is>
       </c>
     </row>
@@ -7025,12 +7117,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>significativo</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Significativo</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
@@ -7042,29 +7134,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>significativo</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Significativo</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>1 — Nada confiante(a)</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7076,12 +7168,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2 — Pouco confiante</t>
+          <t>1 — Nada confiante(a)</t>
         </is>
       </c>
     </row>
@@ -7093,12 +7185,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3 — Moderadamente confiante</t>
+          <t>2 — Pouco confiante</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7202,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>4 — Confiante</t>
+          <t>3 — Moderadamente confiante</t>
         </is>
       </c>
     </row>
@@ -7127,29 +7219,29 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>5 — Muito confiante</t>
+          <t>4 — Confiante</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>5 — Muito confiante</t>
         </is>
       </c>
     </row>
@@ -7161,12 +7253,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>material_didatico</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Material didático</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -7178,12 +7270,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>tempo_de_planejamento</t>
+          <t>material_didatico</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tempo de planejamento</t>
+          <t>Material didático</t>
         </is>
       </c>
     </row>
@@ -7195,12 +7287,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>tempo_de_planejamento</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Tempo de planejamento</t>
         </is>
       </c>
     </row>
@@ -7212,12 +7304,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>parcerias</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Parcerias</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7321,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>parcerias</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Parcerias</t>
         </is>
       </c>
     </row>
@@ -7246,29 +7338,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -7280,12 +7372,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>curriculo_sobrecarregado</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Currículo sobrecarregado</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -7297,12 +7389,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>curriculo_sobrecarregado</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Currículo sobrecarregado</t>
         </is>
       </c>
     </row>
@@ -7314,12 +7406,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Materiais</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7423,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Materiais</t>
         </is>
       </c>
     </row>
@@ -7348,12 +7440,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -7365,12 +7457,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>planejamento_coletivo</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Planejamento coletivo</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
@@ -7382,12 +7474,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>interdisciplinaridade</t>
+          <t>planejamento_coletivo</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Interdisciplinaridade</t>
+          <t>Planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -7399,12 +7491,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>informacoes_territoriais</t>
+          <t>interdisciplinaridade</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Informações territoriais</t>
+          <t>Interdisciplinaridade</t>
         </is>
       </c>
     </row>
@@ -7416,12 +7508,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>descontinuidade</t>
+          <t>informacoes_territoriais</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Descontinuidade</t>
+          <t>Informações territoriais</t>
         </is>
       </c>
     </row>
@@ -7433,12 +7525,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>rotatividade_de_profissionais</t>
+          <t>descontinuidade</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Rotatividade de profissionais</t>
+          <t>Descontinuidade</t>
         </is>
       </c>
     </row>
@@ -7450,29 +7542,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>rotatividade_de_profissionais</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Rotatividade de profissionais</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Outras</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7576,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
@@ -7501,12 +7593,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
@@ -7518,29 +7610,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>reserva_tempo_para_planejamento_</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Reserva tempo para planejamento coletivo</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -7552,12 +7644,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>inclui_a_ea_no_ppp_planejamento_</t>
+          <t>reserva_tempo_para_planejamento_</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Inclui a EA no PPP/planejamento anual</t>
+          <t>Reserva tempo para planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7661,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>viabiliza_recursos_e_materiais</t>
+          <t>inclui_a_ea_no_ppp_planejamento_</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Viabiliza recursos e materiais</t>
+          <t>Inclui a EA no PPP/planejamento anual</t>
         </is>
       </c>
     </row>
@@ -7586,12 +7678,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>articula_parcerias_externas</t>
+          <t>viabiliza_recursos_e_materiais</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Articula parcerias externas</t>
+          <t>Viabiliza recursos e materiais</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7695,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>apoia_projetos_de_estudantes</t>
+          <t>articula_parcerias_externas</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Apoia projetos de estudantes</t>
+          <t>Articula parcerias externas</t>
         </is>
       </c>
     </row>
@@ -7620,12 +7712,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>participa_de_formacoes_sobre_o_t</t>
+          <t>apoia_projetos_de_estudantes</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Participa de formações sobre o tema</t>
+          <t>Apoia projetos de estudantes</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7729,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>acompanha_e_valoriza_as_praticas</t>
+          <t>participa_de_formacoes_sobre_o_t</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Acompanha e valoriza as práticas da equipe</t>
+          <t>Participa de formações sobre o tema</t>
         </is>
       </c>
     </row>
@@ -7654,12 +7746,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>acompanha_e_valoriza_as_praticas</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Nenhum apoio sistemático</t>
+          <t>Acompanha e valoriza as práticas da equipe</t>
         </is>
       </c>
     </row>
@@ -7671,29 +7763,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Nenhum apoio sistemático</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>conselho_escolar</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Conselho escolar</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -7705,12 +7797,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>apm_caixa_escolar</t>
+          <t>conselho_escolar</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>APM / caixa escolar</t>
+          <t>Conselho escolar</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7814,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>apm_caixa_escolar</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>APM / caixa escolar</t>
         </is>
       </c>
     </row>
@@ -7739,12 +7831,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>conselho_de_classe</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Conselho de classe</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
@@ -7756,12 +7848,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>reuniao_pedagogica_planejamento_</t>
+          <t>conselho_de_classe</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Reunião pedagógica/planejamento coletivo</t>
+          <t>Conselho de classe</t>
         </is>
       </c>
     </row>
@@ -7773,12 +7865,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>associacao_de_pais_e_mestres</t>
+          <t>reuniao_pedagogica_planejamento_</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Associação de pais e mestres</t>
+          <t>Reunião pedagógica/planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -7790,12 +7882,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>associacao_de_pais_e_mestres</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Associação de pais e mestres</t>
         </is>
       </c>
     </row>
@@ -7807,29 +7899,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>livros_didaticos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Livros didáticos</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -7841,12 +7933,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>livros_didaticos</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Vídeos</t>
+          <t>Livros didáticos</t>
         </is>
       </c>
     </row>
@@ -7858,12 +7950,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>jogos</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Jogos</t>
+          <t>Vídeos</t>
         </is>
       </c>
     </row>
@@ -7875,12 +7967,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>kits_cientificos</t>
+          <t>jogos</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Kits científicos</t>
+          <t>Jogos</t>
         </is>
       </c>
     </row>
@@ -7892,12 +7984,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>materiais_produzidos_pela_escola</t>
+          <t>kits_cientificos</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Materiais produzidos pelo local</t>
+          <t>Kits científicos</t>
         </is>
       </c>
     </row>
@@ -7909,12 +8001,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>recursos_digitais</t>
+          <t>materiais_produzidos_pela_escola</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Recursos digitais</t>
+          <t>Materiais produzidos pelo local</t>
         </is>
       </c>
     </row>
@@ -7926,29 +8018,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>recursos_digitais</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Recursos digitais</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -7960,12 +8052,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>facil</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Fácil</t>
         </is>
       </c>
     </row>
@@ -7977,12 +8069,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>dificil</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
@@ -7994,12 +8086,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>dificil</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Difícil</t>
         </is>
       </c>
     </row>
@@ -8011,29 +8103,29 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>espectadores</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Espectadores</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -8045,12 +8137,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>colaboradores_pontuais</t>
+          <t>espectadores</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Colaboradores pontuais</t>
+          <t>Espectadores</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8154,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>protagonistas_em_alguns_momentos</t>
+          <t>colaboradores_pontuais</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Protagonistas em alguns momentos</t>
+          <t>Colaboradores pontuais</t>
         </is>
       </c>
     </row>
@@ -8079,12 +8171,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>protagonistas_continuos</t>
+          <t>protagonistas_em_alguns_momentos</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Protagonistas contínuos</t>
+          <t>Protagonistas em alguns momentos</t>
         </is>
       </c>
     </row>
@@ -8096,29 +8188,29 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonistas_continuos</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonistas contínuos</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>garantida_institucionalmente</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Garantida institucionalmente</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8222,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>dependente_de_pessoas_especifica</t>
+          <t>garantida_institucionalmente</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Dependente de pessoas específicas</t>
+          <t>Garantida institucionalmente</t>
         </is>
       </c>
     </row>
@@ -8147,12 +8239,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>dependente_de_pessoas_especifica</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Dependente de pessoas específicas</t>
         </is>
       </c>
     </row>
@@ -8164,29 +8256,29 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -8198,12 +8290,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -8215,12 +8307,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -8232,12 +8324,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>funcionarios</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Funcionários(as)</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8341,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>funcionarios</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Funcionários(as)</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8358,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -8283,29 +8375,29 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>informativa</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Informativa (recebem informação)</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8409,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>consultiva</t>
+          <t>informativa</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Consultiva (são ouvidos)</t>
+          <t>Informativa (recebem informação)</t>
         </is>
       </c>
     </row>
@@ -8334,12 +8426,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>colaborativa</t>
+          <t>consultiva</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Colaborativa (constroem junto)</t>
+          <t>Consultiva (são ouvidos)</t>
         </is>
       </c>
     </row>
@@ -8351,12 +8443,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>colaborativa</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Protagonista (decidem e conduzem)</t>
+          <t>Colaborativa (constroem junto)</t>
         </is>
       </c>
     </row>
@@ -8368,29 +8460,29 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonista (decidem e conduzem)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -8402,12 +8494,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>assembleias</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Assembleias</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
@@ -8419,12 +8511,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>projetos_protagonizados_por_estu</t>
+          <t>assembleias</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Projetos protagonizados por estudantes</t>
+          <t>Assembleias</t>
         </is>
       </c>
     </row>
@@ -8436,12 +8528,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>conselhos</t>
+          <t>projetos_protagonizados_por_estu</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Conselhos</t>
+          <t>Projetos protagonizados por estudantes</t>
         </is>
       </c>
     </row>
@@ -8453,12 +8545,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>conselhos</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Conselhos</t>
         </is>
       </c>
     </row>
@@ -8470,29 +8562,29 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ausente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -8504,12 +8596,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>esporadico</t>
+          <t>ausente</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Esporádico</t>
+          <t>Ausente</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8613,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>esporadico</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Esporádico</t>
         </is>
       </c>
     </row>
@@ -8538,12 +8630,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ativo_protagonista</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Ativo/protagonista</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
@@ -8555,29 +8647,29 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>ativo_protagonista</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Ativo/protagonista</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>horario_de_trabalho</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Horário de trabalho</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8681,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>distancia</t>
+          <t>horario_de_trabalho</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Distância</t>
+          <t>Horário de trabalho</t>
         </is>
       </c>
     </row>
@@ -8606,12 +8698,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>comunicacao_inadequada</t>
+          <t>distancia</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Comunicação inadequada</t>
+          <t>Distância</t>
         </is>
       </c>
     </row>
@@ -8623,12 +8715,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>falta_de_convite_convocacao</t>
+          <t>comunicacao_inadequada</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Falta de convite/convocação</t>
+          <t>Comunicação inadequada</t>
         </is>
       </c>
     </row>
@@ -8640,29 +8732,29 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>falta_de_convite_convocacao</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Falta de convite/convocação</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>sec_educacao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -8674,12 +8766,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>sec_meio_amb</t>
+          <t>sec_educacao</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
+          <t>Secretaria de Educação</t>
         </is>
       </c>
     </row>
@@ -8691,12 +8783,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>defesa_civil</t>
+          <t>sec_meio_amb</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Secretaria de Meio Ambiente</t>
         </is>
       </c>
     </row>
@@ -8708,12 +8800,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>sec_saude</t>
+          <t>defesa_civil</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8817,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>assist_social</t>
+          <t>sec_saude</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
     </row>
@@ -8742,12 +8834,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>obras</t>
+          <t>assist_social</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>Assistência Social</t>
         </is>
       </c>
     </row>
@@ -8759,12 +8851,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>bombeiros</t>
+          <t>obras</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
+          <t>Obras</t>
         </is>
       </c>
     </row>
@@ -8776,12 +8868,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ubs</t>
+          <t>bombeiros</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Bombeiros</t>
         </is>
       </c>
     </row>
@@ -8793,12 +8885,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>vigilancia</t>
+          <t>ubs</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Vigilância</t>
+          <t>UBS</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8902,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>outro_publico</t>
+          <t>vigilancia</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
+          <t>Vigilância</t>
         </is>
       </c>
     </row>
@@ -8827,12 +8919,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>universidade</t>
+          <t>outro_publico</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Outro (poder público)</t>
         </is>
       </c>
     </row>
@@ -8844,12 +8936,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>inst_federal</t>
+          <t>universidade</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
+          <t>Universidade</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8953,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>escola_tecnica</t>
+          <t>inst_federal</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Escola técnica</t>
+          <t>Instituto Federal</t>
         </is>
       </c>
     </row>
@@ -8878,12 +8970,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>centro_pesquisa</t>
+          <t>escola_tecnica</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>Escola técnica</t>
         </is>
       </c>
     </row>
@@ -8895,12 +8987,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>museu</t>
+          <t>centro_pesquisa</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Museu</t>
+          <t>Centro de pesquisa</t>
         </is>
       </c>
     </row>
@@ -8912,12 +9004,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>jardim_botanico</t>
+          <t>museu</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Museu</t>
         </is>
       </c>
     </row>
@@ -8929,12 +9021,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>outro_educ_ciencia</t>
+          <t>jardim_botanico</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>Jardim botânico</t>
         </is>
       </c>
     </row>
@@ -8946,12 +9038,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>assoc_moradores</t>
+          <t>outro_educ_ciencia</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Outro (educação/ciência)</t>
         </is>
       </c>
     </row>
@@ -8963,12 +9055,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>assoc_moradores</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -8980,12 +9072,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>cooperativa</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>ONG</t>
         </is>
       </c>
     </row>
@@ -8997,12 +9089,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>catadores</t>
+          <t>cooperativa</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>Cooperativa</t>
         </is>
       </c>
     </row>
@@ -9014,12 +9106,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>mov_sociais</t>
+          <t>catadores</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
+          <t>Catadores</t>
         </is>
       </c>
     </row>
@@ -9031,12 +9123,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>coletivos</t>
+          <t>mov_sociais</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Coletivos</t>
+          <t>Movimentos sociais</t>
         </is>
       </c>
     </row>
@@ -9048,12 +9140,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>grupos_culturais</t>
+          <t>coletivos</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
+          <t>Coletivos</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9157,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>org_comunit_relig</t>
+          <t>grupos_culturais</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Grupos culturais</t>
         </is>
       </c>
     </row>
@@ -9082,12 +9174,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>outro_soc_civil</t>
+          <t>org_comunit_relig</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
+          <t>Organizações comunitárias/religiosas</t>
         </is>
       </c>
     </row>
@@ -9099,12 +9191,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>povos_indigenas</t>
+          <t>outro_soc_civil</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
+          <t>Outro (sociedade civil)</t>
         </is>
       </c>
     </row>
@@ -9116,12 +9208,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>quilombolas</t>
+          <t>povos_indigenas</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Quilombolas</t>
+          <t>Povos indígenas</t>
         </is>
       </c>
     </row>
@@ -9133,12 +9225,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>agric_familiares</t>
+          <t>quilombolas</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Agricultores familiares</t>
+          <t>Quilombolas</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9242,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>pescadores</t>
+          <t>agric_familiares</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Pescadores</t>
+          <t>Agricultores familiares</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9259,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>com_tradicionais</t>
+          <t>pescadores</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
+          <t>Pescadores</t>
         </is>
       </c>
     </row>
@@ -9184,12 +9276,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>liderancas</t>
+          <t>com_tradicionais</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Comunidades tradicionais</t>
         </is>
       </c>
     </row>
@@ -9201,12 +9293,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>detentores_saberes</t>
+          <t>liderancas</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Detentores de conhecimentos locais</t>
+          <t>Lideranças</t>
         </is>
       </c>
     </row>
@@ -9218,29 +9310,29 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>outro_comunidades</t>
+          <t>detentores_saberes</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Outro (comunidades e conhecimentos)</t>
+          <t>Detentores de conhecimentos locais</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>nivel_rel</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>nao_existe</t>
+          <t>outro_comunidades</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Não existe relação — não é parceiro(a)</t>
+          <t>Outro (comunidades e conhecimentos)</t>
         </is>
       </c>
     </row>
@@ -9252,12 +9344,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>sabe_existe</t>
+          <t>nao_existe</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Sabe que existe, mas nunca houve contato — não é parceiro(a)</t>
+          <t>Não existe relação — não é parceiro(a)</t>
         </is>
       </c>
     </row>
@@ -9269,12 +9361,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>contato_pontual</t>
+          <t>sabe_existe</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Já houve contato pontual, sem combinação formal — ainda não é parceiro(a)</t>
+          <t>Sabe que existe, mas nunca houve contato — não é parceiro(a)</t>
         </is>
       </c>
     </row>
@@ -9286,12 +9378,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>parceria</t>
+          <t>contato_pontual</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Parceria — já colaboram em ações combinadas</t>
+          <t>Já houve contato pontual, sem combinação formal — ainda não é parceiro(a)</t>
         </is>
       </c>
     </row>
@@ -9303,29 +9395,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>parceria</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Articulação permanente — parceria contínua e estruturada</t>
+          <t>Parceria — já colaboram em ações combinadas</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>nivel_rel</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>recursos</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Recursos</t>
+          <t>Articulação permanente — parceria contínua e estruturada</t>
         </is>
       </c>
     </row>
@@ -9337,12 +9429,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>recursos</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Recursos</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9446,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>articulacao_institucional</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Articulação institucional</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9463,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>apoio_tecnico</t>
+          <t>articulacao_institucional</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Apoio técnico</t>
+          <t>Articulação institucional</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9480,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>mobilizacao_comunitaria</t>
+          <t>apoio_tecnico</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Mobilização comunitária</t>
+          <t>Apoio técnico</t>
         </is>
       </c>
     </row>
@@ -9405,12 +9497,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>conhecimentos_tradicionais_locai</t>
+          <t>mobilizacao_comunitaria</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Conhecimentos tradicionais/locais</t>
+          <t>Mobilização comunitária</t>
         </is>
       </c>
     </row>
@@ -9422,29 +9514,29 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>conhecimentos_tradicionais_locai</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Conhecimentos tradicionais/locais</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>contrib</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -9456,12 +9548,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>comunicados_impressos</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Comunicados impressos</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
@@ -9473,12 +9565,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>reunioes</t>
+          <t>comunicados_impressos</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>Comunicados impressos</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9582,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>reunioes</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Reuniões</t>
         </is>
       </c>
     </row>
@@ -9507,12 +9599,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>alto_falante_radio_local</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Alto-falante/rádio local</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
@@ -9524,29 +9616,29 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>alto_falante_radio_local</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Alto-falante/rádio local</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -9558,12 +9650,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -9575,12 +9667,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
@@ -9592,29 +9684,29 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>falta_de_contato</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Falta de contato</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -9626,12 +9718,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>burocracia</t>
+          <t>falta_de_contato</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Burocracia</t>
+          <t>Falta de contato</t>
         </is>
       </c>
     </row>
@@ -9643,12 +9735,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>desconfianca_historico_de_relaca</t>
+          <t>burocracia</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Desconfiança/histórico de relação</t>
+          <t>Burocracia</t>
         </is>
       </c>
     </row>
@@ -9660,12 +9752,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>desconfianca_historico_de_relaca</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Desconfiança/histórico de relação</t>
         </is>
       </c>
     </row>
@@ -9677,10 +9769,27 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
+          <t>falta_de_tempo</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Falta de tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>barr_artic</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
           <t>outro</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
+      <c r="C282" t="inlineStr">
         <is>
           <t>Outra</t>
         </is>

--- a/kobo/gestores_semana2_diagnostico.xlsx
+++ b/kobo/gestores_semana2_diagnostico.xlsx
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir.</t>
+          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>

--- a/kobo/gestores_semana2_diagnostico.xlsx
+++ b/kobo/gestores_semana2_diagnostico.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J175"/>
+  <dimension ref="A1:J276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3755,12 +3755,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>q3_10a</t>
+          <t>q3_11</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Q3.10a. Quais instâncias de decisão colegiada existem e funcionam neste local?</t>
+          <t>Q3.11. Quais instâncias de decisão colegiada existem e funcionam neste local?</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>q3_10a_outro</t>
+          <t>q3_11_outro</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3799,7 +3799,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>selected(${q3_10a}, 'outro')</t>
+          <t>selected(${q3_11}, 'outro')</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -3815,12 +3815,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>q3_10b</t>
+          <t>q3_12</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Q3.10b. A gestão tem autonomia para decidir e destinar recursos a ações de Educação Ambiental?</t>
+          <t>Q3.12. A gestão tem autonomia para decidir e destinar recursos a ações de Educação Ambiental?</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -3834,17 +3834,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>net_actors</t>
+          <t>net_nota</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Atores do território (NET_ACTORS)</t>
+          <t>Atores do território (NET_ACTORS). Existência, contato, parceria e articulação permanente são níveis diferentes — não confunda um com o outro. Só marque "Parceria" ou "Articulação permanente" se o local já colabora de fato com esse ator; se ele apenas existe no território ou já houve um contato pontual, isso ainda NÃO é parceria.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -3858,23 +3858,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>net_nota</t>
+          <t>net_rel</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Existência, contato, parceria e articulação permanente são níveis diferentes — não confunda um com o outro. Só marque "Parceria" ou "Articulação permanente" se o local já colabora de fato com esse ator; se ele apenas existe no território ou já houve um contato pontual, isso ainda NÃO é parceria. Use "Adicionar" para registrar um ator por vez.</t>
+          <t>Q3.13. Para cada tipo de ator, qual é a relação atual do local com ele?</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>table-list</t>
+        </is>
+      </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
@@ -3882,21 +3886,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>select_one cat_ator</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>net_cat</t>
+          <t>net_rel_01</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Categoria do ator</t>
+          <t>Secretaria de Educação</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
@@ -3906,21 +3914,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>net_nome</t>
+          <t>net_rel_02</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nome do ator (ex.: UBS Vila Nova)</t>
+          <t>Secretaria de Meio Ambiente</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
@@ -3930,21 +3942,25 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>select_one sim_nao_nsabe</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>net_existe</t>
+          <t>net_rel_03</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Existe no território?</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
@@ -3954,21 +3970,25 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>select_one nivel_rel</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>net_nivel</t>
+          <t>net_rel_04</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nível de relação</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
@@ -3978,21 +3998,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>net_contrib_atual</t>
+          <t>net_rel_05</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Contribuições atuais</t>
+          <t>Assistência Social</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
@@ -4002,26 +4026,26 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>net_contrib_atual_outro</t>
+          <t>net_rel_06</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Obras</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>selected(${net_contrib_atual}, 'outro')</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
@@ -4030,21 +4054,25 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>net_contrib_pot</t>
+          <t>net_rel_07</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Contribuições potenciais</t>
+          <t>Bombeiros</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
@@ -4054,26 +4082,26 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>net_contrib_pot_outro</t>
+          <t>net_rel_08</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>selected(${net_contrib_pot}, 'outro')</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
@@ -4082,21 +4110,25 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>select_one sim_nao</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>net_prioridade</t>
+          <t>net_rel_09</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Prioridade para fortalecimento (NET_PRIORITY_ACTORS) — é um ator prioritário a fortalecer?</t>
+          <t>Vigilância</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
@@ -4106,13 +4138,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
+          <t>select_one nivel_rel_grade</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>net_rel_10</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Outro (poder público)</t>
+        </is>
+      </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
@@ -4122,17 +4166,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>q3_11</t>
+          <t>net_rel_11</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Q3.11. O local sabe a quem contatar em uma emergência climática?</t>
+          <t>Universidade</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -4150,31 +4194,27 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>q3_12</t>
+          <t>net_rel_12</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Q3.12. Quais são esses contatos?</t>
+          <t>Instituto Federal</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>${q3_11}='sim'</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
@@ -4182,17 +4222,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>q3_13</t>
+          <t>net_rel_13</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Q3.13. Existe um procedimento de emergência definido para eventos climáticos?</t>
+          <t>Local técnica</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -4210,26 +4250,26 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>q3_14</t>
+          <t>net_rel_14</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Q3.14. Esse procedimento está documentado/formalizado?</t>
+          <t>Centro de pesquisa</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>${q3_13}='sim'</t>
-        </is>
-      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
@@ -4238,27 +4278,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>q3_15</t>
+          <t>net_rel_15</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Q3.15. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
+          <t>Museu</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
@@ -4266,21 +4306,25 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>select_multiple canais</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>q3_16</t>
+          <t>net_rel_16</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Q3.16. Canais de comunicação do local com a comunidade</t>
+          <t>Jardim botânico</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
@@ -4290,26 +4334,26 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>q3_16_outro</t>
+          <t>net_rel_17</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Outro (educação/ciência)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>selected(${q3_16}, 'outro')</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
@@ -4318,21 +4362,25 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>select_one suficiente</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>q3_17</t>
+          <t>net_rel_18</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Q3.17. Esses canais seriam suficientes numa emergência?</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
@@ -4342,27 +4390,27 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>q3_18</t>
+          <t>net_rel_19</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Q3.18. Algum grupo fica de fora desses canais de comunicação?</t>
+          <t>ONG</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
@@ -4370,31 +4418,27 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>q3_19</t>
+          <t>net_rel_20</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Q3.19. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
+          <t>Cooperativa</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
@@ -4402,27 +4446,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>q3_20</t>
+          <t>net_rel_21</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Q3.20. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
+          <t>Catadores</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
@@ -4430,21 +4474,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>select_multiple barr_artic</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>q3_21</t>
+          <t>net_rel_22</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Q3.21. Barreiras para articular com atores do território</t>
+          <t>Movimentos sociais</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
@@ -4454,26 +4502,26 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>q3_21_outro</t>
+          <t>net_rel_23</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Coletivos</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>selected(${q3_21}, 'outro')</t>
-        </is>
-      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
@@ -4482,27 +4530,27 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>q3_22</t>
+          <t>net_rel_24</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Q3.22. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
+          <t>Grupos culturais</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
@@ -4510,31 +4558,27 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>q3_23</t>
+          <t>net_rel_25</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Q3.23. Quem participou desse caso?</t>
+          <t>Organizações comunitárias/religiosas</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>${q3_22} != ''</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
@@ -4542,31 +4586,27 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>q3_24</t>
+          <t>net_rel_26</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Q3.24. O que funcionou bem?</t>
+          <t>Outro (sociedade civil)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>${q3_22} != ''</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
@@ -4574,31 +4614,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>q3_25</t>
+          <t>net_rel_27</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Q3.25. Quais foram as dificuldades?</t>
+          <t>Povos indígenas</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>${q3_22} != ''</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
@@ -4606,31 +4642,27 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>q3_26</t>
+          <t>net_rel_28</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Q3.26. O que essa experiência ensinou?</t>
+          <t>Quilombolas</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>${q3_22} != ''</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
@@ -4638,27 +4670,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>q3_27</t>
+          <t>net_rel_29</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Q3.27. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
+          <t>Agricultores familiares</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
@@ -4666,31 +4698,27 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>q3_28</t>
+          <t>net_rel_30</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Q3.28. Por quê?</t>
+          <t>Pescadores</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>${q3_27} != ''</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
@@ -4698,21 +4726,25 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>evid_e3</t>
+          <t>net_rel_31</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Evidências — Evidências sobre participação e redes</t>
+          <t>Comunidades tradicionais</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
@@ -4722,21 +4754,25 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>evid_e3_nota</t>
+          <t>net_rel_32</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
+          <t>Lideranças</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
@@ -4746,21 +4782,25 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>select_one tipo_evid</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>evid_e3_tipo</t>
+          <t>net_rel_33</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tipo de evidência</t>
+          <t>Detentores de conhecimentos locais</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
@@ -4770,26 +4810,26 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>evid_e3_tipo_outro</t>
+          <t>net_rel_34</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Outro (comunidades e conhecimentos)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>${evid_e3_tipo}='outro'</t>
-        </is>
-      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
@@ -4798,27 +4838,15 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>evid_e3_desc</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Descreva a evidência</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
@@ -4826,23 +4854,31 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>evid_e3_anexo</t>
+          <t>net_atual</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Anexo (foto/documento) — opcional</t>
+          <t>Q3.14. Contribuições atuais — o que cada ator parceiro(a) já oferece ao local?</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>(${net_rel_01} = 'parceria' or ${net_rel_01} = 'articulacao') or (${net_rel_02} = 'parceria' or ${net_rel_02} = 'articulacao') or (${net_rel_03} = 'parceria' or ${net_rel_03} = 'articulacao') or (${net_rel_04} = 'parceria' or ${net_rel_04} = 'articulacao') or (${net_rel_05} = 'parceria' or ${net_rel_05} = 'articulacao') or (${net_rel_06} = 'parceria' or ${net_rel_06} = 'articulacao') or (${net_rel_07} = 'parceria' or ${net_rel_07} = 'articulacao') or (${net_rel_08} = 'parceria' or ${net_rel_08} = 'articulacao') or (${net_rel_09} = 'parceria' or ${net_rel_09} = 'articulacao') or (${net_rel_10} = 'parceria' or ${net_rel_10} = 'articulacao') or (${net_rel_11} = 'parceria' or ${net_rel_11} = 'articulacao') or (${net_rel_12} = 'parceria' or ${net_rel_12} = 'articulacao') or (${net_rel_13} = 'parceria' or ${net_rel_13} = 'articulacao') or (${net_rel_14} = 'parceria' or ${net_rel_14} = 'articulacao') or (${net_rel_15} = 'parceria' or ${net_rel_15} = 'articulacao') or (${net_rel_16} = 'parceria' or ${net_rel_16} = 'articulacao') or (${net_rel_17} = 'parceria' or ${net_rel_17} = 'articulacao') or (${net_rel_18} = 'parceria' or ${net_rel_18} = 'articulacao') or (${net_rel_19} = 'parceria' or ${net_rel_19} = 'articulacao') or (${net_rel_20} = 'parceria' or ${net_rel_20} = 'articulacao') or (${net_rel_21} = 'parceria' or ${net_rel_21} = 'articulacao') or (${net_rel_22} = 'parceria' or ${net_rel_22} = 'articulacao') or (${net_rel_23} = 'parceria' or ${net_rel_23} = 'articulacao') or (${net_rel_24} = 'parceria' or ${net_rel_24} = 'articulacao') or (${net_rel_25} = 'parceria' or ${net_rel_25} = 'articulacao') or (${net_rel_26} = 'parceria' or ${net_rel_26} = 'articulacao') or (${net_rel_27} = 'parceria' or ${net_rel_27} = 'articulacao') or (${net_rel_28} = 'parceria' or ${net_rel_28} = 'articulacao') or (${net_rel_29} = 'parceria' or ${net_rel_29} = 'articulacao') or (${net_rel_30} = 'parceria' or ${net_rel_30} = 'articulacao') or (${net_rel_31} = 'parceria' or ${net_rel_31} = 'articulacao') or (${net_rel_32} = 'parceria' or ${net_rel_32} = 'articulacao') or (${net_rel_33} = 'parceria' or ${net_rel_33} = 'articulacao') or (${net_rel_34} = 'parceria' or ${net_rel_34} = 'articulacao')</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>table-list</t>
+        </is>
+      </c>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
@@ -4850,14 +4886,26 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
-      <c r="C169" t="inlineStr"/>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>net_atual_01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Secretaria de Educação</t>
+        </is>
+      </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>${net_rel_01} = 'parceria' or ${net_rel_01} = 'articulacao'</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -4866,14 +4914,26 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr"/>
-      <c r="C170" t="inlineStr"/>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>net_atual_02</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Secretaria de Meio Ambiente</t>
+        </is>
+      </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>${net_rel_02} = 'parceria' or ${net_rel_02} = 'articulacao'</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
@@ -4882,22 +4942,26 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_multiple contrib</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>confirmacao</t>
+          <t>net_atual_03</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Confirmação final</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>${net_rel_03} = 'parceria' or ${net_rel_03} = 'articulacao'</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
@@ -4906,22 +4970,26 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple contrib</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>confirmacao_msg</t>
+          <t>net_atual_04</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>${net_rel_04} = 'parceria' or ${net_rel_04} = 'articulacao'</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
@@ -4930,26 +4998,26 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>select_one confirmo</t>
+          <t>select_multiple contrib</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>confirmacao_envio</t>
+          <t>net_atual_05</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Revisei minhas respostas e confirmo o envio.</t>
+          <t>Assistência Social</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>${net_rel_05} = 'parceria' or ${net_rel_05} = 'articulacao'</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
@@ -4958,14 +5026,26 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>net_atual_06</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Obras</t>
+        </is>
+      </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>${net_rel_06} = 'parceria' or ${net_rel_06} = 'articulacao'</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -4974,18 +5054,2786 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
-      <c r="C175" t="inlineStr"/>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>net_atual_07</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Bombeiros</t>
+        </is>
+      </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>${net_rel_07} = 'parceria' or ${net_rel_07} = 'articulacao'</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>net_atual_08</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>UBS</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>${net_rel_08} = 'parceria' or ${net_rel_08} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>net_atual_09</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Vigilância</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>${net_rel_09} = 'parceria' or ${net_rel_09} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>net_atual_10</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Outro (poder público)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>${net_rel_10} = 'parceria' or ${net_rel_10} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>net_atual_11</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Universidade</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>${net_rel_11} = 'parceria' or ${net_rel_11} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>net_atual_12</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Instituto Federal</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>${net_rel_12} = 'parceria' or ${net_rel_12} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>net_atual_13</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Local técnica</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>${net_rel_13} = 'parceria' or ${net_rel_13} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>net_atual_14</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Centro de pesquisa</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>${net_rel_14} = 'parceria' or ${net_rel_14} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>net_atual_15</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Museu</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>${net_rel_15} = 'parceria' or ${net_rel_15} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>net_atual_16</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Jardim botânico</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>${net_rel_16} = 'parceria' or ${net_rel_16} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>net_atual_17</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Outro (educação/ciência)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>${net_rel_17} = 'parceria' or ${net_rel_17} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>net_atual_18</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Associação de moradores</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>${net_rel_18} = 'parceria' or ${net_rel_18} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>net_atual_19</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ONG</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>${net_rel_19} = 'parceria' or ${net_rel_19} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>net_atual_20</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Cooperativa</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>${net_rel_20} = 'parceria' or ${net_rel_20} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>net_atual_21</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Catadores</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>${net_rel_21} = 'parceria' or ${net_rel_21} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>net_atual_22</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Movimentos sociais</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>${net_rel_22} = 'parceria' or ${net_rel_22} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>net_atual_23</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Coletivos</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>${net_rel_23} = 'parceria' or ${net_rel_23} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>net_atual_24</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Grupos culturais</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>${net_rel_24} = 'parceria' or ${net_rel_24} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>net_atual_25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Organizações comunitárias/religiosas</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>${net_rel_25} = 'parceria' or ${net_rel_25} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>net_atual_26</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Outro (sociedade civil)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>${net_rel_26} = 'parceria' or ${net_rel_26} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>net_atual_27</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Povos indígenas</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>${net_rel_27} = 'parceria' or ${net_rel_27} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>net_atual_28</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Quilombolas</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>${net_rel_28} = 'parceria' or ${net_rel_28} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>net_atual_29</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Agricultores familiares</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>${net_rel_29} = 'parceria' or ${net_rel_29} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>net_atual_30</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Pescadores</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>${net_rel_30} = 'parceria' or ${net_rel_30} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>net_atual_31</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Comunidades tradicionais</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>${net_rel_31} = 'parceria' or ${net_rel_31} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>net_atual_32</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Lideranças</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>${net_rel_32} = 'parceria' or ${net_rel_32} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>net_atual_33</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Detentores de conhecimentos locais</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>${net_rel_33} = 'parceria' or ${net_rel_33} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>net_atual_34</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Outro (comunidades e conhecimentos)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>${net_rel_34} = 'parceria' or ${net_rel_34} = 'articulacao'</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>net_atual_outro</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Especifique (Outro) — contribuições atuais</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>selected(${net_atual_01}, 'outro') or selected(${net_atual_02}, 'outro') or selected(${net_atual_03}, 'outro') or selected(${net_atual_04}, 'outro') or selected(${net_atual_05}, 'outro') or selected(${net_atual_06}, 'outro') or selected(${net_atual_07}, 'outro') or selected(${net_atual_08}, 'outro') or selected(${net_atual_09}, 'outro') or selected(${net_atual_10}, 'outro') or selected(${net_atual_11}, 'outro') or selected(${net_atual_12}, 'outro') or selected(${net_atual_13}, 'outro') or selected(${net_atual_14}, 'outro') or selected(${net_atual_15}, 'outro') or selected(${net_atual_16}, 'outro') or selected(${net_atual_17}, 'outro') or selected(${net_atual_18}, 'outro') or selected(${net_atual_19}, 'outro') or selected(${net_atual_20}, 'outro') or selected(${net_atual_21}, 'outro') or selected(${net_atual_22}, 'outro') or selected(${net_atual_23}, 'outro') or selected(${net_atual_24}, 'outro') or selected(${net_atual_25}, 'outro') or selected(${net_atual_26}, 'outro') or selected(${net_atual_27}, 'outro') or selected(${net_atual_28}, 'outro') or selected(${net_atual_29}, 'outro') or selected(${net_atual_30}, 'outro') or selected(${net_atual_31}, 'outro') or selected(${net_atual_32}, 'outro') or selected(${net_atual_33}, 'outro') or selected(${net_atual_34}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>net_pot</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Q3.15. Contribuições potenciais — o que cada ator que existe no território poderia oferecer?</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>(${net_rel_01} != '' and ${net_rel_01} != 'nao_existe' and ${net_rel_01} != 'nao_sei') or (${net_rel_02} != '' and ${net_rel_02} != 'nao_existe' and ${net_rel_02} != 'nao_sei') or (${net_rel_03} != '' and ${net_rel_03} != 'nao_existe' and ${net_rel_03} != 'nao_sei') or (${net_rel_04} != '' and ${net_rel_04} != 'nao_existe' and ${net_rel_04} != 'nao_sei') or (${net_rel_05} != '' and ${net_rel_05} != 'nao_existe' and ${net_rel_05} != 'nao_sei') or (${net_rel_06} != '' and ${net_rel_06} != 'nao_existe' and ${net_rel_06} != 'nao_sei') or (${net_rel_07} != '' and ${net_rel_07} != 'nao_existe' and ${net_rel_07} != 'nao_sei') or (${net_rel_08} != '' and ${net_rel_08} != 'nao_existe' and ${net_rel_08} != 'nao_sei') or (${net_rel_09} != '' and ${net_rel_09} != 'nao_existe' and ${net_rel_09} != 'nao_sei') or (${net_rel_10} != '' and ${net_rel_10} != 'nao_existe' and ${net_rel_10} != 'nao_sei') or (${net_rel_11} != '' and ${net_rel_11} != 'nao_existe' and ${net_rel_11} != 'nao_sei') or (${net_rel_12} != '' and ${net_rel_12} != 'nao_existe' and ${net_rel_12} != 'nao_sei') or (${net_rel_13} != '' and ${net_rel_13} != 'nao_existe' and ${net_rel_13} != 'nao_sei') or (${net_rel_14} != '' and ${net_rel_14} != 'nao_existe' and ${net_rel_14} != 'nao_sei') or (${net_rel_15} != '' and ${net_rel_15} != 'nao_existe' and ${net_rel_15} != 'nao_sei') or (${net_rel_16} != '' and ${net_rel_16} != 'nao_existe' and ${net_rel_16} != 'nao_sei') or (${net_rel_17} != '' and ${net_rel_17} != 'nao_existe' and ${net_rel_17} != 'nao_sei') or (${net_rel_18} != '' and ${net_rel_18} != 'nao_existe' and ${net_rel_18} != 'nao_sei') or (${net_rel_19} != '' and ${net_rel_19} != 'nao_existe' and ${net_rel_19} != 'nao_sei') or (${net_rel_20} != '' and ${net_rel_20} != 'nao_existe' and ${net_rel_20} != 'nao_sei') or (${net_rel_21} != '' and ${net_rel_21} != 'nao_existe' and ${net_rel_21} != 'nao_sei') or (${net_rel_22} != '' and ${net_rel_22} != 'nao_existe' and ${net_rel_22} != 'nao_sei') or (${net_rel_23} != '' and ${net_rel_23} != 'nao_existe' and ${net_rel_23} != 'nao_sei') or (${net_rel_24} != '' and ${net_rel_24} != 'nao_existe' and ${net_rel_24} != 'nao_sei') or (${net_rel_25} != '' and ${net_rel_25} != 'nao_existe' and ${net_rel_25} != 'nao_sei') or (${net_rel_26} != '' and ${net_rel_26} != 'nao_existe' and ${net_rel_26} != 'nao_sei') or (${net_rel_27} != '' and ${net_rel_27} != 'nao_existe' and ${net_rel_27} != 'nao_sei') or (${net_rel_28} != '' and ${net_rel_28} != 'nao_existe' and ${net_rel_28} != 'nao_sei') or (${net_rel_29} != '' and ${net_rel_29} != 'nao_existe' and ${net_rel_29} != 'nao_sei') or (${net_rel_30} != '' and ${net_rel_30} != 'nao_existe' and ${net_rel_30} != 'nao_sei') or (${net_rel_31} != '' and ${net_rel_31} != 'nao_existe' and ${net_rel_31} != 'nao_sei') or (${net_rel_32} != '' and ${net_rel_32} != 'nao_existe' and ${net_rel_32} != 'nao_sei') or (${net_rel_33} != '' and ${net_rel_33} != 'nao_existe' and ${net_rel_33} != 'nao_sei') or (${net_rel_34} != '' and ${net_rel_34} != 'nao_existe' and ${net_rel_34} != 'nao_sei')</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>table-list</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>net_pot_01</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Secretaria de Educação</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>${net_rel_01} != '' and ${net_rel_01} != 'nao_existe' and ${net_rel_01} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>net_pot_02</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Secretaria de Meio Ambiente</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>${net_rel_02} != '' and ${net_rel_02} != 'nao_existe' and ${net_rel_02} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>net_pot_03</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Defesa Civil</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>${net_rel_03} != '' and ${net_rel_03} != 'nao_existe' and ${net_rel_03} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>net_pot_04</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Secretaria de Saúde</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>${net_rel_04} != '' and ${net_rel_04} != 'nao_existe' and ${net_rel_04} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>net_pot_05</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Assistência Social</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>${net_rel_05} != '' and ${net_rel_05} != 'nao_existe' and ${net_rel_05} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>net_pot_06</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Obras</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>${net_rel_06} != '' and ${net_rel_06} != 'nao_existe' and ${net_rel_06} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>net_pot_07</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Bombeiros</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>${net_rel_07} != '' and ${net_rel_07} != 'nao_existe' and ${net_rel_07} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>net_pot_08</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>UBS</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>${net_rel_08} != '' and ${net_rel_08} != 'nao_existe' and ${net_rel_08} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>net_pot_09</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Vigilância</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>${net_rel_09} != '' and ${net_rel_09} != 'nao_existe' and ${net_rel_09} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>net_pot_10</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Outro (poder público)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>${net_rel_10} != '' and ${net_rel_10} != 'nao_existe' and ${net_rel_10} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>net_pot_11</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Universidade</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>${net_rel_11} != '' and ${net_rel_11} != 'nao_existe' and ${net_rel_11} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>net_pot_12</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Instituto Federal</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>${net_rel_12} != '' and ${net_rel_12} != 'nao_existe' and ${net_rel_12} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>net_pot_13</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Local técnica</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>${net_rel_13} != '' and ${net_rel_13} != 'nao_existe' and ${net_rel_13} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>net_pot_14</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Centro de pesquisa</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>${net_rel_14} != '' and ${net_rel_14} != 'nao_existe' and ${net_rel_14} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>net_pot_15</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Museu</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>${net_rel_15} != '' and ${net_rel_15} != 'nao_existe' and ${net_rel_15} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>net_pot_16</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Jardim botânico</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>${net_rel_16} != '' and ${net_rel_16} != 'nao_existe' and ${net_rel_16} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>net_pot_17</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Outro (educação/ciência)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>${net_rel_17} != '' and ${net_rel_17} != 'nao_existe' and ${net_rel_17} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>net_pot_18</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Associação de moradores</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>${net_rel_18} != '' and ${net_rel_18} != 'nao_existe' and ${net_rel_18} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>net_pot_19</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ONG</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>${net_rel_19} != '' and ${net_rel_19} != 'nao_existe' and ${net_rel_19} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>net_pot_20</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Cooperativa</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>${net_rel_20} != '' and ${net_rel_20} != 'nao_existe' and ${net_rel_20} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>net_pot_21</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Catadores</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>${net_rel_21} != '' and ${net_rel_21} != 'nao_existe' and ${net_rel_21} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>net_pot_22</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Movimentos sociais</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>${net_rel_22} != '' and ${net_rel_22} != 'nao_existe' and ${net_rel_22} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>net_pot_23</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Coletivos</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>${net_rel_23} != '' and ${net_rel_23} != 'nao_existe' and ${net_rel_23} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>net_pot_24</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Grupos culturais</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>${net_rel_24} != '' and ${net_rel_24} != 'nao_existe' and ${net_rel_24} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>net_pot_25</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Organizações comunitárias/religiosas</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>${net_rel_25} != '' and ${net_rel_25} != 'nao_existe' and ${net_rel_25} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>net_pot_26</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Outro (sociedade civil)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>${net_rel_26} != '' and ${net_rel_26} != 'nao_existe' and ${net_rel_26} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>net_pot_27</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Povos indígenas</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>${net_rel_27} != '' and ${net_rel_27} != 'nao_existe' and ${net_rel_27} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>net_pot_28</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Quilombolas</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>${net_rel_28} != '' and ${net_rel_28} != 'nao_existe' and ${net_rel_28} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>net_pot_29</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Agricultores familiares</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>${net_rel_29} != '' and ${net_rel_29} != 'nao_existe' and ${net_rel_29} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>net_pot_30</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Pescadores</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>${net_rel_30} != '' and ${net_rel_30} != 'nao_existe' and ${net_rel_30} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>net_pot_31</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Comunidades tradicionais</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>${net_rel_31} != '' and ${net_rel_31} != 'nao_existe' and ${net_rel_31} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>net_pot_32</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Lideranças</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>${net_rel_32} != '' and ${net_rel_32} != 'nao_existe' and ${net_rel_32} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>net_pot_33</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Detentores de conhecimentos locais</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>${net_rel_33} != '' and ${net_rel_33} != 'nao_existe' and ${net_rel_33} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>net_pot_34</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Outro (comunidades e conhecimentos)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>${net_rel_34} != '' and ${net_rel_34} != 'nao_existe' and ${net_rel_34} != 'nao_sei'</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>net_pot_outro</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Especifique (Outro) — contribuições potenciais</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>selected(${net_pot_01}, 'outro') or selected(${net_pot_02}, 'outro') or selected(${net_pot_03}, 'outro') or selected(${net_pot_04}, 'outro') or selected(${net_pot_05}, 'outro') or selected(${net_pot_06}, 'outro') or selected(${net_pot_07}, 'outro') or selected(${net_pot_08}, 'outro') or selected(${net_pot_09}, 'outro') or selected(${net_pot_10}, 'outro') or selected(${net_pot_11}, 'outro') or selected(${net_pot_12}, 'outro') or selected(${net_pot_13}, 'outro') or selected(${net_pot_14}, 'outro') or selected(${net_pot_15}, 'outro') or selected(${net_pot_16}, 'outro') or selected(${net_pot_17}, 'outro') or selected(${net_pot_18}, 'outro') or selected(${net_pot_19}, 'outro') or selected(${net_pot_20}, 'outro') or selected(${net_pot_21}, 'outro') or selected(${net_pot_22}, 'outro') or selected(${net_pot_23}, 'outro') or selected(${net_pot_24}, 'outro') or selected(${net_pot_25}, 'outro') or selected(${net_pot_26}, 'outro') or selected(${net_pot_27}, 'outro') or selected(${net_pot_28}, 'outro') or selected(${net_pot_29}, 'outro') or selected(${net_pot_30}, 'outro') or selected(${net_pot_31}, 'outro') or selected(${net_pot_32}, 'outro') or selected(${net_pot_33}, 'outro') or selected(${net_pot_34}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>select_multiple cat_ator</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>q3_16</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Q3.16. Quais atores são prioritários para fortalecer a relação? (NET_PRIORITY_ACTORS)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>q3_17</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Q3.17. Cite o nome do ator mais relevante para o local hoje (ex.: UBS Vila Nova)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>select_one sim_nao_ns</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>q3_18</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Q3.18. O local sabe a quem contatar em uma emergência climática?</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>q3_19</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Q3.19. Quais são esses contatos?</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>${q3_18}='sim'</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>select_one sim_nao_ns</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>q3_20</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Q3.20. Existe um procedimento de emergência definido para eventos climáticos?</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>select_one sim_nao_ns</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>q3_21</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Q3.21. Esse procedimento está documentado/formalizado?</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>${q3_20}='sim'</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>q3_22</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Q3.22. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>select_multiple canais</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>q3_23</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Q3.23. Canais de comunicação do local com a comunidade</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>q3_23_outro</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>selected(${q3_23}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>select_one suficiente</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>q3_24</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Q3.24. Esses canais seriam suficientes numa emergência?</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>q3_25</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Q3.25. Algum grupo fica de fora desses canais de comunicação?</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>q3_26</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Q3.26. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>q3_27</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Q3.27. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>select_multiple barr_artic</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>q3_28</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Q3.28. Barreiras para articular com atores do território</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>q3_28_outro</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>selected(${q3_28}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>q3_29</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Q3.29. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>q3_30</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Q3.30. Quem participou desse caso?</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>${q3_29} != ''</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>q3_31</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Q3.31. O que funcionou bem?</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>${q3_29} != ''</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>q3_32</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Q3.32. Quais foram as dificuldades?</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>${q3_29} != ''</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>q3_33</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Q3.33. O que essa experiência ensinou?</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>${q3_29} != ''</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>q3_34</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Q3.34. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>q3_35</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Q3.35. Por quê?</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>${q3_34} != ''</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>begin_repeat</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>evid_e3</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Evidências — Evidências sobre participação e redes</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>evid_e3_nota</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>select_one tipo_evid</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>evid_e3_tipo</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Tipo de evidência</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>evid_e3_tipo_outro</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>${evid_e3_tipo}='outro'</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>evid_e3_desc</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Descreva a evidência</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>evid_e3_anexo</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Anexo (foto/documento) — opcional</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>end_repeat</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>confirmacao</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Confirmação final</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>confirmacao_msg</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>select_one confirmo</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>confirmacao_envio</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Revisei minhas respostas e confirmo o envio.</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4998,7 +7846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C282"/>
+  <dimension ref="A1:C278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5123,85 +7971,85 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sim_nao_nsabe</t>
+          <t>tipo_evid</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>observacao_direta</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Observação direta</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sim_nao_nsabe</t>
+          <t>tipo_evid</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>documento</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Documento</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sim_nao_nsabe</t>
+          <t>tipo_evid</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>foto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Foto</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sim_nao</t>
+          <t>tipo_evid</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>depoimento</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Depoimento</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sim_nao</t>
+          <t>tipo_evid</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>registro_historico</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Registro histórico</t>
         </is>
       </c>
     </row>
@@ -5213,97 +8061,97 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>observacao_direta</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Observação direta</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tipo_evid</t>
+          <t>onde_ea</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>documento</t>
+          <t>aulas_regulares</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Aulas regulares</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tipo_evid</t>
+          <t>onde_ea</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>foto</t>
+          <t>projetos_interdisciplinares</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Foto</t>
+          <t>Projetos interdisciplinares</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tipo_evid</t>
+          <t>onde_ea</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>depoimento</t>
+          <t>feiras_mostras</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Depoimento</t>
+          <t>Feiras/mostras</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tipo_evid</t>
+          <t>onde_ea</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>registro_historico</t>
+          <t>momentos_civicos</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Registro histórico</t>
+          <t>Momentos cívicos</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tipo_evid</t>
+          <t>onde_ea</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>em_datas_comemorativas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Em datas comemorativas</t>
         </is>
       </c>
     </row>
@@ -5315,12 +8163,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>aulas_regulares</t>
+          <t>clube_gremio_estudantil</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aulas regulares</t>
+          <t>Clube/grêmio estudantil</t>
         </is>
       </c>
     </row>
@@ -5332,12 +8180,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>projetos_interdisciplinares</t>
+          <t>iniciativas_de_estudantes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Projetos interdisciplinares</t>
+          <t>Iniciativas de estudantes</t>
         </is>
       </c>
     </row>
@@ -5349,12 +8197,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>feiras_mostras</t>
+          <t>parcerias_externas</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Feiras/mostras</t>
+          <t>Parcerias externas</t>
         </is>
       </c>
     </row>
@@ -5366,97 +8214,97 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>momentos_civicos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Momentos cívicos</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>onde_ea</t>
+          <t>instit_ea</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>em_datas_comemorativas</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Em datas comemorativas</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>onde_ea</t>
+          <t>instit_ea</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>clube_gremio_estudantil</t>
+          <t>isolada_ocasional</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Clube/grêmio estudantil</t>
+          <t>Isolada/ocasional</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>onde_ea</t>
+          <t>instit_ea</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>iniciativas_de_estudantes</t>
+          <t>recorrente_dependente_de_algumas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iniciativas de estudantes</t>
+          <t>Recorrente, dependente de algumas pessoas</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>onde_ea</t>
+          <t>instit_ea</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>parcerias_externas</t>
+          <t>presente_em_diferentes_component</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Parcerias externas</t>
+          <t>Presente em diferentes componentes/projetos</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>onde_ea</t>
+          <t>instit_ea</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>integrada_ao_planejamento</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Integrada ao planejamento</t>
         </is>
       </c>
     </row>
@@ -5468,12 +8316,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>institucionalizada_e_continua</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Institucionalizada e contínua</t>
         </is>
       </c>
     </row>
@@ -5485,155 +8333,155 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>isolada_ocasional</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Isolada/ocasional</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>instit_ea</t>
+          <t>ppp_sit</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>recorrente_dependente_de_algumas</t>
+          <t>presente_e_detalhada</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Recorrente, dependente de algumas pessoas</t>
+          <t>Presente e detalhada</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>instit_ea</t>
+          <t>ppp_sit</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>presente_em_diferentes_component</t>
+          <t>presente_de_forma_generica</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Presente em diferentes componentes/projetos</t>
+          <t>Presente de forma genérica</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>instit_ea</t>
+          <t>ppp_sit</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>integrada_ao_planejamento</t>
+          <t>ausente</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Integrada ao planejamento</t>
+          <t>Ausente</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>instit_ea</t>
+          <t>ppp_sit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>institucionalizada_e_continua</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Institucionalizada e contínua</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>instit_ea</t>
+          <t>ppp_pratica</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>totalmente</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Totalmente</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ppp_sit</t>
+          <t>ppp_pratica</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>presente_e_detalhada</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Presente e detalhada</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ppp_sit</t>
+          <t>ppp_pratica</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>presente_de_forma_generica</t>
+          <t>pouco</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Presente de forma genérica</t>
+          <t>Pouco</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ppp_sit</t>
+          <t>ppp_pratica</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ausente</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ppp_sit</t>
+          <t>ppp_pratica</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5650,85 +8498,85 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ppp_pratica</t>
+          <t>areas_curr</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>totalmente</t>
+          <t>ciencias</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Totalmente</t>
+          <t>Ciências</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ppp_pratica</t>
+          <t>areas_curr</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>geografia</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Geografia</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ppp_pratica</t>
+          <t>areas_curr</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pouco</t>
+          <t>historia</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pouco</t>
+          <t>História</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ppp_pratica</t>
+          <t>areas_curr</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>lingua_portuguesa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Língua Portuguesa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ppp_pratica</t>
+          <t>areas_curr</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>matematica</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Matemática</t>
         </is>
       </c>
     </row>
@@ -5740,12 +8588,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ciencias</t>
+          <t>artes</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ciências</t>
+          <t>Artes</t>
         </is>
       </c>
     </row>
@@ -5757,12 +8605,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>geografia</t>
+          <t>educacao_fisica</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Geografia</t>
+          <t>Educação Física</t>
         </is>
       </c>
     </row>
@@ -5774,97 +8622,97 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>historia</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>História</t>
+          <t>Outras</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>areas_curr</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>lingua_portuguesa</t>
+          <t>disciplinas_separadas</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Língua Portuguesa</t>
+          <t>Disciplinas separadas</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>areas_curr</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>matematica</t>
+          <t>mesmo_tema_sem_planejamento_conj</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Matemática</t>
+          <t>Mesmo tema, sem planejamento conjunto</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>areas_curr</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>artes</t>
+          <t>algum_planejamento_conjunto</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Algum planejamento conjunto</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>areas_curr</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>educacao_fisica</t>
+          <t>investigacao_conjunta</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Educação Física</t>
+          <t>Investigação conjunta</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>areas_curr</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>objetivos_comuns</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Objetivos comuns</t>
         </is>
       </c>
     </row>
@@ -5876,12 +8724,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>disciplinas_separadas</t>
+          <t>intervencao_territorial_coletiva</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Disciplinas separadas</t>
+          <t>Intervenção territorial coletiva</t>
         </is>
       </c>
     </row>
@@ -5893,12 +8741,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>mesmo_tema_sem_planejamento_conj</t>
+          <t>sem_articulacao</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mesmo tema, sem planejamento conjunto</t>
+          <t>Sem articulação</t>
         </is>
       </c>
     </row>
@@ -5910,97 +8758,97 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>algum_planejamento_conjunto</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algum planejamento conjunto</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>freq_ea</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>investigacao_conjunta</t>
+          <t>diaria</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Investigação conjunta</t>
+          <t>Diária</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>freq_ea</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>objetivos_comuns</t>
+          <t>semanal</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Objetivos comuns</t>
+          <t>Semanal</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>freq_ea</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>intervencao_territorial_coletiva</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Intervenção territorial coletiva</t>
+          <t>Mensal</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>freq_ea</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>sem_articulacao</t>
+          <t>esporadica</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sem articulação</t>
+          <t>Esporádica</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>freq_ea</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>anual</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Anual</t>
         </is>
       </c>
     </row>
@@ -6012,12 +8860,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>diaria</t>
+          <t>nao_ocorre</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Diária</t>
+          <t>Não ocorre</t>
         </is>
       </c>
     </row>
@@ -6029,97 +8877,97 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Semanal</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>freq_ea</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>sala_de_aula</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Sala de aula</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>freq_ea</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>esporadica</t>
+          <t>patio_area_externa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Esporádica</t>
+          <t>Pátio/área externa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>freq_ea</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>anual</t>
+          <t>visita_de_campo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Anual</t>
+          <t>Visita de campo</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>freq_ea</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nao_ocorre</t>
+          <t>projeto_especial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Não ocorre</t>
+          <t>Projeto especial</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>freq_ea</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>feira</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Feira</t>
         </is>
       </c>
     </row>
@@ -6131,97 +8979,97 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>sala_de_aula</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sala de aula</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>contexto_ea</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>patio_area_externa</t>
+          <t>professor_individualmente</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pátio/área externa</t>
+          <t>Professor(a) individualmente</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>contexto_ea</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>visita_de_campo</t>
+          <t>grupo_de_professores</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Visita de campo</t>
+          <t>Grupo de professores(as)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>contexto_ea</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>projeto_especial</t>
+          <t>coordenacao_pedagogica</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Projeto especial</t>
+          <t>Coordenação pedagógica</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>contexto_ea</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>feira</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Feira</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>contexto_ea</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
@@ -6233,240 +9081,240 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>professor_individualmente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Professor(a) individualmente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>grupo_de_professores</t>
+          <t>espectador</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Grupo de professores(as)</t>
+          <t>Espectador</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>coordenacao_pedagogica</t>
+          <t>participante_pontual</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Coordenação pedagógica</t>
+          <t>Participante pontual</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Protagonista</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>coprodutor</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Coprodutor</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>continuidade_ativ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>espectador</t>
+          <t>depende_da_permanencia_de_profes</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Espectador</t>
+          <t>Depende da permanência de professor(a) específico(a)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>continuidade_ativ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>participante_pontual</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Participante pontual</t>
+          <t>Tem continuidade institucional garantida</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>continuidade_ativ</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Protagonista</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>continuidade_ativ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>coprodutor</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Coprodutor</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nunca</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Nunca</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>continuidade_ativ</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>depende_da_permanencia_de_profes</t>
+          <t>raramente</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Depende da permanência de professor(a) específico(a)</t>
+          <t>Raramente</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>continuidade_ativ</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>as_vezes</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tem continuidade institucional garantida</t>
+          <t>Às vezes</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>continuidade_ativ</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>frequentemente</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Frequentemente</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>continuidade_ativ</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6483,85 +9331,85 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nunca</t>
+          <t>agua</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Nunca</t>
+          <t>Água</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>raramente</t>
+          <t>biodiversidade</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Raramente</t>
+          <t>Biodiversidade</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>as_vezes</t>
+          <t>residuos</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Às vezes</t>
+          <t>Resíduos</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>frequentemente</t>
+          <t>mudancas_climaticas</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Frequentemente</t>
+          <t>Mudanças climáticas</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Energia</t>
         </is>
       </c>
     </row>
@@ -6573,12 +9421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>agua</t>
+          <t>alimentacao</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Alimentação</t>
         </is>
       </c>
     </row>
@@ -6590,12 +9438,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>biodiversidade</t>
+          <t>consumo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Biodiversidade</t>
+          <t>Consumo</t>
         </is>
       </c>
     </row>
@@ -6607,12 +9455,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>residuos</t>
+          <t>saneamento</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Resíduos</t>
+          <t>Saneamento</t>
         </is>
       </c>
     </row>
@@ -6624,12 +9472,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>mudancas_climaticas</t>
+          <t>saude</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mudanças climáticas</t>
+          <t>Saúde</t>
         </is>
       </c>
     </row>
@@ -6641,12 +9489,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>riscos_desastres</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Riscos/desastres</t>
         </is>
       </c>
     </row>
@@ -6658,12 +9506,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>alimentacao</t>
+          <t>justica_socioambiental</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Justiça socioambiental</t>
         </is>
       </c>
     </row>
@@ -6675,12 +9523,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>consumo</t>
+          <t>territorio</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Território</t>
         </is>
       </c>
     </row>
@@ -6692,12 +9540,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>saneamento</t>
+          <t>conflitos</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saneamento</t>
+          <t>Conflitos</t>
         </is>
       </c>
     </row>
@@ -6709,12 +9557,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>saude</t>
+          <t>povos_e_comunidades_tradicionais</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>Povos e comunidades tradicionais</t>
         </is>
       </c>
     </row>
@@ -6726,97 +9574,97 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>riscos_desastres</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Riscos/desastres</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>justica_socioambiental</t>
+          <t>falta_de_formacao</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Justiça socioambiental</t>
+          <t>Falta de formação</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>territorio</t>
+          <t>falta_de_material</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Território</t>
+          <t>Falta de material</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>conflitos</t>
+          <t>tema_sensivel_delicado</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Conflitos</t>
+          <t>Tema sensível/delicado</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>povos_e_comunidades_tradicionais</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Povos e comunidades tradicionais</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>curriculo</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Currículo</t>
         </is>
       </c>
     </row>
@@ -6828,97 +9676,97 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>falta_de_formacao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Falta de formação</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>falta_de_material</t>
+          <t>aula_expositiva</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Falta de material</t>
+          <t>Aula expositiva</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>tema_sensivel_delicado</t>
+          <t>projeto</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tema sensível/delicado</t>
+          <t>Projeto</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>oficina</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Oficina</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>curriculo</t>
+          <t>saida_de_campo</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Currículo</t>
+          <t>Saída de campo</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>horta_experimentacao</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Horta/experimentação</t>
         </is>
       </c>
     </row>
@@ -6930,12 +9778,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>aula_expositiva</t>
+          <t>rodas_de_conversa</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Aula expositiva</t>
+          <t>Rodas de conversa</t>
         </is>
       </c>
     </row>
@@ -6947,12 +9795,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>projeto</t>
+          <t>producao_audiovisual</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Produção audiovisual</t>
         </is>
       </c>
     </row>
@@ -6964,12 +9812,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>oficina</t>
+          <t>cartografia</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Oficina</t>
+          <t>Cartografia</t>
         </is>
       </c>
     </row>
@@ -6981,267 +9829,267 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>saida_de_campo</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Saída de campo</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>horta_experimentacao</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Horta/experimentação</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>rodas_de_conversa</t>
+          <t>pouco</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Rodas de conversa</t>
+          <t>Pouco</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>producao_audiovisual</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Produção audiovisual</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>cartografia</t>
+          <t>significativo</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cartografia</t>
+          <t>Significativo</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>1 — Nada confiante(a)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>pouco</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Pouco</t>
+          <t>2 — Pouco confiante</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>3 — Moderadamente confiante</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>significativo</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Significativo</t>
+          <t>4 — Confiante</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>5 — Muito confiante</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>1 — Nada confiante(a)</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>material_didatico</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2 — Pouco confiante</t>
+          <t>Material didático</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>tempo_de_planejamento</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3 — Moderadamente confiante</t>
+          <t>Tempo de planejamento</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>4 — Confiante</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>parcerias</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>5 — Muito confiante</t>
+          <t>Parcerias</t>
         </is>
       </c>
     </row>
@@ -7253,12 +10101,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -7270,97 +10118,97 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>material_didatico</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Material didático</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>tempo_de_planejamento</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tempo de planejamento</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>curriculo_sobrecarregado</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Currículo sobrecarregado</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>parcerias</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Parcerias</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Materiais</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -7372,12 +10220,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
@@ -7389,12 +10237,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>curriculo_sobrecarregado</t>
+          <t>planejamento_coletivo</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Currículo sobrecarregado</t>
+          <t>Planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -7406,12 +10254,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>interdisciplinaridade</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Interdisciplinaridade</t>
         </is>
       </c>
     </row>
@@ -7423,12 +10271,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>informacoes_territoriais</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Materiais</t>
+          <t>Informações territoriais</t>
         </is>
       </c>
     </row>
@@ -7440,12 +10288,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>descontinuidade</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Descontinuidade</t>
         </is>
       </c>
     </row>
@@ -7457,12 +10305,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>rotatividade_de_profissionais</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Rotatividade de profissionais</t>
         </is>
       </c>
     </row>
@@ -7474,165 +10322,165 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>planejamento_coletivo</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Planejamento coletivo</t>
+          <t>Outras</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>interdisciplinaridade</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Interdisciplinaridade</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>informacoes_territoriais</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Informações territoriais</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>descontinuidade</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Descontinuidade</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>rotatividade_de_profissionais</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Rotatividade de profissionais</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>reserva_tempo_para_planejamento_</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Reserva tempo para planejamento coletivo</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>inclui_a_ea_no_ppp_planejamento_</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Inclui a EA no PPP/planejamento anual</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>viabiliza_recursos_e_materiais</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Viabiliza recursos e materiais</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>articula_parcerias_externas</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Articula parcerias externas</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>apoia_projetos_de_estudantes</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Apoia projetos de estudantes</t>
         </is>
       </c>
     </row>
@@ -7644,12 +10492,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>reserva_tempo_para_planejamento_</t>
+          <t>participa_de_formacoes_sobre_o_t</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Reserva tempo para planejamento coletivo</t>
+          <t>Participa de formações sobre o tema</t>
         </is>
       </c>
     </row>
@@ -7661,12 +10509,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>inclui_a_ea_no_ppp_planejamento_</t>
+          <t>acompanha_e_valoriza_as_praticas</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Inclui a EA no PPP/planejamento anual</t>
+          <t>Acompanha e valoriza as práticas da equipe</t>
         </is>
       </c>
     </row>
@@ -7678,12 +10526,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>viabiliza_recursos_e_materiais</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Viabiliza recursos e materiais</t>
+          <t>Nenhum apoio sistemático</t>
         </is>
       </c>
     </row>
@@ -7695,97 +10543,97 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>articula_parcerias_externas</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Articula parcerias externas</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>apoia_projetos_de_estudantes</t>
+          <t>conselho_escolar</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Apoia projetos de estudantes</t>
+          <t>Conselho escolar</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>participa_de_formacoes_sobre_o_t</t>
+          <t>apm_caixa_escolar</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Participa de formações sobre o tema</t>
+          <t>APM / caixa escolar</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>acompanha_e_valoriza_as_praticas</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Acompanha e valoriza as práticas da equipe</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>conselho_de_classe</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Nenhum apoio sistemático</t>
+          <t>Conselho de classe</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>reuniao_pedagogica_planejamento_</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Reunião pedagógica/planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -7797,12 +10645,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>conselho_escolar</t>
+          <t>associacao_de_pais_e_mestres</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Conselho escolar</t>
+          <t>Associação de pais e mestres</t>
         </is>
       </c>
     </row>
@@ -7814,12 +10662,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>apm_caixa_escolar</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>APM / caixa escolar</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
@@ -7831,97 +10679,97 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>conselho_de_classe</t>
+          <t>livros_didaticos</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Conselho de classe</t>
+          <t>Livros didáticos</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>reuniao_pedagogica_planejamento_</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Reunião pedagógica/planejamento coletivo</t>
+          <t>Vídeos</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>associacao_de_pais_e_mestres</t>
+          <t>jogos</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Associação de pais e mestres</t>
+          <t>Jogos</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>kits_cientificos</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Kits científicos</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>materiais_produzidos_pela_escola</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Materiais produzidos pelo local</t>
         </is>
       </c>
     </row>
@@ -7933,12 +10781,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>livros_didaticos</t>
+          <t>recursos_digitais</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Livros didáticos</t>
+          <t>Recursos digitais</t>
         </is>
       </c>
     </row>
@@ -7950,172 +10798,172 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Vídeos</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>jogos</t>
+          <t>facil</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Jogos</t>
+          <t>Fácil</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>kits_cientificos</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Kits científicos</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>materiais_produzidos_pela_escola</t>
+          <t>dificil</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Materiais produzidos pelo local</t>
+          <t>Difícil</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>recursos_digitais</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Recursos digitais</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>espectadores</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Espectadores</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>colaboradores_pontuais</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Colaboradores pontuais</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>dificil</t>
+          <t>protagonistas_em_alguns_momentos</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Protagonistas em alguns momentos</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>protagonistas_continuos</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Protagonistas contínuos</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8132,153 +10980,153 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>espectadores</t>
+          <t>garantida_institucionalmente</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Espectadores</t>
+          <t>Garantida institucionalmente</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>colaboradores_pontuais</t>
+          <t>dependente_de_pessoas_especifica</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Colaboradores pontuais</t>
+          <t>Dependente de pessoas específicas</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>protagonistas_em_alguns_momentos</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Protagonistas em alguns momentos</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>protagonistas_continuos</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Protagonistas contínuos</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>garantida_institucionalmente</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Garantida institucionalmente</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>dependente_de_pessoas_especifica</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Dependente de pessoas específicas</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>funcionarios</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Funcionários(as)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -8290,12 +11138,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
@@ -8307,182 +11155,182 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>informativa</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Informativa (recebem informação)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>funcionarios</t>
+          <t>consultiva</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Funcionários(as)</t>
+          <t>Consultiva (são ouvidos)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>colaborativa</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Colaborativa (constroem junto)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Protagonista (decidem e conduzem)</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>informativa</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Informativa (recebem informação)</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>consultiva</t>
+          <t>assembleias</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Consultiva (são ouvidos)</t>
+          <t>Assembleias</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>colaborativa</t>
+          <t>projetos_protagonizados_por_estu</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Colaborativa (constroem junto)</t>
+          <t>Projetos protagonizados por estudantes</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>conselhos</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Protagonista (decidem e conduzem)</t>
+          <t>Conselhos</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
@@ -8494,267 +11342,267 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>assembleias</t>
+          <t>ausente</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Assembleias</t>
+          <t>Ausente</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>projetos_protagonizados_por_estu</t>
+          <t>esporadico</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Projetos protagonizados por estudantes</t>
+          <t>Esporádico</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>conselhos</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Conselhos</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>ativo_protagonista</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Ativo/protagonista</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ausente</t>
+          <t>horario_de_trabalho</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Horário de trabalho</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>esporadico</t>
+          <t>distancia</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Esporádico</t>
+          <t>Distância</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>comunicacao_inadequada</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Comunicação inadequada</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>ativo_protagonista</t>
+          <t>falta_de_convite_convocacao</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Ativo/protagonista</t>
+          <t>Falta de convite/convocação</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>horario_de_trabalho</t>
+          <t>sec_educacao</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Horário de trabalho</t>
+          <t>Secretaria de Educação</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>distancia</t>
+          <t>sec_meio_amb</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Distância</t>
+          <t>Secretaria de Meio Ambiente</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>comunicacao_inadequada</t>
+          <t>defesa_civil</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Comunicação inadequada</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>falta_de_convite_convocacao</t>
+          <t>sec_saude</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Falta de convite/convocação</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>assist_social</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Assistência Social</t>
         </is>
       </c>
     </row>
@@ -8766,12 +11614,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>sec_educacao</t>
+          <t>obras</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
+          <t>Obras</t>
         </is>
       </c>
     </row>
@@ -8783,12 +11631,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>sec_meio_amb</t>
+          <t>bombeiros</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
+          <t>Bombeiros</t>
         </is>
       </c>
     </row>
@@ -8800,12 +11648,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>defesa_civil</t>
+          <t>ubs</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>UBS</t>
         </is>
       </c>
     </row>
@@ -8817,12 +11665,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>sec_saude</t>
+          <t>vigilancia</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
+          <t>Vigilância</t>
         </is>
       </c>
     </row>
@@ -8834,12 +11682,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>assist_social</t>
+          <t>outro_publico</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Outro (poder público)</t>
         </is>
       </c>
     </row>
@@ -8851,12 +11699,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>obras</t>
+          <t>universidade</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>Universidade</t>
         </is>
       </c>
     </row>
@@ -8868,12 +11716,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>bombeiros</t>
+          <t>inst_federal</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
+          <t>Instituto Federal</t>
         </is>
       </c>
     </row>
@@ -8885,12 +11733,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ubs</t>
+          <t>escola_tecnica</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Escola técnica</t>
         </is>
       </c>
     </row>
@@ -8902,12 +11750,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>vigilancia</t>
+          <t>centro_pesquisa</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Vigilância</t>
+          <t>Centro de pesquisa</t>
         </is>
       </c>
     </row>
@@ -8919,12 +11767,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>outro_publico</t>
+          <t>museu</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
+          <t>Museu</t>
         </is>
       </c>
     </row>
@@ -8936,12 +11784,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>universidade</t>
+          <t>jardim_botanico</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Jardim botânico</t>
         </is>
       </c>
     </row>
@@ -8953,12 +11801,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>inst_federal</t>
+          <t>outro_educ_ciencia</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
+          <t>Outro (educação/ciência)</t>
         </is>
       </c>
     </row>
@@ -8970,12 +11818,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>escola_tecnica</t>
+          <t>assoc_moradores</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Escola técnica</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -8987,12 +11835,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>centro_pesquisa</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>ONG</t>
         </is>
       </c>
     </row>
@@ -9004,12 +11852,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>museu</t>
+          <t>cooperativa</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Museu</t>
+          <t>Cooperativa</t>
         </is>
       </c>
     </row>
@@ -9021,12 +11869,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>jardim_botanico</t>
+          <t>catadores</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Catadores</t>
         </is>
       </c>
     </row>
@@ -9038,12 +11886,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>outro_educ_ciencia</t>
+          <t>mov_sociais</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>Movimentos sociais</t>
         </is>
       </c>
     </row>
@@ -9055,12 +11903,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>assoc_moradores</t>
+          <t>coletivos</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Coletivos</t>
         </is>
       </c>
     </row>
@@ -9072,12 +11920,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>grupos_culturais</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Grupos culturais</t>
         </is>
       </c>
     </row>
@@ -9089,12 +11937,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>cooperativa</t>
+          <t>org_comunit_relig</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Organizações comunitárias/religiosas</t>
         </is>
       </c>
     </row>
@@ -9106,12 +11954,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>catadores</t>
+          <t>outro_soc_civil</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>Outro (sociedade civil)</t>
         </is>
       </c>
     </row>
@@ -9123,12 +11971,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>mov_sociais</t>
+          <t>povos_indigenas</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
+          <t>Povos indígenas</t>
         </is>
       </c>
     </row>
@@ -9140,12 +11988,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>coletivos</t>
+          <t>quilombolas</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Coletivos</t>
+          <t>Quilombolas</t>
         </is>
       </c>
     </row>
@@ -9157,12 +12005,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>grupos_culturais</t>
+          <t>agric_familiares</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
+          <t>Agricultores familiares</t>
         </is>
       </c>
     </row>
@@ -9174,12 +12022,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>org_comunit_relig</t>
+          <t>pescadores</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Pescadores</t>
         </is>
       </c>
     </row>
@@ -9191,12 +12039,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>outro_soc_civil</t>
+          <t>com_tradicionais</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
+          <t>Comunidades tradicionais</t>
         </is>
       </c>
     </row>
@@ -9208,12 +12056,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>povos_indigenas</t>
+          <t>liderancas</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
+          <t>Lideranças</t>
         </is>
       </c>
     </row>
@@ -9225,12 +12073,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>quilombolas</t>
+          <t>detentores_saberes</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Quilombolas</t>
+          <t>Detentores de conhecimentos locais</t>
         </is>
       </c>
     </row>
@@ -9242,182 +12090,182 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>agric_familiares</t>
+          <t>outro_comunidades</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Agricultores familiares</t>
+          <t>Outro (comunidades e conhecimentos)</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>pescadores</t>
+          <t>nao_existe</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Pescadores</t>
+          <t>Não existe no território</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>com_tradicionais</t>
+          <t>nao_sei</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
+          <t>Não sei se existe</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>liderancas</t>
+          <t>sem_contato</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Existe, mas nunca houve contato</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>detentores_saberes</t>
+          <t>contato_pontual</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Detentores de conhecimentos locais</t>
+          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>outro_comunidades</t>
+          <t>parceria</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Outro (comunidades e conhecimentos)</t>
+          <t>Parceria — já colaboram em ações combinadas</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>nivel_rel</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>nao_existe</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Não existe relação — não é parceiro(a)</t>
+          <t>Articulação permanente — parceria contínua e estruturada</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>nivel_rel</t>
+          <t>contrib</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>sabe_existe</t>
+          <t>recursos</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Sabe que existe, mas nunca houve contato — não é parceiro(a)</t>
+          <t>Recursos</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>nivel_rel</t>
+          <t>contrib</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>contato_pontual</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Já houve contato pontual, sem combinação formal — ainda não é parceiro(a)</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>nivel_rel</t>
+          <t>contrib</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>parceria</t>
+          <t>articulacao_institucional</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Parceria — já colaboram em ações combinadas</t>
+          <t>Articulação institucional</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>nivel_rel</t>
+          <t>contrib</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>apoio_tecnico</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Articulação permanente — parceria contínua e estruturada</t>
+          <t>Apoio técnico</t>
         </is>
       </c>
     </row>
@@ -9429,12 +12277,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>recursos</t>
+          <t>mobilizacao_comunitaria</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Recursos</t>
+          <t>Mobilização comunitária</t>
         </is>
       </c>
     </row>
@@ -9446,12 +12294,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>conhecimentos_tradicionais_locai</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Conhecimentos tradicionais/locais</t>
         </is>
       </c>
     </row>
@@ -9463,80 +12311,80 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>articulacao_institucional</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Articulação institucional</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>apoio_tecnico</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Apoio técnico</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>mobilizacao_comunitaria</t>
+          <t>comunicados_impressos</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Mobilização comunitária</t>
+          <t>Comunicados impressos</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>conhecimentos_tradicionais_locai</t>
+          <t>reunioes</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Conhecimentos tradicionais/locais</t>
+          <t>Reuniões</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
@@ -9548,12 +12396,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>alto_falante_radio_local</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Alto-falante/rádio local</t>
         </is>
       </c>
     </row>
@@ -9565,148 +12413,148 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>comunicados_impressos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Comunicados impressos</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>reunioes</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>alto_falante_radio_local</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Alto-falante/rádio local</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>falta_de_contato</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Falta de contato</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>burocracia</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Burocracia</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>desconfianca_historico_de_relaca</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Desconfiança/histórico de relação</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
@@ -9718,78 +12566,10 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>falta_de_contato</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
-        <is>
-          <t>Falta de contato</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>barr_artic</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>burocracia</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Burocracia</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>barr_artic</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>desconfianca_historico_de_relaca</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Desconfiança/histórico de relação</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>barr_artic</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>falta_de_tempo</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Falta de tempo</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>barr_artic</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>outro</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
         <is>
           <t>Outra</t>
         </is>

--- a/kobo/gestores_semana2_diagnostico.xlsx
+++ b/kobo/gestores_semana2_diagnostico.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J276"/>
+  <dimension ref="A1:J202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4854,31 +4854,23 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_multiple cat_ator</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>net_atual</t>
+          <t>q3_14</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Q3.14. Contribuições atuais — o que cada ator parceiro(a) já oferece ao local?</t>
+          <t>Q3.14. Quais atores são prioritários para fortalecer a relação? (NET_PRIORITY_ACTORS)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>(${net_rel_01} = 'parceria' or ${net_rel_01} = 'articulacao') or (${net_rel_02} = 'parceria' or ${net_rel_02} = 'articulacao') or (${net_rel_03} = 'parceria' or ${net_rel_03} = 'articulacao') or (${net_rel_04} = 'parceria' or ${net_rel_04} = 'articulacao') or (${net_rel_05} = 'parceria' or ${net_rel_05} = 'articulacao') or (${net_rel_06} = 'parceria' or ${net_rel_06} = 'articulacao') or (${net_rel_07} = 'parceria' or ${net_rel_07} = 'articulacao') or (${net_rel_08} = 'parceria' or ${net_rel_08} = 'articulacao') or (${net_rel_09} = 'parceria' or ${net_rel_09} = 'articulacao') or (${net_rel_10} = 'parceria' or ${net_rel_10} = 'articulacao') or (${net_rel_11} = 'parceria' or ${net_rel_11} = 'articulacao') or (${net_rel_12} = 'parceria' or ${net_rel_12} = 'articulacao') or (${net_rel_13} = 'parceria' or ${net_rel_13} = 'articulacao') or (${net_rel_14} = 'parceria' or ${net_rel_14} = 'articulacao') or (${net_rel_15} = 'parceria' or ${net_rel_15} = 'articulacao') or (${net_rel_16} = 'parceria' or ${net_rel_16} = 'articulacao') or (${net_rel_17} = 'parceria' or ${net_rel_17} = 'articulacao') or (${net_rel_18} = 'parceria' or ${net_rel_18} = 'articulacao') or (${net_rel_19} = 'parceria' or ${net_rel_19} = 'articulacao') or (${net_rel_20} = 'parceria' or ${net_rel_20} = 'articulacao') or (${net_rel_21} = 'parceria' or ${net_rel_21} = 'articulacao') or (${net_rel_22} = 'parceria' or ${net_rel_22} = 'articulacao') or (${net_rel_23} = 'parceria' or ${net_rel_23} = 'articulacao') or (${net_rel_24} = 'parceria' or ${net_rel_24} = 'articulacao') or (${net_rel_25} = 'parceria' or ${net_rel_25} = 'articulacao') or (${net_rel_26} = 'parceria' or ${net_rel_26} = 'articulacao') or (${net_rel_27} = 'parceria' or ${net_rel_27} = 'articulacao') or (${net_rel_28} = 'parceria' or ${net_rel_28} = 'articulacao') or (${net_rel_29} = 'parceria' or ${net_rel_29} = 'articulacao') or (${net_rel_30} = 'parceria' or ${net_rel_30} = 'articulacao') or (${net_rel_31} = 'parceria' or ${net_rel_31} = 'articulacao') or (${net_rel_32} = 'parceria' or ${net_rel_32} = 'articulacao') or (${net_rel_33} = 'parceria' or ${net_rel_33} = 'articulacao') or (${net_rel_34} = 'parceria' or ${net_rel_34} = 'articulacao')</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>table-list</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
@@ -4886,27 +4878,27 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>net_atual_01</t>
+          <t>q3_15</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
+          <t>Q3.15. Cite o nome do ator mais relevante para o local hoje (ex.: UBS Vila Nova)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>${net_rel_01} = 'parceria' or ${net_rel_01} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
@@ -4914,26 +4906,26 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>net_atual_02</t>
+          <t>q3_16</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
+          <t>Q3.16. O local sabe a quem contatar em uma emergência climática?</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>${net_rel_02} = 'parceria' or ${net_rel_02} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
@@ -4942,27 +4934,31 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>net_atual_03</t>
+          <t>q3_17</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Q3.17. Quais são esses contatos?</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>${net_rel_03} = 'parceria' or ${net_rel_03} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr"/>
+          <t>${q3_16}='sim'</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
@@ -4970,26 +4966,26 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>net_atual_04</t>
+          <t>q3_18</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
+          <t>Q3.18. Existe um procedimento de emergência definido para eventos climáticos?</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>${net_rel_04} = 'parceria' or ${net_rel_04} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
@@ -4998,24 +4994,24 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>net_atual_05</t>
+          <t>q3_19</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Q3.19. Esse procedimento está documentado/formalizado?</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>${net_rel_05} = 'parceria' or ${net_rel_05} = 'articulacao'</t>
+          <t>${q3_18}='sim'</t>
         </is>
       </c>
       <c r="G173" t="inlineStr"/>
@@ -5026,27 +5022,27 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>net_atual_06</t>
+          <t>q3_20</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>Q3.20. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>${net_rel_06} = 'parceria' or ${net_rel_06} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
@@ -5054,26 +5050,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_multiple canais</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>net_atual_07</t>
+          <t>q3_21</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
+          <t>Q3.21. Canais de comunicação do local com a comunidade</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>${net_rel_07} = 'parceria' or ${net_rel_07} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -5082,24 +5074,24 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>net_atual_08</t>
+          <t>q3_21_outro</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>${net_rel_08} = 'parceria' or ${net_rel_08} = 'articulacao'</t>
+          <t>selected(${q3_21}, 'outro')</t>
         </is>
       </c>
       <c r="G176" t="inlineStr"/>
@@ -5110,26 +5102,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one suficiente</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>net_atual_09</t>
+          <t>q3_22</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Vigilância</t>
+          <t>Q3.22. Esses canais seriam suficientes numa emergência?</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>${net_rel_09} = 'parceria' or ${net_rel_09} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
@@ -5138,27 +5126,27 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>net_atual_10</t>
+          <t>q3_23</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
+          <t>Q3.23. Algum grupo fica de fora desses canais de comunicação?</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>${net_rel_10} = 'parceria' or ${net_rel_10} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
@@ -5166,27 +5154,31 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>net_atual_11</t>
+          <t>q3_24</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Universidade</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
+          <t>Q3.24. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>${net_rel_11} = 'parceria' or ${net_rel_11} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
@@ -5194,27 +5186,27 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>net_atual_12</t>
+          <t>q3_25</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
+          <t>Q3.25. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>${net_rel_12} = 'parceria' or ${net_rel_12} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
@@ -5222,26 +5214,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_multiple barr_artic</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>net_atual_13</t>
+          <t>q3_26</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Local técnica</t>
+          <t>Q3.26. Barreiras para articular com atores do território</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>${net_rel_13} = 'parceria' or ${net_rel_13} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
@@ -5250,24 +5238,24 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>net_atual_14</t>
+          <t>q3_26_outro</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>${net_rel_14} = 'parceria' or ${net_rel_14} = 'articulacao'</t>
+          <t>selected(${q3_26}, 'outro')</t>
         </is>
       </c>
       <c r="G182" t="inlineStr"/>
@@ -5278,27 +5266,27 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>net_atual_15</t>
+          <t>q3_27</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Museu</t>
+          <t>Q3.27. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>${net_rel_15} = 'parceria' or ${net_rel_15} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
@@ -5306,27 +5294,31 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>net_atual_16</t>
+          <t>q3_28</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Q3.28. Quem participou desse caso?</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>${net_rel_16} = 'parceria' or ${net_rel_16} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr"/>
+          <t>${q3_27} != ''</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
@@ -5334,27 +5326,31 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>net_atual_17</t>
+          <t>q3_29</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>Q3.29. O que funcionou bem?</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>${net_rel_17} = 'parceria' or ${net_rel_17} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr"/>
+          <t>${q3_27} != ''</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
@@ -5362,27 +5358,31 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>net_atual_18</t>
+          <t>q3_30</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Q3.30. Quais foram as dificuldades?</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>${net_rel_18} = 'parceria' or ${net_rel_18} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr"/>
+          <t>${q3_27} != ''</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
@@ -5390,27 +5390,31 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>net_atual_19</t>
+          <t>q3_31</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Q3.31. O que essa experiência ensinou?</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>${net_rel_19} = 'parceria' or ${net_rel_19} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr"/>
+          <t>${q3_27} != ''</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
@@ -5418,27 +5422,27 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>net_atual_20</t>
+          <t>q3_32</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Q3.32. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>${net_rel_20} = 'parceria' or ${net_rel_20} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
@@ -5446,27 +5450,31 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>net_atual_21</t>
+          <t>q3_33</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>Q3.33. Por quê?</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>${net_rel_21} = 'parceria' or ${net_rel_21} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr"/>
+          <t>${q3_32} != ''</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
@@ -5474,26 +5482,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>net_atual_22</t>
+          <t>evid_e3</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
+          <t>Evidências — Evidências sobre participação e redes</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>${net_rel_22} = 'parceria' or ${net_rel_22} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
@@ -5502,26 +5506,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>net_atual_23</t>
+          <t>evid_e3_nota</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Coletivos</t>
+          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>${net_rel_23} = 'parceria' or ${net_rel_23} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
@@ -5530,26 +5530,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one tipo_evid</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>net_atual_24</t>
+          <t>evid_e3_tipo</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
+          <t>Tipo de evidência</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>${net_rel_24} = 'parceria' or ${net_rel_24} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
@@ -5558,24 +5554,24 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>net_atual_25</t>
+          <t>evid_e3_tipo_outro</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>${net_rel_25} = 'parceria' or ${net_rel_25} = 'articulacao'</t>
+          <t>${evid_e3_tipo}='outro'</t>
         </is>
       </c>
       <c r="G193" t="inlineStr"/>
@@ -5586,27 +5582,27 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>net_atual_26</t>
+          <t>evid_e3_desc</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
+          <t>Descreva a evidência</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>${net_rel_26} = 'parceria' or ${net_rel_26} = 'articulacao'</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
@@ -5614,26 +5610,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>file</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>net_atual_27</t>
+          <t>evid_e3_anexo</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
+          <t>Anexo (foto/documento) — opcional</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>${net_rel_27} = 'parceria' or ${net_rel_27} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
@@ -5642,26 +5634,14 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>net_atual_28</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Quilombolas</t>
-        </is>
-      </c>
+          <t>end_repeat</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>${net_rel_28} = 'parceria' or ${net_rel_28} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
@@ -5670,26 +5650,14 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>net_atual_29</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Agricultores familiares</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>${net_rel_29} = 'parceria' or ${net_rel_29} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
@@ -5698,26 +5666,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>net_atual_30</t>
+          <t>confirmacao</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Pescadores</t>
+          <t>Confirmação final</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>${net_rel_30} = 'parceria' or ${net_rel_30} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
@@ -5726,26 +5690,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>net_atual_31</t>
+          <t>confirmacao_msg</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
+          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>${net_rel_31} = 'parceria' or ${net_rel_31} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
@@ -5754,26 +5714,26 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one confirmo</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>net_atual_32</t>
+          <t>confirmacao_envio</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Revisei minhas respostas e confirmo o envio.</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>${net_rel_32} = 'parceria' or ${net_rel_32} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
@@ -5782,26 +5742,14 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>net_atual_33</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Detentores de conhecimentos locais</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>${net_rel_33} = 'parceria' or ${net_rel_33} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
@@ -5810,2030 +5758,18 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>net_atual_34</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Outro (comunidades e conhecimentos)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>${net_rel_34} = 'parceria' or ${net_rel_34} = 'articulacao'</t>
-        </is>
-      </c>
+      <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr"/>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>net_atual_outro</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Especifique (Outro) — contribuições atuais</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>selected(${net_atual_01}, 'outro') or selected(${net_atual_02}, 'outro') or selected(${net_atual_03}, 'outro') or selected(${net_atual_04}, 'outro') or selected(${net_atual_05}, 'outro') or selected(${net_atual_06}, 'outro') or selected(${net_atual_07}, 'outro') or selected(${net_atual_08}, 'outro') or selected(${net_atual_09}, 'outro') or selected(${net_atual_10}, 'outro') or selected(${net_atual_11}, 'outro') or selected(${net_atual_12}, 'outro') or selected(${net_atual_13}, 'outro') or selected(${net_atual_14}, 'outro') or selected(${net_atual_15}, 'outro') or selected(${net_atual_16}, 'outro') or selected(${net_atual_17}, 'outro') or selected(${net_atual_18}, 'outro') or selected(${net_atual_19}, 'outro') or selected(${net_atual_20}, 'outro') or selected(${net_atual_21}, 'outro') or selected(${net_atual_22}, 'outro') or selected(${net_atual_23}, 'outro') or selected(${net_atual_24}, 'outro') or selected(${net_atual_25}, 'outro') or selected(${net_atual_26}, 'outro') or selected(${net_atual_27}, 'outro') or selected(${net_atual_28}, 'outro') or selected(${net_atual_29}, 'outro') or selected(${net_atual_30}, 'outro') or selected(${net_atual_31}, 'outro') or selected(${net_atual_32}, 'outro') or selected(${net_atual_33}, 'outro') or selected(${net_atual_34}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>net_pot</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Q3.15. Contribuições potenciais — o que cada ator que existe no território poderia oferecer?</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>(${net_rel_01} != '' and ${net_rel_01} != 'nao_existe' and ${net_rel_01} != 'nao_sei') or (${net_rel_02} != '' and ${net_rel_02} != 'nao_existe' and ${net_rel_02} != 'nao_sei') or (${net_rel_03} != '' and ${net_rel_03} != 'nao_existe' and ${net_rel_03} != 'nao_sei') or (${net_rel_04} != '' and ${net_rel_04} != 'nao_existe' and ${net_rel_04} != 'nao_sei') or (${net_rel_05} != '' and ${net_rel_05} != 'nao_existe' and ${net_rel_05} != 'nao_sei') or (${net_rel_06} != '' and ${net_rel_06} != 'nao_existe' and ${net_rel_06} != 'nao_sei') or (${net_rel_07} != '' and ${net_rel_07} != 'nao_existe' and ${net_rel_07} != 'nao_sei') or (${net_rel_08} != '' and ${net_rel_08} != 'nao_existe' and ${net_rel_08} != 'nao_sei') or (${net_rel_09} != '' and ${net_rel_09} != 'nao_existe' and ${net_rel_09} != 'nao_sei') or (${net_rel_10} != '' and ${net_rel_10} != 'nao_existe' and ${net_rel_10} != 'nao_sei') or (${net_rel_11} != '' and ${net_rel_11} != 'nao_existe' and ${net_rel_11} != 'nao_sei') or (${net_rel_12} != '' and ${net_rel_12} != 'nao_existe' and ${net_rel_12} != 'nao_sei') or (${net_rel_13} != '' and ${net_rel_13} != 'nao_existe' and ${net_rel_13} != 'nao_sei') or (${net_rel_14} != '' and ${net_rel_14} != 'nao_existe' and ${net_rel_14} != 'nao_sei') or (${net_rel_15} != '' and ${net_rel_15} != 'nao_existe' and ${net_rel_15} != 'nao_sei') or (${net_rel_16} != '' and ${net_rel_16} != 'nao_existe' and ${net_rel_16} != 'nao_sei') or (${net_rel_17} != '' and ${net_rel_17} != 'nao_existe' and ${net_rel_17} != 'nao_sei') or (${net_rel_18} != '' and ${net_rel_18} != 'nao_existe' and ${net_rel_18} != 'nao_sei') or (${net_rel_19} != '' and ${net_rel_19} != 'nao_existe' and ${net_rel_19} != 'nao_sei') or (${net_rel_20} != '' and ${net_rel_20} != 'nao_existe' and ${net_rel_20} != 'nao_sei') or (${net_rel_21} != '' and ${net_rel_21} != 'nao_existe' and ${net_rel_21} != 'nao_sei') or (${net_rel_22} != '' and ${net_rel_22} != 'nao_existe' and ${net_rel_22} != 'nao_sei') or (${net_rel_23} != '' and ${net_rel_23} != 'nao_existe' and ${net_rel_23} != 'nao_sei') or (${net_rel_24} != '' and ${net_rel_24} != 'nao_existe' and ${net_rel_24} != 'nao_sei') or (${net_rel_25} != '' and ${net_rel_25} != 'nao_existe' and ${net_rel_25} != 'nao_sei') or (${net_rel_26} != '' and ${net_rel_26} != 'nao_existe' and ${net_rel_26} != 'nao_sei') or (${net_rel_27} != '' and ${net_rel_27} != 'nao_existe' and ${net_rel_27} != 'nao_sei') or (${net_rel_28} != '' and ${net_rel_28} != 'nao_existe' and ${net_rel_28} != 'nao_sei') or (${net_rel_29} != '' and ${net_rel_29} != 'nao_existe' and ${net_rel_29} != 'nao_sei') or (${net_rel_30} != '' and ${net_rel_30} != 'nao_existe' and ${net_rel_30} != 'nao_sei') or (${net_rel_31} != '' and ${net_rel_31} != 'nao_existe' and ${net_rel_31} != 'nao_sei') or (${net_rel_32} != '' and ${net_rel_32} != 'nao_existe' and ${net_rel_32} != 'nao_sei') or (${net_rel_33} != '' and ${net_rel_33} != 'nao_existe' and ${net_rel_33} != 'nao_sei') or (${net_rel_34} != '' and ${net_rel_34} != 'nao_existe' and ${net_rel_34} != 'nao_sei')</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>table-list</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>net_pot_01</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Secretaria de Educação</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>${net_rel_01} != '' and ${net_rel_01} != 'nao_existe' and ${net_rel_01} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>net_pot_02</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Secretaria de Meio Ambiente</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>${net_rel_02} != '' and ${net_rel_02} != 'nao_existe' and ${net_rel_02} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>net_pot_03</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Defesa Civil</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>${net_rel_03} != '' and ${net_rel_03} != 'nao_existe' and ${net_rel_03} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>net_pot_04</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Secretaria de Saúde</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>${net_rel_04} != '' and ${net_rel_04} != 'nao_existe' and ${net_rel_04} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>net_pot_05</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Assistência Social</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>${net_rel_05} != '' and ${net_rel_05} != 'nao_existe' and ${net_rel_05} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>net_pot_06</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Obras</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>${net_rel_06} != '' and ${net_rel_06} != 'nao_existe' and ${net_rel_06} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>net_pot_07</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Bombeiros</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>${net_rel_07} != '' and ${net_rel_07} != 'nao_existe' and ${net_rel_07} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>net_pot_08</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>UBS</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>${net_rel_08} != '' and ${net_rel_08} != 'nao_existe' and ${net_rel_08} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>net_pot_09</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Vigilância</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>${net_rel_09} != '' and ${net_rel_09} != 'nao_existe' and ${net_rel_09} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>net_pot_10</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Outro (poder público)</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>${net_rel_10} != '' and ${net_rel_10} != 'nao_existe' and ${net_rel_10} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>net_pot_11</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Universidade</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>${net_rel_11} != '' and ${net_rel_11} != 'nao_existe' and ${net_rel_11} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>net_pot_12</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Instituto Federal</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>${net_rel_12} != '' and ${net_rel_12} != 'nao_existe' and ${net_rel_12} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>net_pot_13</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Local técnica</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>${net_rel_13} != '' and ${net_rel_13} != 'nao_existe' and ${net_rel_13} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>net_pot_14</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Centro de pesquisa</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>${net_rel_14} != '' and ${net_rel_14} != 'nao_existe' and ${net_rel_14} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>net_pot_15</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Museu</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>${net_rel_15} != '' and ${net_rel_15} != 'nao_existe' and ${net_rel_15} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>net_pot_16</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Jardim botânico</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>${net_rel_16} != '' and ${net_rel_16} != 'nao_existe' and ${net_rel_16} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>net_pot_17</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Outro (educação/ciência)</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>${net_rel_17} != '' and ${net_rel_17} != 'nao_existe' and ${net_rel_17} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>net_pot_18</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Associação de moradores</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>${net_rel_18} != '' and ${net_rel_18} != 'nao_existe' and ${net_rel_18} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>net_pot_19</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>ONG</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>${net_rel_19} != '' and ${net_rel_19} != 'nao_existe' and ${net_rel_19} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>net_pot_20</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Cooperativa</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>${net_rel_20} != '' and ${net_rel_20} != 'nao_existe' and ${net_rel_20} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>net_pot_21</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Catadores</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>${net_rel_21} != '' and ${net_rel_21} != 'nao_existe' and ${net_rel_21} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>net_pot_22</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Movimentos sociais</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>${net_rel_22} != '' and ${net_rel_22} != 'nao_existe' and ${net_rel_22} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>net_pot_23</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Coletivos</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>${net_rel_23} != '' and ${net_rel_23} != 'nao_existe' and ${net_rel_23} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>net_pot_24</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Grupos culturais</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>${net_rel_24} != '' and ${net_rel_24} != 'nao_existe' and ${net_rel_24} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>net_pot_25</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Organizações comunitárias/religiosas</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>${net_rel_25} != '' and ${net_rel_25} != 'nao_existe' and ${net_rel_25} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>net_pot_26</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Outro (sociedade civil)</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>${net_rel_26} != '' and ${net_rel_26} != 'nao_existe' and ${net_rel_26} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>net_pot_27</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Povos indígenas</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>${net_rel_27} != '' and ${net_rel_27} != 'nao_existe' and ${net_rel_27} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>net_pot_28</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Quilombolas</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>${net_rel_28} != '' and ${net_rel_28} != 'nao_existe' and ${net_rel_28} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>net_pot_29</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Agricultores familiares</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>${net_rel_29} != '' and ${net_rel_29} != 'nao_existe' and ${net_rel_29} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>net_pot_30</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Pescadores</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>${net_rel_30} != '' and ${net_rel_30} != 'nao_existe' and ${net_rel_30} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>net_pot_31</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Comunidades tradicionais</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>${net_rel_31} != '' and ${net_rel_31} != 'nao_existe' and ${net_rel_31} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>net_pot_32</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Lideranças</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>${net_rel_32} != '' and ${net_rel_32} != 'nao_existe' and ${net_rel_32} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>net_pot_33</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Detentores de conhecimentos locais</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>${net_rel_33} != '' and ${net_rel_33} != 'nao_existe' and ${net_rel_33} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>net_pot_34</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Outro (comunidades e conhecimentos)</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>${net_rel_34} != '' and ${net_rel_34} != 'nao_existe' and ${net_rel_34} != 'nao_sei'</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr"/>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>net_pot_outro</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Especifique (Outro) — contribuições potenciais</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>selected(${net_pot_01}, 'outro') or selected(${net_pot_02}, 'outro') or selected(${net_pot_03}, 'outro') or selected(${net_pot_04}, 'outro') or selected(${net_pot_05}, 'outro') or selected(${net_pot_06}, 'outro') or selected(${net_pot_07}, 'outro') or selected(${net_pot_08}, 'outro') or selected(${net_pot_09}, 'outro') or selected(${net_pot_10}, 'outro') or selected(${net_pot_11}, 'outro') or selected(${net_pot_12}, 'outro') or selected(${net_pot_13}, 'outro') or selected(${net_pot_14}, 'outro') or selected(${net_pot_15}, 'outro') or selected(${net_pot_16}, 'outro') or selected(${net_pot_17}, 'outro') or selected(${net_pot_18}, 'outro') or selected(${net_pot_19}, 'outro') or selected(${net_pot_20}, 'outro') or selected(${net_pot_21}, 'outro') or selected(${net_pot_22}, 'outro') or selected(${net_pot_23}, 'outro') or selected(${net_pot_24}, 'outro') or selected(${net_pot_25}, 'outro') or selected(${net_pot_26}, 'outro') or selected(${net_pot_27}, 'outro') or selected(${net_pot_28}, 'outro') or selected(${net_pot_29}, 'outro') or selected(${net_pot_30}, 'outro') or selected(${net_pot_31}, 'outro') or selected(${net_pot_32}, 'outro') or selected(${net_pot_33}, 'outro') or selected(${net_pot_34}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>select_multiple cat_ator</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>q3_16</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Q3.16. Quais atores são prioritários para fortalecer a relação? (NET_PRIORITY_ACTORS)</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>q3_17</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Q3.17. Cite o nome do ator mais relevante para o local hoje (ex.: UBS Vila Nova)</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>select_one sim_nao_ns</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>q3_18</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Q3.18. O local sabe a quem contatar em uma emergência climática?</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>q3_19</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Q3.19. Quais são esses contatos?</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>${q3_18}='sim'</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>select_one sim_nao_ns</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>q3_20</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Q3.20. Existe um procedimento de emergência definido para eventos climáticos?</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>select_one sim_nao_ns</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>q3_21</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Q3.21. Esse procedimento está documentado/formalizado?</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>${q3_20}='sim'</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>q3_22</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Q3.22. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>select_multiple canais</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>q3_23</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Q3.23. Canais de comunicação do local com a comunidade</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>q3_23_outro</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>selected(${q3_23}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>select_one suficiente</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>q3_24</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Q3.24. Esses canais seriam suficientes numa emergência?</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>q3_25</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Q3.25. Algum grupo fica de fora desses canais de comunicação?</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>q3_26</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Q3.26. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>q3_27</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Q3.27. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr"/>
-      <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>select_multiple barr_artic</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>q3_28</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Q3.28. Barreiras para articular com atores do território</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>q3_28_outro</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>selected(${q3_28}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr"/>
-      <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>q3_29</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Q3.29. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>q3_30</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Q3.30. Quem participou desse caso?</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>${q3_29} != ''</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>q3_31</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Q3.31. O que funcionou bem?</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>${q3_29} != ''</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>q3_32</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Q3.32. Quais foram as dificuldades?</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>${q3_29} != ''</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>q3_33</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Q3.33. O que essa experiência ensinou?</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>${q3_29} != ''</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>q3_34</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Q3.34. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr"/>
-      <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>q3_35</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Q3.35. Por quê?</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>${q3_34} != ''</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>begin_repeat</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>evid_e3</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Evidências — Evidências sobre participação e redes</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>evid_e3_nota</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
-      <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>select_one tipo_evid</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>evid_e3_tipo</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Tipo de evidência</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>evid_e3_tipo_outro</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>${evid_e3_tipo}='outro'</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr"/>
-      <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>evid_e3_desc</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Descreva a evidência</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>evid_e3_anexo</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Anexo (foto/documento) — opcional</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr"/>
-      <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
-      <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr"/>
-      <c r="C270" t="inlineStr"/>
-      <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
-      <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr"/>
-      <c r="C271" t="inlineStr"/>
-      <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>confirmacao</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Confirmação final</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>confirmacao_msg</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>select_one confirmo</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>confirmacao_envio</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Revisei minhas respostas e confirmo o envio.</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr"/>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr"/>
-      <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr"/>
-      <c r="C276" t="inlineStr"/>
-      <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr"/>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7846,7 +5782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C278"/>
+  <dimension ref="A1:C271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12204,372 +10140,253 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>recursos</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Recursos</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>comunicados_impressos</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Comunicados impressos</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>articulacao_institucional</t>
+          <t>reunioes</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Articulação institucional</t>
+          <t>Reuniões</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>apoio_tecnico</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Apoio técnico</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>mobilizacao_comunitaria</t>
+          <t>alto_falante_radio_local</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Mobilização comunitária</t>
+          <t>Alto-falante/rádio local</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>conhecimentos_tradicionais_locai</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Conhecimentos tradicionais/locais</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>comunicados_impressos</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Comunicados impressos</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>reunioes</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>falta_de_contato</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Falta de contato</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>alto_falante_radio_local</t>
+          <t>burocracia</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Alto-falante/rádio local</t>
+          <t>Burocracia</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>desconfianca_historico_de_relaca</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Desconfiança/histórico de relação</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
-        <is>
-          <t>Parcialmente</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>suficiente</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>nao</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>suficiente</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>nao_sabe</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Não sabe</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>barr_artic</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>falta_de_contato</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Falta de contato</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>barr_artic</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>burocracia</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Burocracia</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>barr_artic</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>desconfianca_historico_de_relaca</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Desconfiança/histórico de relação</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>barr_artic</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>falta_de_tempo</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Falta de tempo</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>barr_artic</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>outro</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
         <is>
           <t>Outra</t>
         </is>

--- a/kobo/gestores_semana2_diagnostico.xlsx
+++ b/kobo/gestores_semana2_diagnostico.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J202"/>
+  <dimension ref="A1:J200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Q2.7. Como ocorre a articulação entre áreas/disciplinas?</t>
+          <t>Q2.7. Como ocorre a articulação da educação ambiental entre áreas/disciplinas?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Q2.18. Que problema territorial foi abordado?</t>
+          <t>Q2.18. Qual problema territorial foi abordado?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Q2.20. O que essa atividade mudou ou gerou?</t>
+          <t>Q2.20. Quais foram os resultados dessa atividade (ex. O que essa atividade mudou ou gerou?)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Q2.24. Quais métodos/estratégias o local já utilizou em práticas de Educação Ambiental?</t>
+          <t>Q2.24. Quais métodos/estratégias a escola já utilizou em práticas de Educação Ambiental?</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Q2.26. Frequência de uso do território como espaço pedagógico</t>
+          <t>Q2.26. Frequência de uso pedagógico dos espaços do entorno da escola, como aulas de campo, visitas e trilhas e outras atividades educativas fora da sala de aula.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2254,23 +2254,31 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>q2_28</t>
+          <t>q2_27_quais</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Q2.28. Houve formação recente em Educação Ambiental?</t>
+          <t>Quais problemas locais/territoriais são abordados?</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>${q2_27}='sim'</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
@@ -2278,26 +2286,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>q2_29</t>
+          <t>q2_28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Q2.29. Quem ofereceu a formação?</t>
+          <t>Q2.28. Houve formação recente em Educação Ambiental?</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>${q2_28}='sim'</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -2311,12 +2315,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>q2_30</t>
+          <t>q2_29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Q2.30. Quais temas foram abordados?</t>
+          <t>Q2.29. Quem ofereceu a formação?</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -2326,11 +2330,7 @@
           <t>${q2_28}='sim'</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
@@ -2338,17 +2338,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>select_one impacto_form</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>q2_31</t>
+          <t>q2_30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Q2.31. Qual o impacto dessa formação na prática?</t>
+          <t>Q2.30. Quais temas foram abordados?</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -2358,7 +2358,11 @@
           <t>${q2_28}='sim'</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
@@ -2366,17 +2370,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one impacto_form</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>q2_32</t>
+          <t>q2_31</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Q2.32. Dê um exemplo desse impacto</t>
+          <t>Q2.31. Qual o impacto dessa formação na prática?</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2386,11 +2390,7 @@
           <t>${q2_28}='sim'</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
@@ -2398,29 +2398,29 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>select_one confianca</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>q2_33</t>
+          <t>q2_32</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Q2.33. Quão confiante você se sente, como gestor(a), para liderar e apoiar a Educação Ambiental neste local hoje?</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Escala de 1 (nada confiante) a 5 (muito confiante).</t>
-        </is>
-      </c>
+          <t>Q2.32. Dê um exemplo desse impacto</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>${q2_28}='sim'</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>horizontal-compact</t>
+          <t>multiline</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -2430,23 +2430,31 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>select_multiple apoio</t>
+          <t>select_one confianca</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>q2_34</t>
+          <t>q2_33</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Q2.34. Que tipo de apoio faria diferença?</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Q2.33. Quão confiante você se sente, como gestor(a), para liderar e apoiar a Educação Ambiental neste local hoje?</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Escala de 1 (nada confiante) a 5 (muito confiante).</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>horizontal-compact</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
@@ -2454,26 +2462,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple apoio</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>q2_34_outro</t>
+          <t>q2_34</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q2.34. Que tipo de apoio faria diferença para integração da Educação Ambiental no território escolar?</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>selected(${q2_34}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -2482,27 +2486,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>t2_35</t>
+          <t>q2_34_outro</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Q2.35. Intensidade de cada barreira percebida</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>table-list</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>selected(${q2_34}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
@@ -2510,23 +2514,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>select_one intensidade</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>q2_35_01</t>
+          <t>t2_35</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Q2.35. Intensidade de cada barreira percebida</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>table-list</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
@@ -2539,12 +2547,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>q2_35_02</t>
+          <t>q2_35_01</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Currículo sobrecarregado</t>
+          <t>Tempo</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2563,12 +2571,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>q2_35_03</t>
+          <t>q2_35_02</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Currículo sobrecarregado</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -2587,12 +2595,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>q2_35_04</t>
+          <t>q2_35_03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Materiais</t>
+          <t>Formação</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2611,12 +2619,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>q2_35_05</t>
+          <t>q2_35_04</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Materiais</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2635,12 +2643,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>q2_35_06</t>
+          <t>q2_35_05</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2659,12 +2667,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>q2_35_07</t>
+          <t>q2_35_06</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Planejamento coletivo</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2683,12 +2691,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>q2_35_08</t>
+          <t>q2_35_07</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Interdisciplinaridade</t>
+          <t>Planejamento coletivo</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2707,12 +2715,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>q2_35_09</t>
+          <t>q2_35_08</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Informações territoriais</t>
+          <t>Interdisciplinaridade</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -2731,12 +2739,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>q2_35_10</t>
+          <t>q2_35_09</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Descontinuidade</t>
+          <t>Informações territoriais</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -2755,12 +2763,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>q2_35_11</t>
+          <t>q2_35_10</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Rotatividade de profissionais</t>
+          <t>Descontinuidade</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -2779,12 +2787,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>q2_35_12</t>
+          <t>q2_35_11</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Rotatividade de profissionais</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -2798,11 +2806,19 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
+          <t>select_one intensidade</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>q2_35_12</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Outras</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
@@ -2814,31 +2830,15 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>q2_35a</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Q2.35a. Você marcou uma intensidade para "Outras" barreiras acima — quais são elas?</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>${q2_35_12} != ''</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
@@ -2846,23 +2846,31 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>select_one barreiras</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>q2_36</t>
+          <t>q2_35a</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Q2.36. Principal barreira hoje</t>
+          <t>Q2.35a. Você marcou uma intensidade para "Outras" barreiras acima — quais são elas?</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>${q2_35_12} != ''</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
@@ -2870,26 +2878,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one barreiras</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>q2_36_outro</t>
+          <t>q2_36</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q2.36. Principal barreira hoje</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>${q2_36}='outro'</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -2898,22 +2902,26 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>select_multiple materiais</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>q2_37</t>
+          <t>q2_36_outro</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Q2.37. Materiais didáticos utilizados</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>${q2_36}='outro'</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -2922,26 +2930,26 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple materiais</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>q2_37_outro</t>
+          <t>q2_37</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Q2.37. Materiais didáticos utilizados (para Educação Ambiental e/ou no dia a dia escolar)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Indique todos os que se aplicam, tanto os usados especificamente em Educação Ambiental quanto os do dia a dia escolar.</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>selected(${q2_37}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
@@ -2950,22 +2958,26 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>select_one acesso_mat</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>q2_38</t>
+          <t>q2_37_outro</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Q2.38. Facilidade de acesso a esses materiais</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>selected(${q2_37}, 'outro')</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
@@ -2974,27 +2986,23 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one acesso_mat</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>q2_39</t>
+          <t>q2_38</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Q2.39. Que materiais fazem falta?</t>
+          <t>Q2.38. Facilidade de acesso a esses materiais</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
@@ -3002,27 +3010,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>select_one part_estud</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>q2_40</t>
+          <t>q2_39</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Q2.40. Como caracterizar, de modo geral, a participação dos estudantes nas ações de EA?</t>
+          <t>Q2.39. Quais materiais fazem falta?</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
@@ -3030,21 +3038,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>select_one continuidade_proj</t>
+          <t>select_one part_estud</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>q2_41</t>
+          <t>q2_40</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Q2.41. De modo geral, a continuidade dos projetos de EA está...</t>
+          <t>Q2.40. Como caracterizar, de modo geral, a participação dos estudantes nas ações de EA?</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
@@ -3054,86 +3066,86 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>select_multiple apoio_gestao</t>
+          <t>select_one continuidade_proj</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>q2_41a</t>
+          <t>q2_41</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Q2.41a. Como a gestão escolar apoia a Educação Ambiental hoje?</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Pense no que a gestão efetivamente faz, não no que deveria fazer.</t>
-        </is>
-      </c>
+          <t>Q2.41. De modo geral, a continuidade dos projetos de EA está...</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>not(selected(., 'nenhum') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>"Nenhum apoio sistemático" não pode ser combinado com outras opções.</t>
-        </is>
-      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple apoio_gestao</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>q2_41a_outro</t>
+          <t>q2_41a</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>Q2.41a. Como a gestão escolar apoia a Educação Ambiental hoje?</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Pense no que a gestão efetivamente faz, não no que deveria fazer.</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>selected(${q2_41a}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nenhum') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>"Nenhum apoio sistemático" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>e2_leitura</t>
+          <t>q2_41a_outro</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Como o sistema está lendo suas respostas (revise e confirme) — no Kobo não há leitura automática: a tutoria/quem aplica o formulário deve revisar as respostas desta etapa antes de responder abaixo.</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>selected(${q2_41a}, 'outro')</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
@@ -3142,17 +3154,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>q2_42</t>
+          <t>evid_e2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Q2.42. Essa leitura reflete a realidade do local?</t>
+          <t>Evidências — Evidências sobre Educação Ambiental</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -3166,31 +3178,23 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>q2_43</t>
+          <t>evid_e2_nota</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Q2.43. O que precisa ser corrigido ou complementado?</t>
+          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>${q2_42}='nao' or ${q2_42}='nao_sabemos'</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
@@ -3198,17 +3202,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>select_one tipo_evid</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>evid_e2</t>
+          <t>evid_e2_tipo</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Evidências — Evidências sobre Educação Ambiental</t>
+          <t>Tipo de evidência</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -3222,22 +3226,26 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>evid_e2_nota</t>
+          <t>evid_e2_tipo_outro</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>${evid_e2_tipo}='outro'</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
@@ -3246,23 +3254,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>select_one tipo_evid</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>evid_e2_tipo</t>
+          <t>evid_e2_desc</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tipo de evidência</t>
+          <t>Descreva a evidência</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
@@ -3270,26 +3282,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>file</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>evid_e2_tipo_outro</t>
+          <t>evid_e2_anexo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Anexo (foto/documento) — opcional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>${evid_e2_tipo}='outro'</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
@@ -3298,27 +3306,15 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>evid_e2_desc</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Descreva a evidência</t>
-        </is>
-      </c>
+          <t>end_repeat</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
@@ -3326,19 +3322,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>evid_e2_anexo</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Anexo (foto/documento) — opcional</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
@@ -3350,11 +3338,19 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>etapa3</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Etapa 3 — Participação e Redes</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
@@ -3366,11 +3362,19 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
+          <t>select_multiple quem_part</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>q3_1</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Q3.1. Quem participa das ações de Educação Ambiental hoje?</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
@@ -3382,22 +3386,26 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>etapa3</t>
+          <t>q3_1_outro</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Etapa 3 — Participação e Redes</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>selected(${q3_1}, 'outro')</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
@@ -3406,20 +3414,24 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>select_multiple quem_part</t>
+          <t>select_one nivel_part</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>q3_1</t>
+          <t>q3_2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Q3.1. Quem participa das ações de Educação Ambiental hoje?</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>Q3.2. Como essa participação costuma acontecer?</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Participação não é sinônimo de presença — o que importa é o nível de envolvimento na decisão.</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
@@ -3430,54 +3442,58 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple esp_estud</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>q3_1_outro</t>
+          <t>q3_3</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q3.3. Espaços de participação estudantil existentes</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>selected(${q3_1}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nenhum') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>"Nenhum" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>select_one nivel_part</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>q3_2</t>
+          <t>q3_3_outro</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Q3.2. Como essa participação costuma acontecer?</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Participação não é sinônimo de presença — o que importa é o nível de envolvimento na decisão.</t>
-        </is>
-      </c>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>selected(${q3_3}, 'outro')</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
@@ -3486,58 +3502,50 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>select_multiple esp_estud</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>q3_3</t>
+          <t>q3_4</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Q3.3. Espaços de participação estudantil existentes</t>
+          <t>Q3.4. Descreva práticas concretas de participação estudantil (se houver)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>not(selected(., 'nenhum') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>"Nenhum" não pode ser combinado com outras opções.</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one env_fam</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>q3_3_outro</t>
+          <t>q3_5</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q3.5. Nível de envolvimento das famílias com o local</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>selected(${q3_3}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
@@ -3546,27 +3554,23 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple barr_fam</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>q3_4</t>
+          <t>q3_6</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Q3.4. Descreva práticas concretas de participação estudantil (se houver)</t>
+          <t>Q3.6. Barreiras à participação das famílias</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
@@ -3574,22 +3578,26 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>q3_5</t>
+          <t>q3_6_outro</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Q3.5. O nível de participação estudantil descrito na Etapa 2 continua condizente?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>selected(${q3_6}, 'outro')</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
@@ -3598,17 +3606,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>select_one env_fam</t>
+          <t>select_one freq5</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>q3_6</t>
+          <t>q3_7</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Q3.6. Nível de envolvimento das famílias com o local</t>
+          <t>Q3.7. Frequência de atividades do local com o território/comunidade</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3622,23 +3630,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>select_multiple barr_fam</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>q3_7</t>
+          <t>q3_8</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Q3.7. Barreiras à participação das famílias</t>
+          <t>Q3.8. Quais atividades com o território/comunidade já ocorreram?</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
@@ -3646,26 +3658,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>q3_7_outro</t>
+          <t>q3_9</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q3.9. O local tem mecanismos de escuta da comunidade?</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>selected(${q3_7}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
@@ -3674,23 +3682,31 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>select_one freq5</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>q3_8</t>
+          <t>q3_10_quais</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Q3.8. Frequência de atividades do local com o território/comunidade</t>
+          <t>Quais mecanismos de escuta existem?</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>${q3_9}='sim'</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
@@ -3698,50 +3714,58 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple instancias</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>q3_9</t>
+          <t>q3_10</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Q3.9. Quais atividades com o território/comunidade já ocorreram?</t>
+          <t>Q3.10. Quais instâncias de decisão colegiada existem e funcionam na escola?</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nenhuma') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>"Nenhuma" não pode ser combinada com outras opções.</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>q3_10</t>
+          <t>q3_10_outro</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Q3.10. O local tem mecanismos de escuta da comunidade?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>selected(${q3_10}, 'outro')</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
@@ -3750,7 +3774,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>select_multiple instancias</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3760,48 +3784,36 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Q3.11. Quais instâncias de decisão colegiada existem e funcionam neste local?</t>
+          <t>Q3.11. A gestão tem autonomia para decidir e destinar recursos a ações de Educação Ambiental?</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>not(selected(., 'nenhuma') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>"Nenhuma" não pode ser combinada com outras opções.</t>
-        </is>
-      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>q3_11_outro</t>
+          <t>net_nota</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Atores do território (NET_ACTORS). Existência, contato, parceria e articulação permanente são níveis diferentes — não confunda um com o outro. Só marque "Parceria" ou "Articulação permanente" se o local já colabora de fato com esse ator; se ele apenas existe no território ou já houve um contato pontual, isso ainda NÃO é parceria.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>selected(${q3_11}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
@@ -3810,23 +3822,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>q3_12</t>
+          <t>net_rel</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Q3.12. A gestão tem autonomia para decidir e destinar recursos a ações de Educação Ambiental?</t>
+          <t>Q3.12. Para cada tipo de ator, qual é a relação atual do local com ele?</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>table-list</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
@@ -3834,21 +3850,25 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>net_nota</t>
+          <t>net_rel_01</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Atores do território (NET_ACTORS). Existência, contato, parceria e articulação permanente são níveis diferentes — não confunda um com o outro. Só marque "Parceria" ou "Articulação permanente" se o local já colabora de fato com esse ator; se ele apenas existe no território ou já houve um contato pontual, isso ainda NÃO é parceria.</t>
+          <t>Secretaria de Educação</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
@@ -3858,27 +3878,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>net_rel</t>
+          <t>net_rel_02</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Q3.13. Para cada tipo de ator, qual é a relação atual do local com ele?</t>
+          <t>Secretaria de Meio Ambiente</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>table-list</t>
-        </is>
-      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
@@ -3891,12 +3911,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>net_rel_01</t>
+          <t>net_rel_03</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -3919,12 +3939,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>net_rel_02</t>
+          <t>net_rel_04</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -3947,12 +3967,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>net_rel_03</t>
+          <t>net_rel_05</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Assistência Social</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -3975,12 +3995,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>net_rel_04</t>
+          <t>net_rel_06</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
+          <t>Obras</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -4003,12 +4023,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>net_rel_05</t>
+          <t>net_rel_07</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Bombeiros</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -4031,12 +4051,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>net_rel_06</t>
+          <t>net_rel_08</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -4059,12 +4079,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>net_rel_07</t>
+          <t>net_rel_09</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
+          <t>Vigilância</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -4087,12 +4107,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>net_rel_08</t>
+          <t>net_rel_10</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Outro (poder público)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -4115,12 +4135,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>net_rel_09</t>
+          <t>net_rel_11</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Vigilância</t>
+          <t>Universidade</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -4143,12 +4163,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>net_rel_10</t>
+          <t>net_rel_12</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
+          <t>Instituto Federal</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -4171,12 +4191,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>net_rel_11</t>
+          <t>net_rel_13</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Local técnica</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -4199,12 +4219,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>net_rel_12</t>
+          <t>net_rel_14</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
+          <t>Centro de pesquisa</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -4227,12 +4247,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>net_rel_13</t>
+          <t>net_rel_15</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Local técnica</t>
+          <t>Museu</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -4255,12 +4275,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>net_rel_14</t>
+          <t>net_rel_16</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>Jardim botânico</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4283,12 +4303,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>net_rel_15</t>
+          <t>net_rel_17</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Museu</t>
+          <t>Outro (educação/ciência)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4311,12 +4331,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>net_rel_16</t>
+          <t>net_rel_18</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -4339,12 +4359,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>net_rel_17</t>
+          <t>net_rel_19</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>ONG</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -4367,12 +4387,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>net_rel_18</t>
+          <t>net_rel_20</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -4395,12 +4415,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>net_rel_19</t>
+          <t>net_rel_21</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Catadores</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -4423,12 +4443,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>net_rel_20</t>
+          <t>net_rel_22</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Movimentos sociais</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -4451,12 +4471,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>net_rel_21</t>
+          <t>net_rel_23</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>Coletivos</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -4479,12 +4499,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>net_rel_22</t>
+          <t>net_rel_24</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
+          <t>Grupos culturais</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -4507,12 +4527,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>net_rel_23</t>
+          <t>net_rel_25</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Coletivos</t>
+          <t>Organizações comunitárias/religiosas</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -4535,12 +4555,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>net_rel_24</t>
+          <t>net_rel_26</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
+          <t>Outro (sociedade civil)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4563,12 +4583,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>net_rel_25</t>
+          <t>net_rel_27</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Povos indígenas</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4591,12 +4611,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>net_rel_26</t>
+          <t>net_rel_28</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
+          <t>Quilombolas</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4619,12 +4639,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>net_rel_27</t>
+          <t>net_rel_29</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
+          <t>Agricultores familiares</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4647,12 +4667,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>net_rel_28</t>
+          <t>net_rel_30</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Quilombolas</t>
+          <t>Pescadores</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4675,12 +4695,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>net_rel_29</t>
+          <t>net_rel_31</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Agricultores familiares</t>
+          <t>Comunidades tradicionais</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4703,12 +4723,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>net_rel_30</t>
+          <t>net_rel_32</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Pescadores</t>
+          <t>Lideranças</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4731,12 +4751,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>net_rel_31</t>
+          <t>net_rel_33</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
+          <t>Detentores de conhecimentos locais</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4759,12 +4779,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>net_rel_32</t>
+          <t>net_rel_34</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Outro (comunidades e conhecimentos)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4782,25 +4802,13 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>select_one nivel_rel_grade</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>net_rel_33</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Detentores de conhecimentos locais</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
@@ -4810,25 +4818,21 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>select_one nivel_rel_grade</t>
+          <t>select_multiple cat_ator</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>net_rel_34</t>
+          <t>q3_13</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Outro (comunidades e conhecimentos)</t>
+          <t>Q3.13. Quais atores são prioritários para fortalecer a relação da escola com o território? (NET_PRIORITY_ACTORS)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
@@ -4838,15 +4842,27 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
-      <c r="C167" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>q3_14</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Q3.14. Cite o nome do ator mais relevante para o local hoje (ex.: UBS Vila Nova)</t>
+        </is>
+      </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
@@ -4854,21 +4870,25 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>select_multiple cat_ator</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>q3_14</t>
+          <t>q3_15</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Q3.14. Quais atores são prioritários para fortalecer a relação? (NET_PRIORITY_ACTORS)</t>
+          <t>Q3.15. O local sabe a quem contatar em uma emergência climática?</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
@@ -4883,17 +4903,21 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>q3_15</t>
+          <t>q3_16</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Q3.15. Cite o nome do ator mais relevante para o local hoje (ex.: UBS Vila Nova)</t>
+          <t>Q3.16. Quais são esses contatos?</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>${q3_15}='sim'</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr">
         <is>
           <t>multiline</t>
@@ -4911,12 +4935,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>q3_16</t>
+          <t>q3_17</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Q3.16. O local sabe a quem contatar em uma emergência climática?</t>
+          <t>Q3.17. Existe um procedimento de emergência definido para eventos climáticos?</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -4934,31 +4958,27 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>q3_17</t>
+          <t>q3_18</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Q3.17. Quais são esses contatos?</t>
+          <t>Q3.18. Esse procedimento está documentado/formalizado?</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>${q3_16}='sim'</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+          <t>${q3_17}='sim'</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
@@ -4966,27 +4986,27 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>q3_18</t>
+          <t>q3_19</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Q3.18. Existe um procedimento de emergência definido para eventos climáticos?</t>
+          <t>Q3.19. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
@@ -4994,26 +5014,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>select_multiple canais</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>q3_19</t>
+          <t>q3_20</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Q3.19. Esse procedimento está documentado/formalizado?</t>
+          <t>Q3.20. Canais de comunicação do local com a comunidade</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>${q3_18}='sim'</t>
-        </is>
-      </c>
+      <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
@@ -5027,22 +5043,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>q3_20</t>
+          <t>q3_20_outro</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Q3.20. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>selected(${q3_20}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
@@ -5050,7 +5066,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>select_multiple canais</t>
+          <t>select_one suficiente</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5060,7 +5076,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Q3.21. Canais de comunicação do local com a comunidade</t>
+          <t>Q3.21. Esses canais seriam suficientes numa emergência?</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -5079,22 +5095,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>q3_21_outro</t>
+          <t>q3_22</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q3.22. Algum grupo fica de fora desses canais de comunicação?</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>selected(${q3_21}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
@@ -5102,23 +5118,31 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>select_one suficiente</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>q3_22</t>
+          <t>q3_23</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Q3.22. Esses canais seriam suficientes numa emergência?</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Q3.23. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
@@ -5131,12 +5155,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>q3_23</t>
+          <t>q3_24</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Q3.23. Algum grupo fica de fora desses canais de comunicação?</t>
+          <t>Q3.24. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -5154,31 +5178,23 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple barr_artic</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>q3_24</t>
+          <t>q3_25</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Q3.24. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
-        </is>
-      </c>
+          <t>Q3.25. Barreiras para articular com atores do território</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
@@ -5191,22 +5207,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>q3_25</t>
+          <t>q3_25_outro</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Q3.25. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>selected(${q3_25}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
@@ -5214,7 +5230,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>select_multiple barr_artic</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5224,13 +5240,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Q3.26. Barreiras para articular com atores do território</t>
+          <t>Q3.26. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
@@ -5243,22 +5263,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>q3_26_outro</t>
+          <t>q3_27</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q3.27. Quem participou desse caso?</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>selected(${q3_26}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr"/>
+          <t>${q3_26} != ''</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
@@ -5271,17 +5295,21 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>q3_27</t>
+          <t>q3_28</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Q3.27. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
+          <t>Q3.28. O que funcionou bem?</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>${q3_26} != ''</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr">
         <is>
           <t>multiline</t>
@@ -5299,19 +5327,19 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>q3_28</t>
+          <t>q3_29</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Q3.28. Quem participou desse caso?</t>
+          <t>Q3.29. Quais foram as dificuldades?</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>${q3_27} != ''</t>
+          <t>${q3_26} != ''</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -5331,19 +5359,19 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>q3_29</t>
+          <t>q3_30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Q3.29. O que funcionou bem?</t>
+          <t>Q3.30. O que essa experiência ensinou?</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>${q3_27} != ''</t>
+          <t>${q3_26} != ''</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -5363,21 +5391,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>q3_30</t>
+          <t>q3_31</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Q3.30. Quais foram as dificuldades?</t>
+          <t>Q3.31. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>${q3_27} != ''</t>
-        </is>
-      </c>
+      <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
           <t>multiline</t>
@@ -5395,19 +5419,19 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>q3_31</t>
+          <t>q3_32</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Q3.31. O que essa experiência ensinou?</t>
+          <t>Q3.32. Por quê?</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>${q3_27} != ''</t>
+          <t>${q3_31} != ''</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -5422,27 +5446,23 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>q3_32</t>
+          <t>evid_e3</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Q3.32. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
+          <t>Evidências — Evidências sobre participação e redes</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
@@ -5450,31 +5470,23 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>q3_33</t>
+          <t>evid_e3_nota</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Q3.33. Por quê?</t>
+          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>${q3_32} != ''</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
@@ -5482,17 +5494,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>select_one tipo_evid</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>evid_e3</t>
+          <t>evid_e3_tipo</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Evidências — Evidências sobre participação e redes</t>
+          <t>Tipo de evidência</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -5506,22 +5518,26 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>evid_e3_nota</t>
+          <t>evid_e3_tipo_outro</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>${evid_e3_tipo}='outro'</t>
+        </is>
+      </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
@@ -5530,23 +5546,27 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>select_one tipo_evid</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>evid_e3_tipo</t>
+          <t>evid_e3_desc</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tipo de evidência</t>
+          <t>Descreva a evidência</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
@@ -5554,26 +5574,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>file</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>evid_e3_tipo_outro</t>
+          <t>evid_e3_anexo</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Anexo (foto/documento) — opcional</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>${evid_e3_tipo}='outro'</t>
-        </is>
-      </c>
+      <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
@@ -5582,27 +5598,15 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>evid_e3_desc</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Descreva a evidência</t>
-        </is>
-      </c>
+          <t>end_repeat</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
@@ -5610,19 +5614,11 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>evid_e3_anexo</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Anexo (foto/documento) — opcional</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
@@ -5634,11 +5630,19 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr"/>
-      <c r="C196" t="inlineStr"/>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>confirmacao</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Confirmação final</t>
+        </is>
+      </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
@@ -5650,11 +5654,19 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr"/>
-      <c r="C197" t="inlineStr"/>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>confirmacao_msg</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
+        </is>
+      </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
@@ -5666,21 +5678,25 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one confirmo</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>confirmacao</t>
+          <t>confirmacao_envio</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Confirmação final</t>
+          <t>Revisei minhas respostas e confirmo o envio.</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
@@ -5690,19 +5706,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>confirmacao_msg</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
@@ -5714,62 +5722,18 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>select_one confirmo</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>confirmacao_envio</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Revisei minhas respostas e confirmo o envio.</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5782,7 +5746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C271"/>
+  <dimension ref="A1:C273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7947,17 +7911,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -7969,12 +7933,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>material_didatico</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Material didático</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7950,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>tempo_de_planejamento</t>
+          <t>material_didatico</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tempo de planejamento</t>
+          <t>Material didático</t>
         </is>
       </c>
     </row>
@@ -8003,12 +7967,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>tempo_de_planejamento</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Tempo de planejamento</t>
         </is>
       </c>
     </row>
@@ -8020,12 +7984,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>parcerias</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Parcerias</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
@@ -8037,12 +8001,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>parcerias</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Parcerias</t>
         </is>
       </c>
     </row>
@@ -8054,29 +8018,29 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -8088,12 +8052,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>curriculo_sobrecarregado</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Currículo sobrecarregado</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -8105,12 +8069,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>curriculo_sobrecarregado</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Currículo sobrecarregado</t>
         </is>
       </c>
     </row>
@@ -8122,12 +8086,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Materiais</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -8139,12 +8103,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Materiais</t>
         </is>
       </c>
     </row>
@@ -8156,12 +8120,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8137,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>planejamento_coletivo</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Planejamento coletivo</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
@@ -8190,12 +8154,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>interdisciplinaridade</t>
+          <t>planejamento_coletivo</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Interdisciplinaridade</t>
+          <t>Planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -8207,12 +8171,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>informacoes_territoriais</t>
+          <t>interdisciplinaridade</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Informações territoriais</t>
+          <t>Interdisciplinaridade</t>
         </is>
       </c>
     </row>
@@ -8224,12 +8188,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>descontinuidade</t>
+          <t>informacoes_territoriais</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Descontinuidade</t>
+          <t>Informações territoriais</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8205,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>rotatividade_de_profissionais</t>
+          <t>descontinuidade</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Rotatividade de profissionais</t>
+          <t>Descontinuidade</t>
         </is>
       </c>
     </row>
@@ -8258,29 +8222,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>rotatividade_de_profissionais</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Rotatividade de profissionais</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Outras</t>
         </is>
       </c>
     </row>
@@ -8292,12 +8256,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
@@ -8309,12 +8273,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
@@ -8326,29 +8290,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>reserva_tempo_para_planejamento_</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Reserva tempo para planejamento coletivo</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -8360,12 +8324,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>inclui_a_ea_no_ppp_planejamento_</t>
+          <t>reserva_tempo_para_planejamento_</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Inclui a EA no PPP/planejamento anual</t>
+          <t>Reserva tempo para planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8341,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>viabiliza_recursos_e_materiais</t>
+          <t>inclui_a_ea_no_ppp_planejamento_</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Viabiliza recursos e materiais</t>
+          <t>Inclui a EA no PPP/planejamento anual</t>
         </is>
       </c>
     </row>
@@ -8394,12 +8358,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>articula_parcerias_externas</t>
+          <t>viabiliza_recursos_e_materiais</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Articula parcerias externas</t>
+          <t>Viabiliza recursos e materiais</t>
         </is>
       </c>
     </row>
@@ -8411,12 +8375,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>apoia_projetos_de_estudantes</t>
+          <t>articula_parcerias_externas</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Apoia projetos de estudantes</t>
+          <t>Articula parcerias externas</t>
         </is>
       </c>
     </row>
@@ -8428,12 +8392,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>participa_de_formacoes_sobre_o_t</t>
+          <t>apoia_projetos_de_estudantes</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Participa de formações sobre o tema</t>
+          <t>Apoia projetos de estudantes</t>
         </is>
       </c>
     </row>
@@ -8445,12 +8409,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>acompanha_e_valoriza_as_praticas</t>
+          <t>participa_de_formacoes_sobre_o_t</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Acompanha e valoriza as práticas da equipe</t>
+          <t>Participa de formações sobre o tema</t>
         </is>
       </c>
     </row>
@@ -8462,12 +8426,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>acompanha_e_valoriza_as_praticas</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Nenhum apoio sistemático</t>
+          <t>Acompanha e valoriza as práticas da equipe</t>
         </is>
       </c>
     </row>
@@ -8479,29 +8443,29 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Nenhum apoio sistemático</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>conselho_escolar</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Conselho escolar</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -8513,12 +8477,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>apm_caixa_escolar</t>
+          <t>conselho_escolar</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>APM / caixa escolar</t>
+          <t>Conselho escolar</t>
         </is>
       </c>
     </row>
@@ -8530,12 +8494,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>apm_caixa_escolar</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>APM / caixa escolar</t>
         </is>
       </c>
     </row>
@@ -8547,12 +8511,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>conselho_de_classe</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Conselho de classe</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
@@ -8564,12 +8528,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>reuniao_pedagogica_planejamento_</t>
+          <t>conselho_de_classe</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Reunião pedagógica/planejamento coletivo</t>
+          <t>Conselho de classe</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8545,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>associacao_de_pais_e_mestres</t>
+          <t>reuniao_pedagogica_planejamento_</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Associação de pais e mestres</t>
+          <t>Reunião pedagógica/planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -8598,12 +8562,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>associacao_de_pais_e_mestres</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Associação de pais e mestres</t>
         </is>
       </c>
     </row>
@@ -8615,29 +8579,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>livros_didaticos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Livros didáticos</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -8649,12 +8613,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>livros_didaticos</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Vídeos</t>
+          <t>Livros didáticos</t>
         </is>
       </c>
     </row>
@@ -8666,12 +8630,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jogos</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Jogos</t>
+          <t>Vídeos</t>
         </is>
       </c>
     </row>
@@ -8683,12 +8647,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>kits_cientificos</t>
+          <t>jogos</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Kits científicos</t>
+          <t>Jogos</t>
         </is>
       </c>
     </row>
@@ -8700,12 +8664,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>materiais_produzidos_pela_escola</t>
+          <t>kits_cientificos</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Materiais produzidos pelo local</t>
+          <t>Kits científicos</t>
         </is>
       </c>
     </row>
@@ -8717,12 +8681,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>recursos_digitais</t>
+          <t>materiais_produzidos_pela_escola</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Recursos digitais</t>
+          <t>Materiais produzidos pelo local</t>
         </is>
       </c>
     </row>
@@ -8734,29 +8698,29 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>recursos_digitais</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Recursos digitais</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -8768,12 +8732,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>facil</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Fácil</t>
         </is>
       </c>
     </row>
@@ -8785,12 +8749,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>dificil</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8766,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>dificil</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Difícil</t>
         </is>
       </c>
     </row>
@@ -8819,29 +8783,29 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>espectadores</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Espectadores</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -8853,12 +8817,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>colaboradores_pontuais</t>
+          <t>espectadores</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Colaboradores pontuais</t>
+          <t>Espectadores</t>
         </is>
       </c>
     </row>
@@ -8870,12 +8834,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>protagonistas_em_alguns_momentos</t>
+          <t>colaboradores_pontuais</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Protagonistas em alguns momentos</t>
+          <t>Colaboradores pontuais</t>
         </is>
       </c>
     </row>
@@ -8887,12 +8851,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>protagonistas_continuos</t>
+          <t>protagonistas_em_alguns_momentos</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Protagonistas contínuos</t>
+          <t>Protagonistas em alguns momentos</t>
         </is>
       </c>
     </row>
@@ -8904,29 +8868,29 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonistas_continuos</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonistas contínuos</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>garantida_institucionalmente</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Garantida institucionalmente</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -8938,12 +8902,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>dependente_de_pessoas_especifica</t>
+          <t>garantida_institucionalmente</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Dependente de pessoas específicas</t>
+          <t>Garantida institucionalmente</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8919,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>dependente_de_pessoas_especifica</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Dependente de pessoas específicas</t>
         </is>
       </c>
     </row>
@@ -8972,29 +8936,29 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -9006,12 +8970,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -9023,12 +8987,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -9040,12 +9004,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>funcionarios</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Funcionários(as)</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
@@ -9057,12 +9021,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>funcionarios</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Funcionários(as)</t>
         </is>
       </c>
     </row>
@@ -9074,12 +9038,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -9091,46 +9055,46 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>informativa</t>
+          <t>instituicao_parceira</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Informativa (recebem informação)</t>
+          <t>Instituição parceira</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>consultiva</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Consultiva (são ouvidos)</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
@@ -9142,12 +9106,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>colaborativa</t>
+          <t>informativa</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Colaborativa (constroem junto)</t>
+          <t>Informativa (recebem informação)</t>
         </is>
       </c>
     </row>
@@ -9159,12 +9123,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>consultiva</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Protagonista (decidem e conduzem)</t>
+          <t>Consultiva (são ouvidos)</t>
         </is>
       </c>
     </row>
@@ -9176,46 +9140,46 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>colaborativa</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Colaborativa (constroem junto)</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>Protagonista (decidem e conduzem)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>assembleias</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Assembleias</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -9227,12 +9191,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>projetos_protagonizados_por_estu</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Projetos protagonizados por estudantes</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
@@ -9244,12 +9208,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>conselhos</t>
+          <t>assembleias</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Conselhos</t>
+          <t>Assembleias</t>
         </is>
       </c>
     </row>
@@ -9261,12 +9225,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>projetos_protagonizados_por_estu</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Projetos protagonizados por estudantes</t>
         </is>
       </c>
     </row>
@@ -9278,46 +9242,46 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>conselhos</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Conselhos</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ausente</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>esporadico</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Esporádico</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -9329,12 +9293,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>ausente</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Ausente</t>
         </is>
       </c>
     </row>
@@ -9346,12 +9310,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ativo_protagonista</t>
+          <t>esporadico</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Ativo/protagonista</t>
+          <t>Esporádico</t>
         </is>
       </c>
     </row>
@@ -9363,46 +9327,46 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>horario_de_trabalho</t>
+          <t>ativo_protagonista</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Horário de trabalho</t>
+          <t>Ativo/protagonista</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>distancia</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Distância</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -9414,12 +9378,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>comunicacao_inadequada</t>
+          <t>horario_de_trabalho</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Comunicação inadequada</t>
+          <t>Horário de trabalho</t>
         </is>
       </c>
     </row>
@@ -9431,12 +9395,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>falta_de_convite_convocacao</t>
+          <t>distancia</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Falta de convite/convocação</t>
+          <t>Distância</t>
         </is>
       </c>
     </row>
@@ -9448,46 +9412,46 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunicacao_inadequada</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Comunicação inadequada</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>sec_educacao</t>
+          <t>falta_de_convite_convocacao</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
+          <t>Falta de convite/convocação</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>sec_meio_amb</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -9499,12 +9463,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>defesa_civil</t>
+          <t>sec_educacao</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Secretaria de Educação</t>
         </is>
       </c>
     </row>
@@ -9516,12 +9480,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>sec_saude</t>
+          <t>sec_meio_amb</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
+          <t>Secretaria de Meio Ambiente</t>
         </is>
       </c>
     </row>
@@ -9533,12 +9497,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>assist_social</t>
+          <t>defesa_civil</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9514,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>obras</t>
+          <t>sec_saude</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
     </row>
@@ -9567,12 +9531,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>bombeiros</t>
+          <t>assist_social</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
+          <t>Assistência Social</t>
         </is>
       </c>
     </row>
@@ -9584,12 +9548,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ubs</t>
+          <t>obras</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Obras</t>
         </is>
       </c>
     </row>
@@ -9601,12 +9565,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>vigilancia</t>
+          <t>bombeiros</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Vigilância</t>
+          <t>Bombeiros</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9582,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>outro_publico</t>
+          <t>ubs</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
+          <t>UBS</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9599,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>universidade</t>
+          <t>vigilancia</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Vigilância</t>
         </is>
       </c>
     </row>
@@ -9652,12 +9616,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>inst_federal</t>
+          <t>outro_publico</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
+          <t>Outro (poder público)</t>
         </is>
       </c>
     </row>
@@ -9669,12 +9633,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>escola_tecnica</t>
+          <t>universidade</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Escola técnica</t>
+          <t>Universidade</t>
         </is>
       </c>
     </row>
@@ -9686,12 +9650,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>centro_pesquisa</t>
+          <t>inst_federal</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>Instituto Federal</t>
         </is>
       </c>
     </row>
@@ -9703,12 +9667,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>museu</t>
+          <t>escola_tecnica</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Museu</t>
+          <t>Escola técnica</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9684,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>jardim_botanico</t>
+          <t>centro_pesquisa</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Centro de pesquisa</t>
         </is>
       </c>
     </row>
@@ -9737,12 +9701,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>outro_educ_ciencia</t>
+          <t>museu</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>Museu</t>
         </is>
       </c>
     </row>
@@ -9754,12 +9718,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>assoc_moradores</t>
+          <t>jardim_botanico</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Jardim botânico</t>
         </is>
       </c>
     </row>
@@ -9771,12 +9735,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>outro_educ_ciencia</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Outro (educação/ciência)</t>
         </is>
       </c>
     </row>
@@ -9788,12 +9752,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>cooperativa</t>
+          <t>assoc_moradores</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -9805,12 +9769,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>catadores</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>ONG</t>
         </is>
       </c>
     </row>
@@ -9822,12 +9786,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>mov_sociais</t>
+          <t>cooperativa</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
+          <t>Cooperativa</t>
         </is>
       </c>
     </row>
@@ -9839,12 +9803,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>coletivos</t>
+          <t>catadores</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Coletivos</t>
+          <t>Catadores</t>
         </is>
       </c>
     </row>
@@ -9856,12 +9820,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>grupos_culturais</t>
+          <t>mov_sociais</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
+          <t>Movimentos sociais</t>
         </is>
       </c>
     </row>
@@ -9873,12 +9837,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>org_comunit_relig</t>
+          <t>coletivos</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Coletivos</t>
         </is>
       </c>
     </row>
@@ -9890,12 +9854,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>outro_soc_civil</t>
+          <t>grupos_culturais</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
+          <t>Grupos culturais</t>
         </is>
       </c>
     </row>
@@ -9907,12 +9871,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>povos_indigenas</t>
+          <t>org_comunit_relig</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
+          <t>Organizações comunitárias/religiosas</t>
         </is>
       </c>
     </row>
@@ -9924,12 +9888,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>quilombolas</t>
+          <t>outro_soc_civil</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Quilombolas</t>
+          <t>Outro (sociedade civil)</t>
         </is>
       </c>
     </row>
@@ -9941,12 +9905,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>agric_familiares</t>
+          <t>povos_indigenas</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Agricultores familiares</t>
+          <t>Povos indígenas</t>
         </is>
       </c>
     </row>
@@ -9958,12 +9922,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>pescadores</t>
+          <t>quilombolas</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Pescadores</t>
+          <t>Quilombolas</t>
         </is>
       </c>
     </row>
@@ -9975,12 +9939,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>com_tradicionais</t>
+          <t>agric_familiares</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
+          <t>Agricultores familiares</t>
         </is>
       </c>
     </row>
@@ -9992,12 +9956,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>liderancas</t>
+          <t>pescadores</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Pescadores</t>
         </is>
       </c>
     </row>
@@ -10009,12 +9973,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>detentores_saberes</t>
+          <t>com_tradicionais</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Detentores de conhecimentos locais</t>
+          <t>Comunidades tradicionais</t>
         </is>
       </c>
     </row>
@@ -10026,46 +9990,46 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>outro_comunidades</t>
+          <t>liderancas</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Outro (comunidades e conhecimentos)</t>
+          <t>Lideranças</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>nao_existe</t>
+          <t>detentores_saberes</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Não existe no território</t>
+          <t>Detentores de conhecimentos locais</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>nao_sei</t>
+          <t>outro_comunidades</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Não sei se existe</t>
+          <t>Outro (comunidades e conhecimentos)</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10041,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>sem_contato</t>
+          <t>nao_existe</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Existe, mas nunca houve contato</t>
+          <t>Não existe no território</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10058,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>contato_pontual</t>
+          <t>nao_sei</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
+          <t>Não sei se existe</t>
         </is>
       </c>
     </row>
@@ -10111,12 +10075,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>parceria</t>
+          <t>sem_contato</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Parceria — já colaboram em ações combinadas</t>
+          <t>Existe, mas nunca houve contato</t>
         </is>
       </c>
     </row>
@@ -10128,46 +10092,46 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>contato_pontual</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Articulação permanente — parceria contínua e estruturada</t>
+          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>parceria</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Parceria — já colaboram em ações combinadas</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>comunicados_impressos</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Comunicados impressos</t>
+          <t>Articulação permanente — parceria contínua e estruturada</t>
         </is>
       </c>
     </row>
@@ -10179,12 +10143,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>reunioes</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
@@ -10196,12 +10160,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>comunicados_impressos</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Comunicados impressos</t>
         </is>
       </c>
     </row>
@@ -10213,12 +10177,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>alto_falante_radio_local</t>
+          <t>reunioes</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Alto-falante/rádio local</t>
+          <t>Reuniões</t>
         </is>
       </c>
     </row>
@@ -10230,46 +10194,46 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>alto_falante_radio_local</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Alto-falante/rádio local</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -10281,12 +10245,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -10298,46 +10262,46 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>falta_de_contato</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Falta de contato</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>burocracia</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Burocracia</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -10349,12 +10313,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>desconfianca_historico_de_relaca</t>
+          <t>falta_de_contato</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Desconfiança/histórico de relação</t>
+          <t>Falta de contato</t>
         </is>
       </c>
     </row>
@@ -10366,12 +10330,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>burocracia</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Burocracia</t>
         </is>
       </c>
     </row>
@@ -10383,10 +10347,44 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
+          <t>desconfianca_historico_de_relaca</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Desconfiança/histórico de relação</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>barr_artic</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>falta_de_tempo</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Falta de tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>barr_artic</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
           <t>outro</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
+      <c r="C273" t="inlineStr">
         <is>
           <t>Outra</t>
         </is>

--- a/kobo/gestores_semana2_diagnostico.xlsx
+++ b/kobo/gestores_semana2_diagnostico.xlsx
@@ -1055,8 +1055,16 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1159,8 +1167,16 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1999,8 +2015,16 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2111,8 +2135,16 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2951,8 +2983,16 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
@@ -5746,7 +5786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C273"/>
+  <dimension ref="A1:C278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6534,17 +6574,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>areas_curr</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>disciplinas_separadas</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Disciplinas separadas</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6556,12 +6596,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>mesmo_tema_sem_planejamento_conj</t>
+          <t>disciplinas_separadas</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mesmo tema, sem planejamento conjunto</t>
+          <t>Disciplinas separadas</t>
         </is>
       </c>
     </row>
@@ -6573,12 +6613,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>algum_planejamento_conjunto</t>
+          <t>mesmo_tema_sem_planejamento_conj</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algum planejamento conjunto</t>
+          <t>Mesmo tema, sem planejamento conjunto</t>
         </is>
       </c>
     </row>
@@ -6590,12 +6630,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>investigacao_conjunta</t>
+          <t>algum_planejamento_conjunto</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Investigação conjunta</t>
+          <t>Algum planejamento conjunto</t>
         </is>
       </c>
     </row>
@@ -6607,12 +6647,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>objetivos_comuns</t>
+          <t>investigacao_conjunta</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Objetivos comuns</t>
+          <t>Investigação conjunta</t>
         </is>
       </c>
     </row>
@@ -6624,12 +6664,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>intervencao_territorial_coletiva</t>
+          <t>objetivos_comuns</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Intervenção territorial coletiva</t>
+          <t>Objetivos comuns</t>
         </is>
       </c>
     </row>
@@ -6641,12 +6681,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>sem_articulacao</t>
+          <t>intervencao_territorial_coletiva</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sem articulação</t>
+          <t>Intervenção territorial coletiva</t>
         </is>
       </c>
     </row>
@@ -6658,29 +6698,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>sem_articulacao</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Sem articulação</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>freq_ea</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>diaria</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Diária</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6692,12 +6732,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>diaria</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Semanal</t>
+          <t>Diária</t>
         </is>
       </c>
     </row>
@@ -6709,12 +6749,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>semanal</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Semanal</t>
         </is>
       </c>
     </row>
@@ -6726,12 +6766,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>esporadica</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Esporádica</t>
+          <t>Mensal</t>
         </is>
       </c>
     </row>
@@ -6743,12 +6783,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>anual</t>
+          <t>esporadica</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Anual</t>
+          <t>Esporádica</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6800,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nao_ocorre</t>
+          <t>anual</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Não ocorre</t>
+          <t>Anual</t>
         </is>
       </c>
     </row>
@@ -6777,29 +6817,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nao_ocorre</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Não ocorre</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>contexto_ea</t>
+          <t>freq_ea</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>sala_de_aula</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sala de aula</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6811,12 +6851,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>patio_area_externa</t>
+          <t>sala_de_aula</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pátio/área externa</t>
+          <t>Sala de aula</t>
         </is>
       </c>
     </row>
@@ -6828,12 +6868,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>visita_de_campo</t>
+          <t>patio_area_externa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Visita de campo</t>
+          <t>Pátio/área externa</t>
         </is>
       </c>
     </row>
@@ -6845,12 +6885,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>projeto_especial</t>
+          <t>visita_de_campo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Projeto especial</t>
+          <t>Visita de campo</t>
         </is>
       </c>
     </row>
@@ -6862,12 +6902,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>feira</t>
+          <t>projeto_especial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Feira</t>
+          <t>Projeto especial</t>
         </is>
       </c>
     </row>
@@ -6879,46 +6919,46 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>feira</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Feira</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>professor_individualmente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Professor(a) individualmente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>grupo_de_professores</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Grupo de professores(as)</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6930,12 +6970,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>coordenacao_pedagogica</t>
+          <t>professor_individualmente</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Coordenação pedagógica</t>
+          <t>Professor(a) individualmente</t>
         </is>
       </c>
     </row>
@@ -6947,12 +6987,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>grupo_de_professores</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Grupo de professores(as)</t>
         </is>
       </c>
     </row>
@@ -6964,12 +7004,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>coordenacao_pedagogica</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Coordenação pedagógica</t>
         </is>
       </c>
     </row>
@@ -6981,46 +7021,46 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>espectador</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Espectador</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>participante_pontual</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Participante pontual</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7072,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>espectador</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Protagonista</t>
+          <t>Espectador</t>
         </is>
       </c>
     </row>
@@ -7049,12 +7089,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>coprodutor</t>
+          <t>participante_pontual</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Coprodutor</t>
+          <t>Participante pontual</t>
         </is>
       </c>
     </row>
@@ -7066,46 +7106,46 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonista</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>continuidade_ativ</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>depende_da_permanencia_de_profes</t>
+          <t>coprodutor</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Depende da permanência de professor(a) específico(a)</t>
+          <t>Coprodutor</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>continuidade_ativ</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tem continuidade institucional garantida</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7117,12 +7157,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>depende_da_permanencia_de_profes</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Depende da permanência de professor(a) específico(a)</t>
         </is>
       </c>
     </row>
@@ -7134,46 +7174,46 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Tem continuidade institucional garantida</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>continuidade_ativ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nunca</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Nunca</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>continuidade_ativ</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>raramente</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raramente</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7185,12 +7225,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>as_vezes</t>
+          <t>nunca</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Às vezes</t>
+          <t>Nunca</t>
         </is>
       </c>
     </row>
@@ -7202,12 +7242,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>frequentemente</t>
+          <t>raramente</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Frequentemente</t>
+          <t>Raramente</t>
         </is>
       </c>
     </row>
@@ -7219,46 +7259,46 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>as_vezes</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Às vezes</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>agua</t>
+          <t>frequentemente</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Frequentemente</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>biodiversidade</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Biodiversidade</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7270,12 +7310,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>residuos</t>
+          <t>agua</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Resíduos</t>
+          <t>Água</t>
         </is>
       </c>
     </row>
@@ -7287,12 +7327,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>mudancas_climaticas</t>
+          <t>biodiversidade</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mudanças climáticas</t>
+          <t>Biodiversidade</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7344,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>residuos</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Resíduos</t>
         </is>
       </c>
     </row>
@@ -7321,12 +7361,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>alimentacao</t>
+          <t>mudancas_climaticas</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Mudanças climáticas</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7378,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>consumo</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Energia</t>
         </is>
       </c>
     </row>
@@ -7355,12 +7395,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>saneamento</t>
+          <t>alimentacao</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Saneamento</t>
+          <t>Alimentação</t>
         </is>
       </c>
     </row>
@@ -7372,12 +7412,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>saude</t>
+          <t>consumo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>Consumo</t>
         </is>
       </c>
     </row>
@@ -7389,12 +7429,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>riscos_desastres</t>
+          <t>saneamento</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Riscos/desastres</t>
+          <t>Saneamento</t>
         </is>
       </c>
     </row>
@@ -7406,12 +7446,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>justica_socioambiental</t>
+          <t>saude</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Justiça socioambiental</t>
+          <t>Saúde</t>
         </is>
       </c>
     </row>
@@ -7423,12 +7463,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>territorio</t>
+          <t>riscos_desastres</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Território</t>
+          <t>Riscos/desastres</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7480,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>conflitos</t>
+          <t>justica_socioambiental</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Conflitos</t>
+          <t>Justiça socioambiental</t>
         </is>
       </c>
     </row>
@@ -7457,12 +7497,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>povos_e_comunidades_tradicionais</t>
+          <t>territorio</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Povos e comunidades tradicionais</t>
+          <t>Território</t>
         </is>
       </c>
     </row>
@@ -7474,63 +7514,63 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>conflitos</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Conflitos</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>falta_de_formacao</t>
+          <t>povos_e_comunidades_tradicionais</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Falta de formação</t>
+          <t>Povos e comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>falta_de_material</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Falta de material</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>tema_sensivel_delicado</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tema sensível/delicado</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7582,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>falta_de_formacao</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Falta de formação</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7599,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>curriculo</t>
+          <t>falta_de_material</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Currículo</t>
+          <t>Falta de material</t>
         </is>
       </c>
     </row>
@@ -7576,63 +7616,63 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>tema_sensivel_delicado</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Tema sensível/delicado</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>aula_expositiva</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Aula expositiva</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>projeto</t>
+          <t>curriculo</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Currículo</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>oficina</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Oficina</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -7644,12 +7684,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>saida_de_campo</t>
+          <t>aula_expositiva</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Saída de campo</t>
+          <t>Aula expositiva</t>
         </is>
       </c>
     </row>
@@ -7661,12 +7701,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>horta_experimentacao</t>
+          <t>projeto</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Horta/experimentação</t>
+          <t>Projeto</t>
         </is>
       </c>
     </row>
@@ -7678,12 +7718,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>rodas_de_conversa</t>
+          <t>oficina</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Rodas de conversa</t>
+          <t>Oficina</t>
         </is>
       </c>
     </row>
@@ -7695,12 +7735,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>producao_audiovisual</t>
+          <t>saida_de_campo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Produção audiovisual</t>
+          <t>Saída de campo</t>
         </is>
       </c>
     </row>
@@ -7712,12 +7752,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>cartografia</t>
+          <t>horta_experimentacao</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Cartografia</t>
+          <t>Horta/experimentação</t>
         </is>
       </c>
     </row>
@@ -7729,80 +7769,80 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>rodas_de_conversa</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Rodas de conversa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>producao_audiovisual</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Produção audiovisual</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>pouco</t>
+          <t>cartografia</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pouco</t>
+          <t>Cartografia</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>significativo</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Significativo</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7814,80 +7854,80 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>pouco</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>1 — Nada confiante(a)</t>
+          <t>Pouco</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2 — Pouco confiante</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>significativo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>3 — Moderadamente confiante</t>
+          <t>Significativo</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>4 — Confiante</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7939,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>5 — Muito confiante</t>
+          <t>1 — Nada confiante(a)</t>
         </is>
       </c>
     </row>
@@ -7916,80 +7956,80 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>2 — Pouco confiante</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>3 — Moderadamente confiante</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>material_didatico</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Material didático</t>
+          <t>4 — Confiante</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>tempo_de_planejamento</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tempo de planejamento</t>
+          <t>5 — Muito confiante</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -8001,12 +8041,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>parcerias</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Parcerias</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -8018,12 +8058,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>material_didatico</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Material didático</t>
         </is>
       </c>
     </row>
@@ -8035,80 +8075,80 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>tempo_de_planejamento</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Tempo de planejamento</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>curriculo_sobrecarregado</t>
+          <t>parcerias</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Currículo sobrecarregado</t>
+          <t>Parcerias</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Materiais</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8160,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8177,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>curriculo_sobrecarregado</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Currículo sobrecarregado</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8194,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>planejamento_coletivo</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Planejamento coletivo</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -8171,12 +8211,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>interdisciplinaridade</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Interdisciplinaridade</t>
+          <t>Materiais</t>
         </is>
       </c>
     </row>
@@ -8188,12 +8228,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>informacoes_territoriais</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Informações territoriais</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -8205,12 +8245,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>descontinuidade</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Descontinuidade</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
@@ -8222,12 +8262,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>rotatividade_de_profissionais</t>
+          <t>planejamento_coletivo</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Rotatividade de profissionais</t>
+          <t>Planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -8239,148 +8279,148 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>interdisciplinaridade</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Interdisciplinaridade</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>informacoes_territoriais</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Informações territoriais</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>descontinuidade</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Descontinuidade</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>rotatividade_de_profissionais</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Rotatividade de profissionais</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Outras</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>reserva_tempo_para_planejamento_</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Reserva tempo para planejamento coletivo</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>inclui_a_ea_no_ppp_planejamento_</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Inclui a EA no PPP/planejamento anual</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>viabiliza_recursos_e_materiais</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Viabiliza recursos e materiais</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>articula_parcerias_externas</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Articula parcerias externas</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -8392,12 +8432,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>apoia_projetos_de_estudantes</t>
+          <t>reserva_tempo_para_planejamento_</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Apoia projetos de estudantes</t>
+          <t>Reserva tempo para planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -8409,12 +8449,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>participa_de_formacoes_sobre_o_t</t>
+          <t>inclui_a_ea_no_ppp_planejamento_</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Participa de formações sobre o tema</t>
+          <t>Inclui a EA no PPP/planejamento anual</t>
         </is>
       </c>
     </row>
@@ -8426,12 +8466,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>acompanha_e_valoriza_as_praticas</t>
+          <t>viabiliza_recursos_e_materiais</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Acompanha e valoriza as práticas da equipe</t>
+          <t>Viabiliza recursos e materiais</t>
         </is>
       </c>
     </row>
@@ -8443,12 +8483,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>articula_parcerias_externas</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Nenhum apoio sistemático</t>
+          <t>Articula parcerias externas</t>
         </is>
       </c>
     </row>
@@ -8460,80 +8500,80 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>apoia_projetos_de_estudantes</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Apoia projetos de estudantes</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>conselho_escolar</t>
+          <t>participa_de_formacoes_sobre_o_t</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Conselho escolar</t>
+          <t>Participa de formações sobre o tema</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>apm_caixa_escolar</t>
+          <t>acompanha_e_valoriza_as_praticas</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>APM / caixa escolar</t>
+          <t>Acompanha e valoriza as práticas da equipe</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>Nenhum apoio sistemático</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>conselho_de_classe</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Conselho de classe</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -8545,12 +8585,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>reuniao_pedagogica_planejamento_</t>
+          <t>conselho_escolar</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Reunião pedagógica/planejamento coletivo</t>
+          <t>Conselho escolar</t>
         </is>
       </c>
     </row>
@@ -8562,12 +8602,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>associacao_de_pais_e_mestres</t>
+          <t>apm_caixa_escolar</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Associação de pais e mestres</t>
+          <t>APM / caixa escolar</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8619,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
@@ -8596,80 +8636,80 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>conselho_de_classe</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Conselho de classe</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>livros_didaticos</t>
+          <t>reuniao_pedagogica_planejamento_</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Livros didáticos</t>
+          <t>Reunião pedagógica/planejamento coletivo</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>associacao_de_pais_e_mestres</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Vídeos</t>
+          <t>Associação de pais e mestres</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>jogos</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Jogos</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>kits_cientificos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Kits científicos</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -8681,12 +8721,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>materiais_produzidos_pela_escola</t>
+          <t>livros_didaticos</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Materiais produzidos pelo local</t>
+          <t>Livros didáticos</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8738,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>recursos_digitais</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Recursos digitais</t>
+          <t>Vídeos</t>
         </is>
       </c>
     </row>
@@ -8715,87 +8755,87 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>jogos</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Jogos</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>kits_cientificos</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Kits científicos</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>materiais_produzidos_pela_escola</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Materiais produzidos pelo local</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>dificil</t>
+          <t>recursos_digitais</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Recursos digitais</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8812,75 +8852,75 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>espectadores</t>
+          <t>facil</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Espectadores</t>
+          <t>Fácil</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>colaboradores_pontuais</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Colaboradores pontuais</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>protagonistas_em_alguns_momentos</t>
+          <t>dificil</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Protagonistas em alguns momentos</t>
+          <t>Difícil</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>protagonistas_continuos</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Protagonistas contínuos</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8897,153 +8937,153 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>garantida_institucionalmente</t>
+          <t>espectadores</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Garantida institucionalmente</t>
+          <t>Espectadores</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>dependente_de_pessoas_especifica</t>
+          <t>colaboradores_pontuais</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Dependente de pessoas específicas</t>
+          <t>Colaboradores pontuais</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>protagonistas_em_alguns_momentos</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Protagonistas em alguns momentos</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonistas_continuos</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonistas contínuos</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>garantida_institucionalmente</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Garantida institucionalmente</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>dependente_de_pessoas_especifica</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Dependente de pessoas específicas</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>funcionarios</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Funcionários(as)</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -9055,12 +9095,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -9072,12 +9112,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>instituicao_parceira</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Instituição parceira</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -9089,182 +9129,182 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>informativa</t>
+          <t>funcionarios</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Informativa (recebem informação)</t>
+          <t>Funcionários(as)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>consultiva</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Consultiva (são ouvidos)</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>colaborativa</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Colaborativa (constroem junto)</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>instituicao_parceira</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Protagonista (decidem e conduzem)</t>
+          <t>Instituição parceira</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>informativa</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>Informativa (recebem informação)</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>assembleias</t>
+          <t>consultiva</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Assembleias</t>
+          <t>Consultiva (são ouvidos)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>projetos_protagonizados_por_estu</t>
+          <t>colaborativa</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Projetos protagonizados por estudantes</t>
+          <t>Colaborativa (constroem junto)</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>conselhos</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Conselhos</t>
+          <t>Protagonista (decidem e conduzem)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -9276,267 +9316,267 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ausente</t>
+          <t>assembleias</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Assembleias</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>esporadico</t>
+          <t>projetos_protagonizados_por_estu</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Esporádico</t>
+          <t>Projetos protagonizados por estudantes</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>conselhos</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Conselhos</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ativo_protagonista</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Ativo/protagonista</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>horario_de_trabalho</t>
+          <t>ausente</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Horário de trabalho</t>
+          <t>Ausente</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>distancia</t>
+          <t>esporadico</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Distância</t>
+          <t>Esporádico</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>comunicacao_inadequada</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Comunicação inadequada</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>falta_de_convite_convocacao</t>
+          <t>ativo_protagonista</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Falta de convite/convocação</t>
+          <t>Ativo/protagonista</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>sec_educacao</t>
+          <t>horario_de_trabalho</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
+          <t>Horário de trabalho</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>sec_meio_amb</t>
+          <t>distancia</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
+          <t>Distância</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>defesa_civil</t>
+          <t>comunicacao_inadequada</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Comunicação inadequada</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>sec_saude</t>
+          <t>falta_de_convite_convocacao</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
+          <t>Falta de convite/convocação</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>assist_social</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -9548,12 +9588,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>obras</t>
+          <t>sec_educacao</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>Secretaria de Educação</t>
         </is>
       </c>
     </row>
@@ -9565,12 +9605,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>bombeiros</t>
+          <t>sec_meio_amb</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
+          <t>Secretaria de Meio Ambiente</t>
         </is>
       </c>
     </row>
@@ -9582,12 +9622,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ubs</t>
+          <t>defesa_civil</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
     </row>
@@ -9599,12 +9639,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>vigilancia</t>
+          <t>sec_saude</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Vigilância</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
     </row>
@@ -9616,12 +9656,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>outro_publico</t>
+          <t>assist_social</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
+          <t>Assistência Social</t>
         </is>
       </c>
     </row>
@@ -9633,12 +9673,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>universidade</t>
+          <t>obras</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Obras</t>
         </is>
       </c>
     </row>
@@ -9650,12 +9690,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>inst_federal</t>
+          <t>bombeiros</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
+          <t>Bombeiros</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9707,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>escola_tecnica</t>
+          <t>ubs</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Escola técnica</t>
+          <t>UBS</t>
         </is>
       </c>
     </row>
@@ -9684,12 +9724,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>centro_pesquisa</t>
+          <t>vigilancia</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>Vigilância</t>
         </is>
       </c>
     </row>
@@ -9701,12 +9741,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>museu</t>
+          <t>outro_publico</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Museu</t>
+          <t>Outro (poder público)</t>
         </is>
       </c>
     </row>
@@ -9718,12 +9758,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>jardim_botanico</t>
+          <t>universidade</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Universidade</t>
         </is>
       </c>
     </row>
@@ -9735,12 +9775,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>outro_educ_ciencia</t>
+          <t>inst_federal</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>Instituto Federal</t>
         </is>
       </c>
     </row>
@@ -9752,12 +9792,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>assoc_moradores</t>
+          <t>escola_tecnica</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Escola técnica</t>
         </is>
       </c>
     </row>
@@ -9769,12 +9809,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>centro_pesquisa</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Centro de pesquisa</t>
         </is>
       </c>
     </row>
@@ -9786,12 +9826,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>cooperativa</t>
+          <t>museu</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Museu</t>
         </is>
       </c>
     </row>
@@ -9803,12 +9843,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>catadores</t>
+          <t>jardim_botanico</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>Jardim botânico</t>
         </is>
       </c>
     </row>
@@ -9820,12 +9860,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>mov_sociais</t>
+          <t>outro_educ_ciencia</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
+          <t>Outro (educação/ciência)</t>
         </is>
       </c>
     </row>
@@ -9837,12 +9877,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>coletivos</t>
+          <t>assoc_moradores</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Coletivos</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -9854,12 +9894,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>grupos_culturais</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
+          <t>ONG</t>
         </is>
       </c>
     </row>
@@ -9871,12 +9911,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>org_comunit_relig</t>
+          <t>cooperativa</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Cooperativa</t>
         </is>
       </c>
     </row>
@@ -9888,12 +9928,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>outro_soc_civil</t>
+          <t>catadores</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
+          <t>Catadores</t>
         </is>
       </c>
     </row>
@@ -9905,12 +9945,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>povos_indigenas</t>
+          <t>mov_sociais</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
+          <t>Movimentos sociais</t>
         </is>
       </c>
     </row>
@@ -9922,12 +9962,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>quilombolas</t>
+          <t>coletivos</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Quilombolas</t>
+          <t>Coletivos</t>
         </is>
       </c>
     </row>
@@ -9939,12 +9979,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>agric_familiares</t>
+          <t>grupos_culturais</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Agricultores familiares</t>
+          <t>Grupos culturais</t>
         </is>
       </c>
     </row>
@@ -9956,12 +9996,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>pescadores</t>
+          <t>org_comunit_relig</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Pescadores</t>
+          <t>Organizações comunitárias/religiosas</t>
         </is>
       </c>
     </row>
@@ -9973,12 +10013,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>com_tradicionais</t>
+          <t>outro_soc_civil</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
+          <t>Outro (sociedade civil)</t>
         </is>
       </c>
     </row>
@@ -9990,12 +10030,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>liderancas</t>
+          <t>povos_indigenas</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Povos indígenas</t>
         </is>
       </c>
     </row>
@@ -10007,12 +10047,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>detentores_saberes</t>
+          <t>quilombolas</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Detentores de conhecimentos locais</t>
+          <t>Quilombolas</t>
         </is>
       </c>
     </row>
@@ -10024,97 +10064,97 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>outro_comunidades</t>
+          <t>agric_familiares</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Outro (comunidades e conhecimentos)</t>
+          <t>Agricultores familiares</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>nao_existe</t>
+          <t>pescadores</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Não existe no território</t>
+          <t>Pescadores</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>nao_sei</t>
+          <t>com_tradicionais</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Não sei se existe</t>
+          <t>Comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>sem_contato</t>
+          <t>liderancas</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Existe, mas nunca houve contato</t>
+          <t>Lideranças</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>contato_pontual</t>
+          <t>detentores_saberes</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
+          <t>Detentores de conhecimentos locais</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>parceria</t>
+          <t>outro_comunidades</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Parceria — já colaboram em ações combinadas</t>
+          <t>Outro (comunidades e conhecimentos)</t>
         </is>
       </c>
     </row>
@@ -10126,97 +10166,97 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>nao_existe</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Articulação permanente — parceria contínua e estruturada</t>
+          <t>Não existe no território</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>nao_sei</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Não sei se existe</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>comunicados_impressos</t>
+          <t>sem_contato</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Comunicados impressos</t>
+          <t>Existe, mas nunca houve contato</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>reunioes</t>
+          <t>contato_pontual</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>parceria</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Parceria — já colaboram em ações combinadas</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>alto_falante_radio_local</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Alto-falante/rádio local</t>
+          <t>Articulação permanente — parceria contínua e estruturada</t>
         </is>
       </c>
     </row>
@@ -10228,163 +10268,248 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>comunicados_impressos</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Comunicados impressos</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>reunioes</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Reuniões</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>alto_falante_radio_local</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Alto-falante/rádio local</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>falta_de_contato</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Falta de contato</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>burocracia</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Burocracia</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>desconfianca_historico_de_relaca</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Desconfiança/histórico de relação</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
+          <t>suficiente</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>nao_sabe</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Não sabe</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
           <t>barr_artic</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>falta_de_contato</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Falta de contato</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>barr_artic</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>burocracia</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Burocracia</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>barr_artic</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>desconfianca_historico_de_relaca</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Desconfiança/histórico de relação</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>barr_artic</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>falta_de_tempo</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Falta de tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>barr_artic</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
         <is>
           <t>outro</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
+      <c r="C278" t="inlineStr">
         <is>
           <t>Outra</t>
         </is>
